--- a/assets/deen/madrasa/class_manager.xlsx
+++ b/assets/deen/madrasa/class_manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SehhaDeveloper\src\l3\edu-journey\assets\deen\madrasa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E3159B-6602-4AB5-849E-6090519BBF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F97A1FA-5CD9-41E7-B1B9-080268B6994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="211">
   <si>
     <t>Madrasa Class Dashboard</t>
   </si>
@@ -1022,6 +1022,15 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1051,15 +1060,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2082,40 +2082,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="59"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="62"/>
     </row>
     <row r="3" spans="1:14" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -2187,11 +2187,11 @@
       </c>
       <c r="H5" s="52">
         <f>COUNTIF(AttendanceTable[Student],$B$4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="52">
         <f>COUNTIF(ProgressTable[Student],$B$4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2229,14 +2229,14 @@
         <v>14</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="63" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="60"/>
-      <c r="F7" s="60"/>
-      <c r="G7" s="60"/>
-      <c r="H7" s="60"/>
-      <c r="I7" s="60"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -2297,13 +2297,13 @@
       <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:14" ht="25" customHeight="1">
-      <c r="A11" s="61" t="s">
+      <c r="A11" s="64" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="62"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="E20" s="3">
         <f>COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],D20)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2731,13 +2731,13 @@
       <c r="N29" s="4"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="63" t="s">
+      <c r="A30" s="66" t="s">
         <v>204</v>
       </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
+      <c r="B30" s="63"/>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -2749,11 +2749,11 @@
       <c r="N30" s="4"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="63"/>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
+      <c r="A31" s="66"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -3031,30 +3031,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="62"/>
     </row>
     <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -10657,28 +10657,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -10880,7 +10880,9 @@
       <c r="E8" s="18">
         <v>0.47986111111111113</v>
       </c>
-      <c r="F8" s="17"/>
+      <c r="F8" s="17">
+        <v>1</v>
+      </c>
       <c r="G8" s="17"/>
       <c r="H8" s="19"/>
       <c r="I8" s="1"/>
@@ -10918,7 +10920,9 @@
       <c r="E9" s="26">
         <v>0.47986111111111113</v>
       </c>
-      <c r="F9" s="25"/>
+      <c r="F9" s="25">
+        <v>1</v>
+      </c>
       <c r="G9" s="25"/>
       <c r="H9" s="27"/>
       <c r="I9" s="1"/>
@@ -10956,7 +10960,9 @@
       <c r="E10" s="18">
         <v>0.47986111111111113</v>
       </c>
-      <c r="F10" s="17"/>
+      <c r="F10" s="17">
+        <v>1</v>
+      </c>
       <c r="G10" s="17"/>
       <c r="H10" s="19"/>
       <c r="I10" s="1"/>
@@ -10979,12 +10985,24 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="25" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="25"/>
+      <c r="A11" s="29">
+        <v>46278</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="26">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="F11" s="25">
+        <v>1</v>
+      </c>
       <c r="G11" s="25"/>
       <c r="H11" s="27"/>
       <c r="I11" s="1"/>
@@ -11007,12 +11025,24 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="25" customHeight="1">
-      <c r="A12" s="29"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="17"/>
+      <c r="A12" s="29">
+        <v>46278</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="F12" s="17">
+        <v>1</v>
+      </c>
       <c r="G12" s="17"/>
       <c r="H12" s="19"/>
       <c r="I12" s="1"/>
@@ -11035,12 +11065,24 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="25" customHeight="1">
-      <c r="A13" s="28"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="25"/>
+      <c r="A13" s="29">
+        <v>46278</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="26">
+        <v>0.52361111111111114</v>
+      </c>
+      <c r="F13" s="25">
+        <v>1</v>
+      </c>
       <c r="G13" s="25"/>
       <c r="H13" s="27"/>
       <c r="I13" s="1"/>
@@ -17807,24 +17849,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="62"/>
     </row>
     <row r="3" spans="1:6" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -18008,28 +18050,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -18209,28 +18251,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="59"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="1:8" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -18788,32 +18830,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="59"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -25826,30 +25868,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="62"/>
     </row>
     <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -26052,7 +26094,7 @@
       <c r="C8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="64" t="s">
+      <c r="D8" s="54" t="s">
         <v>205</v>
       </c>
       <c r="E8" s="40">
@@ -26098,7 +26140,7 @@
       <c r="C9" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="65" t="s">
+      <c r="D9" s="55" t="s">
         <v>206</v>
       </c>
       <c r="E9" s="42">
@@ -26142,7 +26184,7 @@
       <c r="C10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="66" t="s">
+      <c r="D10" s="56" t="s">
         <v>209</v>
       </c>
       <c r="E10" s="40">
@@ -26179,10 +26221,18 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="25" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
+      <c r="A11" s="28">
+        <v>46278</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="25">
+        <v>423</v>
+      </c>
       <c r="E11" s="42"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
@@ -26207,9 +26257,15 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="25" customHeight="1">
-      <c r="A12" s="29"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="28">
+        <v>46278</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="D12" s="17"/>
       <c r="E12" s="40"/>
       <c r="F12" s="17"/>
@@ -26235,9 +26291,15 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="25" customHeight="1">
-      <c r="A13" s="28"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="28">
+        <v>46278</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>15</v>
+      </c>
       <c r="D13" s="25"/>
       <c r="E13" s="42"/>
       <c r="F13" s="25"/>
@@ -32974,32 +33036,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="59"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="62"/>
     </row>
     <row r="3" spans="1:10" ht="25" customHeight="1">
       <c r="A3" s="2"/>
@@ -33432,30 +33494,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="57" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="56"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="60" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="59"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="62"/>
     </row>
     <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>

--- a/assets/deen/madrasa/class_manager.xlsx
+++ b/assets/deen/madrasa/class_manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SehhaDeveloper\src\l3\edu-journey\assets\deen\madrasa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F97A1FA-5CD9-41E7-B1B9-080268B6994C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D04C380-6FE9-44DC-AB03-EC8F88B25B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="210">
   <si>
     <t>Madrasa Class Dashboard</t>
   </si>
@@ -662,9 +662,6 @@
     <t>`447-448</t>
   </si>
   <si>
-    <t>548</t>
-  </si>
-  <si>
     <t>Secure</t>
   </si>
   <si>
@@ -1236,13 +1233,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.6</c:v>
+                  <c:v>0.70000000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.66666666666666663</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.95</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1529,7 +1526,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.5</c:v>
+                  <c:v>0.70000000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2138,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="50" t="s">
@@ -2179,7 +2176,7 @@
       </c>
       <c r="F5" s="51">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],$B$4,ProgressTable[Mastery %]))</f>
-        <v>0.5</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="G5" s="51" t="str">
         <f>IF(COUNTIFS(AssessmentTable[Student],$B$4,AssessmentTable[Percentage],"&lt;&gt;")=0,"",AVERAGEIF(AssessmentTable[Student],$B$4,AssessmentTable[Percentage]))</f>
@@ -2205,7 +2202,7 @@
       </c>
       <c r="B6" s="16" t="str">
         <f>B4</f>
-        <v>Nafisa</v>
+        <v>Mudhir</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -2226,7 +2223,7 @@
       </c>
       <c r="B7" s="16">
         <f>IFERROR(VLOOKUP(B4,Students!$B$5:$D$50,2,FALSE),"")</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="63" t="s">
@@ -2347,7 +2344,7 @@
       </c>
       <c r="B13" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A13,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A13,ProgressTable[Mastery %]))</f>
-        <v>0.6</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="C13" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A13)=0,"",(COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A13))</f>
@@ -2378,7 +2375,7 @@
       </c>
       <c r="B14" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A14,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A14,ProgressTable[Mastery %]))</f>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="C14" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A14)=0,"",(COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A14))</f>
@@ -2409,7 +2406,7 @@
       </c>
       <c r="B15" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A15,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A15,ProgressTable[Mastery %]))</f>
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="C15" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A15)=0,"",(COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A15))</f>
@@ -2511,7 +2508,7 @@
       </c>
       <c r="B20" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;")=0,"",SUMIFS(ProgressTable[Mastery %],ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20)/COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;"))</f>
-        <v>0.5</v>
+        <v>0.70000000000000007</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="53" t="s">
@@ -26140,8 +26137,8 @@
       <c r="C9" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="55" t="s">
-        <v>206</v>
+      <c r="D9" s="55">
+        <v>547</v>
       </c>
       <c r="E9" s="42">
         <v>0.7</v>
@@ -26150,10 +26147,10 @@
         <v>56</v>
       </c>
       <c r="G9" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="H9" s="25" t="s">
         <v>207</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>208</v>
       </c>
       <c r="I9" s="27"/>
       <c r="J9" s="1"/>
@@ -26185,7 +26182,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E10" s="40">
         <v>0.9</v>
@@ -26197,7 +26194,7 @@
         <v>104</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I10" s="19" t="s">
         <v>106</v>
@@ -26233,11 +26230,21 @@
       <c r="D11" s="25">
         <v>423</v>
       </c>
-      <c r="E11" s="42"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="27"/>
+      <c r="E11" s="42">
+        <v>0.8</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="I11" s="27" t="s">
+        <v>106</v>
+      </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -26266,12 +26273,24 @@
       <c r="C12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="19"/>
+      <c r="D12" s="17">
+        <v>548</v>
+      </c>
+      <c r="E12" s="40">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>106</v>
+      </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -26300,12 +26319,24 @@
       <c r="C13" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="27"/>
+      <c r="D13" s="25">
+        <v>449</v>
+      </c>
+      <c r="E13" s="42">
+        <v>1</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="I13" s="27" t="s">
+        <v>106</v>
+      </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>

--- a/assets/deen/madrasa/class_manager.xlsx
+++ b/assets/deen/madrasa/class_manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SehhaDeveloper\src\l3\edu-journey\assets\deen\madrasa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D04C380-6FE9-44DC-AB03-EC8F88B25B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A381B3C7-BC96-4B67-94AA-9E7A2B796B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,11 +18,11 @@
     <sheet name="Lists" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="How to Use" sheetId="2" state="hidden" r:id="rId4"/>
     <sheet name="Students" sheetId="3" state="hidden" r:id="rId5"/>
-    <sheet name="Lesson Log" sheetId="9" r:id="rId6"/>
+    <sheet name="Lesson Log" sheetId="9" state="hidden" r:id="rId6"/>
     <sheet name="Progress" sheetId="7" r:id="rId7"/>
     <sheet name="Class Plan" sheetId="4" state="hidden" r:id="rId8"/>
-    <sheet name="Homework" sheetId="6" r:id="rId9"/>
-    <sheet name="Assessments" sheetId="8" r:id="rId10"/>
+    <sheet name="Homework" sheetId="6" state="hidden" r:id="rId9"/>
+    <sheet name="Assessments" sheetId="8" state="hidden" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="212">
   <si>
     <t>Madrasa Class Dashboard</t>
   </si>
@@ -673,6 +673,12 @@
   <si>
     <t>Very good read</t>
   </si>
+  <si>
+    <t>545-549</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
 </sst>
 </file>
 
@@ -1233,10 +1239,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.70000000000000007</c:v>
+                  <c:v>0.72500000000000009</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.66666666666666663</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.9</c:v>
@@ -1298,7 +1304,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -1526,7 +1532,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.70000000000000007</c:v>
+                  <c:v>0.72500000000000009</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2176,7 +2182,7 @@
       </c>
       <c r="F5" s="51">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],$B$4,ProgressTable[Mastery %]))</f>
-        <v>0.70000000000000007</v>
+        <v>0.72500000000000009</v>
       </c>
       <c r="G5" s="51" t="str">
         <f>IF(COUNTIFS(AssessmentTable[Student],$B$4,AssessmentTable[Percentage],"&lt;&gt;")=0,"",AVERAGEIF(AssessmentTable[Student],$B$4,AssessmentTable[Percentage]))</f>
@@ -2184,11 +2190,11 @@
       </c>
       <c r="H5" s="52">
         <f>COUNTIF(AttendanceTable[Student],$B$4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="52">
         <f>COUNTIF(ProgressTable[Student],$B$4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2344,7 +2350,7 @@
       </c>
       <c r="B13" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A13,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A13,ProgressTable[Mastery %]))</f>
-        <v>0.70000000000000007</v>
+        <v>0.72500000000000009</v>
       </c>
       <c r="C13" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A13)=0,"",(COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A13))</f>
@@ -2375,11 +2381,11 @@
       </c>
       <c r="B14" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A14,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A14,ProgressTable[Mastery %]))</f>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A14)=0,"",(COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A14))</f>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D14" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A14)=0,"",COUNTIFS(HomeworkTable[Student],A14,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A14))</f>
@@ -2508,7 +2514,7 @@
       </c>
       <c r="B20" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;")=0,"",SUMIFS(ProgressTable[Mastery %],ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20)/COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;"))</f>
-        <v>0.70000000000000007</v>
+        <v>0.72500000000000009</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="53" t="s">
@@ -2516,7 +2522,7 @@
       </c>
       <c r="E20" s="3">
         <f>COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],D20)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -10748,7 +10754,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="F5" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G5" s="25" t="s">
         <v>35</v>
@@ -10792,7 +10798,7 @@
         <v>0.45902777777777776</v>
       </c>
       <c r="F6" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>35</v>
@@ -10836,7 +10842,7 @@
         <v>0.4597222222222222</v>
       </c>
       <c r="F7" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>39</v>
@@ -10878,7 +10884,7 @@
         <v>0.47986111111111113</v>
       </c>
       <c r="F8" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="19"/>
@@ -10918,7 +10924,7 @@
         <v>0.47986111111111113</v>
       </c>
       <c r="F9" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="27"/>
@@ -10958,7 +10964,7 @@
         <v>0.47986111111111113</v>
       </c>
       <c r="F10" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="19"/>
@@ -10998,7 +11004,7 @@
         <v>0.52361111111111114</v>
       </c>
       <c r="F11" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G11" s="25"/>
       <c r="H11" s="27"/>
@@ -11038,7 +11044,7 @@
         <v>0.52361111111111114</v>
       </c>
       <c r="F12" s="17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="19"/>
@@ -11078,7 +11084,7 @@
         <v>0.52361111111111114</v>
       </c>
       <c r="F13" s="25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G13" s="25"/>
       <c r="H13" s="27"/>
@@ -11102,12 +11108,24 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="25" customHeight="1">
-      <c r="A14" s="29"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="17"/>
+      <c r="A14" s="29">
+        <v>46284</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="18">
+        <v>0.47708333333333336</v>
+      </c>
+      <c r="F14" s="17">
+        <v>4</v>
+      </c>
       <c r="G14" s="17"/>
       <c r="H14" s="19"/>
       <c r="I14" s="1"/>
@@ -11130,12 +11148,24 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="25" customHeight="1">
-      <c r="A15" s="28"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="25"/>
+      <c r="A15" s="28">
+        <v>46284</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="26">
+        <v>0</v>
+      </c>
+      <c r="F15" s="25">
+        <v>0</v>
+      </c>
       <c r="G15" s="25"/>
       <c r="H15" s="27"/>
       <c r="I15" s="1"/>
@@ -11158,12 +11188,24 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="25" customHeight="1">
-      <c r="A16" s="29"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="17"/>
+      <c r="A16" s="29">
+        <v>46284</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="18">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F16" s="17">
+        <v>4</v>
+      </c>
       <c r="G16" s="17"/>
       <c r="H16" s="19"/>
       <c r="I16" s="1"/>
@@ -26356,15 +26398,33 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="25" customHeight="1">
-      <c r="A14" s="29"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="19"/>
+      <c r="A14" s="29">
+        <v>46284</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="40">
+        <v>0.8</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>106</v>
+      </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -26384,15 +26444,33 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="25" customHeight="1">
-      <c r="A15" s="28"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="27"/>
+      <c r="A15" s="28">
+        <v>46284</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="25">
+        <v>424</v>
+      </c>
+      <c r="E15" s="42">
+        <v>0.9</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="25" t="s">
+        <v>206</v>
+      </c>
+      <c r="H15" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="I15" s="27" t="s">
+        <v>106</v>
+      </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -26412,14 +26490,30 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="25" customHeight="1">
-      <c r="A16" s="29"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
+      <c r="A16" s="29">
+        <v>46284</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="40">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>53</v>
+      </c>
       <c r="I16" s="19"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>

--- a/assets/deen/madrasa/class_manager.xlsx
+++ b/assets/deen/madrasa/class_manager.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SehhaDeveloper\src\l3\edu-journey\assets\deen\madrasa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A381B3C7-BC96-4B67-94AA-9E7A2B796B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C598B2-8693-4732-8E76-E0C1102BD7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="212">
   <si>
     <t>Madrasa Class Dashboard</t>
   </si>
@@ -1239,13 +1239,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.72500000000000009</c:v>
+                  <c:v>0.62000000000000011</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.9</c:v>
+                  <c:v>0.91999999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1304,7 +1304,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.75</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -1532,7 +1532,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.72500000000000009</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2141,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="50" t="s">
@@ -2174,7 +2174,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="51">
         <f>IF(COUNTIF(AttendanceTable[Student],$B$4)=0,"",(COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],$B$4))</f>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="51" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],$B$4)=0,"",COUNTIFS(HomeworkTable[Student],$B$4,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],$B$4))</f>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F5" s="51">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],$B$4,ProgressTable[Mastery %]))</f>
-        <v>0.72500000000000009</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="51" t="str">
         <f>IF(COUNTIFS(AssessmentTable[Student],$B$4,AssessmentTable[Percentage],"&lt;&gt;")=0,"",AVERAGEIF(AssessmentTable[Student],$B$4,AssessmentTable[Percentage]))</f>
@@ -2190,11 +2190,11 @@
       </c>
       <c r="H5" s="52">
         <f>COUNTIF(AttendanceTable[Student],$B$4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="52">
         <f>COUNTIF(ProgressTable[Student],$B$4)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B6" s="16" t="str">
         <f>B4</f>
-        <v>Mudhir</v>
+        <v>Nafisa</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B7" s="16">
         <f>IFERROR(VLOOKUP(B4,Students!$B$5:$D$50,2,FALSE),"")</f>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="63" t="s">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="B13" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A13,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A13,ProgressTable[Mastery %]))</f>
-        <v>0.72500000000000009</v>
+        <v>0.62000000000000011</v>
       </c>
       <c r="C13" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A13)=0,"",(COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A13))</f>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="C14" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A14)=0,"",(COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A14))</f>
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D14" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A14)=0,"",COUNTIFS(HomeworkTable[Student],A14,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A14))</f>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B15" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A15,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A15,ProgressTable[Mastery %]))</f>
-        <v>0.9</v>
+        <v>0.91999999999999993</v>
       </c>
       <c r="C15" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A15)=0,"",(COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A15))</f>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B20" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;")=0,"",SUMIFS(ProgressTable[Mastery %],ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20)/COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;"))</f>
-        <v>0.72500000000000009</v>
+        <v>0.5</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="53" t="s">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E22" s="3">
         <f>COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],D22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -11228,12 +11228,24 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="25" customHeight="1">
-      <c r="A17" s="28"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="26"/>
-      <c r="F17" s="25"/>
+      <c r="A17" s="28">
+        <v>46285</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="F17" s="25">
+        <v>4</v>
+      </c>
       <c r="G17" s="25"/>
       <c r="H17" s="27"/>
       <c r="I17" s="1"/>
@@ -11256,12 +11268,24 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="25" customHeight="1">
-      <c r="A18" s="29"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="17"/>
+      <c r="A18" s="29">
+        <v>46285</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="17">
+        <v>4</v>
+      </c>
       <c r="G18" s="17"/>
       <c r="H18" s="19"/>
       <c r="I18" s="1"/>
@@ -11284,12 +11308,24 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="25" customHeight="1">
-      <c r="A19" s="28"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="25"/>
+      <c r="A19" s="28">
+        <v>46285</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="26">
+        <v>0.5</v>
+      </c>
+      <c r="F19" s="25">
+        <v>4</v>
+      </c>
       <c r="G19" s="25"/>
       <c r="H19" s="27"/>
       <c r="I19" s="1"/>
@@ -26534,13 +26570,27 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="25" customHeight="1">
-      <c r="A17" s="28"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
+      <c r="A17" s="28">
+        <v>46285</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="25">
+        <v>542</v>
+      </c>
+      <c r="E17" s="42">
+        <v>0.2</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>59</v>
+      </c>
       <c r="H17" s="25"/>
       <c r="I17" s="27"/>
       <c r="J17" s="1"/>
@@ -26562,13 +26612,27 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="25" customHeight="1">
-      <c r="A18" s="29"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
+      <c r="A18" s="29">
+        <v>46285</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="17">
+        <v>450</v>
+      </c>
+      <c r="E18" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>59</v>
+      </c>
       <c r="H18" s="17"/>
       <c r="I18" s="19"/>
       <c r="J18" s="1"/>
@@ -26590,13 +26654,27 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="25" customHeight="1">
-      <c r="A19" s="28"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
+      <c r="A19" s="28">
+        <v>46285</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="25">
+        <v>425</v>
+      </c>
+      <c r="E19" s="42">
+        <v>1</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>104</v>
+      </c>
       <c r="H19" s="25"/>
       <c r="I19" s="27"/>
       <c r="J19" s="1"/>

--- a/assets/deen/madrasa/class_manager.xlsx
+++ b/assets/deen/madrasa/class_manager.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SehhaDeveloper\src\l3\edu-journey\assets\deen\madrasa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C598B2-8693-4732-8E76-E0C1102BD7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23762FD4-9A74-4314-BEC6-78D28EF31F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="215">
   <si>
     <t>Madrasa Class Dashboard</t>
   </si>
@@ -679,6 +679,15 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>Teacher not well</t>
+  </si>
+  <si>
+    <t>Murajah only</t>
+  </si>
+  <si>
+    <t>Murajaah only</t>
+  </si>
 </sst>
 </file>
 
@@ -864,7 +873,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1064,11 +1073,23 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1239,13 +1260,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.62000000000000011</c:v>
+                  <c:v>0.51428571428571435</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.5</c:v>
+                  <c:v>0.42857142857142855</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.91999999999999993</c:v>
+                  <c:v>0.79999999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1301,13 +1322,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.8571428571428571</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.8</c:v>
+                  <c:v>0.7142857142857143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0.8571428571428571</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1532,7 +1553,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.5</c:v>
+                  <c:v>0.51428571428571435</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1759,6 +1780,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="AttendanceTable" displayName="AttendanceTable" ref="A4:H104" totalsRowShown="0">
+  <autoFilter ref="A4:H104" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Student"/>
@@ -1808,7 +1830,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ProgressTable" displayName="ProgressTable" ref="A4:I204" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ProgressTable" displayName="ProgressTable" ref="A4:I204" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A4:I204" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Student"/>
@@ -2075,16 +2098,16 @@
     <tabColor rgb="FF356BA2"/>
   </sheetPr>
   <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="16.1875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:14" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
@@ -2120,7 +2143,7 @@
       <c r="M2" s="61"/>
       <c r="N2" s="62"/>
     </row>
-    <row r="3" spans="1:14" ht="25" customHeight="1">
+    <row r="3" spans="1:14" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2136,12 +2159,12 @@
       <c r="M3" s="3"/>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="24.6">
+    <row r="4" spans="1:14" ht="25.5">
       <c r="A4" s="48" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="50" t="s">
@@ -2168,13 +2191,13 @@
       <c r="M4" s="46"/>
       <c r="N4" s="47"/>
     </row>
-    <row r="5" spans="1:14" ht="25.2">
+    <row r="5" spans="1:14" ht="26.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="51">
         <f>IF(COUNTIF(AttendanceTable[Student],$B$4)=0,"",(COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],$B$4))</f>
-        <v>0.8</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="E5" s="51" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],$B$4)=0,"",COUNTIFS(HomeworkTable[Student],$B$4,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],$B$4))</f>
@@ -2182,7 +2205,7 @@
       </c>
       <c r="F5" s="51">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],$B$4,ProgressTable[Mastery %]))</f>
-        <v>0.5</v>
+        <v>0.51428571428571435</v>
       </c>
       <c r="G5" s="51" t="str">
         <f>IF(COUNTIFS(AssessmentTable[Student],$B$4,AssessmentTable[Percentage],"&lt;&gt;")=0,"",AVERAGEIF(AssessmentTable[Student],$B$4,AssessmentTable[Percentage]))</f>
@@ -2190,11 +2213,11 @@
       </c>
       <c r="H5" s="52">
         <f>COUNTIF(AttendanceTable[Student],$B$4)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I5" s="52">
         <f>COUNTIF(ProgressTable[Student],$B$4)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2202,13 +2225,13 @@
       <c r="M5" s="3"/>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" ht="14.1">
+    <row r="6" spans="1:14" ht="15">
       <c r="A6" s="15" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="16" t="str">
         <f>B4</f>
-        <v>Nafisa</v>
+        <v>Mudhir</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -2223,13 +2246,13 @@
       <c r="M6" s="3"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="14.1">
+    <row r="7" spans="1:14" ht="15">
       <c r="A7" s="15" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="16">
         <f>IFERROR(VLOOKUP(B4,Students!$B$5:$D$50,2,FALSE),"")</f>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="63" t="s">
@@ -2246,7 +2269,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="14.1">
+    <row r="8" spans="1:14" ht="15">
       <c r="A8" s="15" t="s">
         <v>10</v>
       </c>
@@ -2267,7 +2290,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" ht="25" customHeight="1">
+    <row r="9" spans="1:14" ht="24.95" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2283,7 +2306,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="25" customHeight="1">
+    <row r="10" spans="1:14" ht="24.95" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2299,7 +2322,7 @@
       <c r="M10" s="3"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="25" customHeight="1">
+    <row r="11" spans="1:14" ht="24.95" customHeight="1">
       <c r="A11" s="64" t="s">
         <v>199</v>
       </c>
@@ -2317,7 +2340,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="14.1">
+    <row r="12" spans="1:14" ht="15">
       <c r="A12" s="23" t="s">
         <v>8</v>
       </c>
@@ -2350,11 +2373,11 @@
       </c>
       <c r="B13" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A13,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A13,ProgressTable[Mastery %]))</f>
-        <v>0.62000000000000011</v>
+        <v>0.51428571428571435</v>
       </c>
       <c r="C13" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A13)=0,"",(COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A13))</f>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D13" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A13)=0,"",COUNTIFS(HomeworkTable[Student],A13,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A13))</f>
@@ -2381,11 +2404,11 @@
       </c>
       <c r="B14" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A14,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A14,ProgressTable[Mastery %]))</f>
-        <v>0.5</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="C14" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A14)=0,"",(COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A14))</f>
-        <v>0.8</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="D14" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A14)=0,"",COUNTIFS(HomeworkTable[Student],A14,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A14))</f>
@@ -2412,11 +2435,11 @@
       </c>
       <c r="B15" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A15,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A15,ProgressTable[Mastery %]))</f>
-        <v>0.91999999999999993</v>
+        <v>0.79999999999999993</v>
       </c>
       <c r="C15" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A15)=0,"",(COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A15))</f>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="D15" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A15)=0,"",COUNTIFS(HomeworkTable[Student],A15,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A15))</f>
@@ -2436,7 +2459,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="25" customHeight="1">
+    <row r="16" spans="1:14" ht="24.95" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2452,7 +2475,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="25" customHeight="1">
+    <row r="17" spans="1:14" ht="24.95" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2468,7 +2491,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="25" customHeight="1">
+    <row r="18" spans="1:14" ht="24.95" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2484,7 +2507,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="1:14" ht="14.1">
+    <row r="19" spans="1:14" ht="15">
       <c r="A19" s="23" t="s">
         <v>200</v>
       </c>
@@ -2514,7 +2537,7 @@
       </c>
       <c r="B20" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;")=0,"",SUMIFS(ProgressTable[Mastery %],ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20)/COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;"))</f>
-        <v>0.5</v>
+        <v>0.51428571428571435</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="53" t="s">
@@ -2522,7 +2545,7 @@
       </c>
       <c r="E20" s="3">
         <f>COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],D20)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2574,7 +2597,7 @@
       </c>
       <c r="E22" s="3">
         <f>COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],D22)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -2600,7 +2623,7 @@
       </c>
       <c r="E23" s="3">
         <f>COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],D23)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -2767,7 +2790,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="1:14" ht="25" customHeight="1">
+    <row r="32" spans="1:14" ht="24.95" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2783,7 +2806,7 @@
       <c r="M32" s="3"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="1:14" ht="25" customHeight="1">
+    <row r="33" spans="1:14" ht="24.95" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2799,7 +2822,7 @@
       <c r="M33" s="3"/>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="1:14" ht="25" customHeight="1">
+    <row r="34" spans="1:14" ht="24.95" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2815,7 +2838,7 @@
       <c r="M34" s="3"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="1:14" ht="25" customHeight="1">
+    <row r="35" spans="1:14" ht="24.95" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2831,7 +2854,7 @@
       <c r="M35" s="3"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:14" ht="25" customHeight="1">
+    <row r="36" spans="1:14" ht="24.95" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2847,7 +2870,7 @@
       <c r="M36" s="3"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="1:14" ht="25" customHeight="1">
+    <row r="37" spans="1:14" ht="24.95" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2863,7 +2886,7 @@
       <c r="M37" s="3"/>
       <c r="N37" s="4"/>
     </row>
-    <row r="38" spans="1:14" ht="25" customHeight="1">
+    <row r="38" spans="1:14" ht="24.95" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2879,7 +2902,7 @@
       <c r="M38" s="3"/>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="1:14" ht="25" customHeight="1">
+    <row r="39" spans="1:14" ht="24.95" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2895,7 +2918,7 @@
       <c r="M39" s="3"/>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="1:14" ht="25" customHeight="1">
+    <row r="40" spans="1:14" ht="24.95" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2911,7 +2934,7 @@
       <c r="M40" s="3"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="1:14" ht="25" customHeight="1">
+    <row r="41" spans="1:14" ht="24.95" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2927,7 +2950,7 @@
       <c r="M41" s="3"/>
       <c r="N41" s="4"/>
     </row>
-    <row r="42" spans="1:14" ht="25" customHeight="1">
+    <row r="42" spans="1:14" ht="24.95" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2943,7 +2966,7 @@
       <c r="M42" s="3"/>
       <c r="N42" s="4"/>
     </row>
-    <row r="43" spans="1:14" ht="25" customHeight="1">
+    <row r="43" spans="1:14" ht="24.95" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2959,7 +2982,7 @@
       <c r="M43" s="3"/>
       <c r="N43" s="4"/>
     </row>
-    <row r="44" spans="1:14" ht="25" customHeight="1">
+    <row r="44" spans="1:14" ht="24.95" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2975,7 +2998,7 @@
       <c r="M44" s="3"/>
       <c r="N44" s="4"/>
     </row>
-    <row r="45" spans="1:14" ht="25" customHeight="1">
+    <row r="45" spans="1:14" ht="24.95" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -3000,7 +3023,7 @@
     <mergeCell ref="A30:E31"/>
   </mergeCells>
   <conditionalFormatting sqref="A13:E15">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$A13=$B$4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3027,13 +3050,13 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:26" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>184</v>
       </c>
@@ -3059,7 +3082,7 @@
       <c r="H2" s="61"/>
       <c r="I2" s="62"/>
     </row>
-    <row r="3" spans="1:26" ht="25" customHeight="1">
+    <row r="3" spans="1:26" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3070,7 +3093,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="14.1">
+    <row r="4" spans="1:26" ht="15">
       <c r="A4" s="23" t="s">
         <v>26</v>
       </c>
@@ -3116,7 +3139,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="44.05" customHeight="1">
+    <row r="5" spans="1:26" ht="44.1" customHeight="1">
       <c r="A5" s="28"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -3150,7 +3173,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="44.05" customHeight="1">
+    <row r="6" spans="1:26" ht="44.1" customHeight="1">
       <c r="A6" s="29"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -3184,7 +3207,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="44.05" customHeight="1">
+    <row r="7" spans="1:26" ht="44.1" customHeight="1">
       <c r="A7" s="28"/>
       <c r="B7" s="25"/>
       <c r="C7" s="25"/>
@@ -3218,7 +3241,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="25" customHeight="1">
+    <row r="8" spans="1:26" ht="24.95" customHeight="1">
       <c r="A8" s="29"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -3252,7 +3275,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="25" customHeight="1">
+    <row r="9" spans="1:26" ht="24.95" customHeight="1">
       <c r="A9" s="28"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -3286,7 +3309,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="25" customHeight="1">
+    <row r="10" spans="1:26" ht="24.95" customHeight="1">
       <c r="A10" s="29"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -3320,7 +3343,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="25" customHeight="1">
+    <row r="11" spans="1:26" ht="24.95" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -3354,7 +3377,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="25" customHeight="1">
+    <row r="12" spans="1:26" ht="24.95" customHeight="1">
       <c r="A12" s="29"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -3388,7 +3411,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="25" customHeight="1">
+    <row r="13" spans="1:26" ht="24.95" customHeight="1">
       <c r="A13" s="28"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -3422,7 +3445,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="25" customHeight="1">
+    <row r="14" spans="1:26" ht="24.95" customHeight="1">
       <c r="A14" s="29"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -3456,7 +3479,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="25" customHeight="1">
+    <row r="15" spans="1:26" ht="24.95" customHeight="1">
       <c r="A15" s="28"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -3490,7 +3513,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="25" customHeight="1">
+    <row r="16" spans="1:26" ht="24.95" customHeight="1">
       <c r="A16" s="29"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -3524,7 +3547,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="25" customHeight="1">
+    <row r="17" spans="1:26" ht="24.95" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -3558,7 +3581,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="25" customHeight="1">
+    <row r="18" spans="1:26" ht="24.95" customHeight="1">
       <c r="A18" s="29"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -3592,7 +3615,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="25" customHeight="1">
+    <row r="19" spans="1:26" ht="24.95" customHeight="1">
       <c r="A19" s="28"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -3626,7 +3649,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="25" customHeight="1">
+    <row r="20" spans="1:26" ht="24.95" customHeight="1">
       <c r="A20" s="29"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -3660,7 +3683,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="25" customHeight="1">
+    <row r="21" spans="1:26" ht="24.95" customHeight="1">
       <c r="A21" s="28"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -3694,7 +3717,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="25" customHeight="1">
+    <row r="22" spans="1:26" ht="24.95" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -3728,7 +3751,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="25" customHeight="1">
+    <row r="23" spans="1:26" ht="24.95" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -3762,7 +3785,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="25" customHeight="1">
+    <row r="24" spans="1:26" ht="24.95" customHeight="1">
       <c r="A24" s="29"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -3796,7 +3819,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="25" customHeight="1">
+    <row r="25" spans="1:26" ht="24.95" customHeight="1">
       <c r="A25" s="28"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -3830,7 +3853,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="25" customHeight="1">
+    <row r="26" spans="1:26" ht="24.95" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -3864,7 +3887,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="25" customHeight="1">
+    <row r="27" spans="1:26" ht="24.95" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -3898,7 +3921,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="25" customHeight="1">
+    <row r="28" spans="1:26" ht="24.95" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -3932,7 +3955,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="25" customHeight="1">
+    <row r="29" spans="1:26" ht="24.95" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -3966,7 +3989,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="25" customHeight="1">
+    <row r="30" spans="1:26" ht="24.95" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -4000,7 +4023,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="25" customHeight="1">
+    <row r="31" spans="1:26" ht="24.95" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -4034,7 +4057,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="25" customHeight="1">
+    <row r="32" spans="1:26" ht="24.95" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -4068,7 +4091,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="25" customHeight="1">
+    <row r="33" spans="1:26" ht="24.95" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -4102,7 +4125,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="25" customHeight="1">
+    <row r="34" spans="1:26" ht="24.95" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -4136,7 +4159,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="25" customHeight="1">
+    <row r="35" spans="1:26" ht="24.95" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -4170,7 +4193,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="25" customHeight="1">
+    <row r="36" spans="1:26" ht="24.95" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -4204,7 +4227,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="25" customHeight="1">
+    <row r="37" spans="1:26" ht="24.95" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -4238,7 +4261,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="25" customHeight="1">
+    <row r="38" spans="1:26" ht="24.95" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -4272,7 +4295,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="25" customHeight="1">
+    <row r="39" spans="1:26" ht="24.95" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -4306,7 +4329,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="25" customHeight="1">
+    <row r="40" spans="1:26" ht="24.95" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -4340,7 +4363,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="25" customHeight="1">
+    <row r="41" spans="1:26" ht="24.95" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -4374,7 +4397,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="25" customHeight="1">
+    <row r="42" spans="1:26" ht="24.95" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -4408,7 +4431,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="25" customHeight="1">
+    <row r="43" spans="1:26" ht="24.95" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -4442,7 +4465,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="25" customHeight="1">
+    <row r="44" spans="1:26" ht="24.95" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -4476,7 +4499,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="25" customHeight="1">
+    <row r="45" spans="1:26" ht="24.95" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -4510,7 +4533,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="25" customHeight="1">
+    <row r="46" spans="1:26" ht="24.95" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -4544,7 +4567,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="25" customHeight="1">
+    <row r="47" spans="1:26" ht="24.95" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -4578,7 +4601,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="25" customHeight="1">
+    <row r="48" spans="1:26" ht="24.95" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -4612,7 +4635,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="25" customHeight="1">
+    <row r="49" spans="1:26" ht="24.95" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -4646,7 +4669,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="25" customHeight="1">
+    <row r="50" spans="1:26" ht="24.95" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -4680,7 +4703,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="25" customHeight="1">
+    <row r="51" spans="1:26" ht="24.95" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -4714,7 +4737,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="25" customHeight="1">
+    <row r="52" spans="1:26" ht="24.95" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -4748,7 +4771,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="25" customHeight="1">
+    <row r="53" spans="1:26" ht="24.95" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -4782,7 +4805,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="25" customHeight="1">
+    <row r="54" spans="1:26" ht="24.95" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -4816,7 +4839,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="25" customHeight="1">
+    <row r="55" spans="1:26" ht="24.95" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -4850,7 +4873,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="25" customHeight="1">
+    <row r="56" spans="1:26" ht="24.95" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -4884,7 +4907,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="25" customHeight="1">
+    <row r="57" spans="1:26" ht="24.95" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -4918,7 +4941,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="25" customHeight="1">
+    <row r="58" spans="1:26" ht="24.95" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -4952,7 +4975,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="25" customHeight="1">
+    <row r="59" spans="1:26" ht="24.95" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -4986,7 +5009,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="25" customHeight="1">
+    <row r="60" spans="1:26" ht="24.95" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -5020,7 +5043,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="25" customHeight="1">
+    <row r="61" spans="1:26" ht="24.95" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -5054,7 +5077,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="25" customHeight="1">
+    <row r="62" spans="1:26" ht="24.95" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -5088,7 +5111,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="25" customHeight="1">
+    <row r="63" spans="1:26" ht="24.95" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -5122,7 +5145,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="25" customHeight="1">
+    <row r="64" spans="1:26" ht="24.95" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -5156,7 +5179,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="25" customHeight="1">
+    <row r="65" spans="1:26" ht="24.95" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -5190,7 +5213,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="25" customHeight="1">
+    <row r="66" spans="1:26" ht="24.95" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -5224,7 +5247,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="25" customHeight="1">
+    <row r="67" spans="1:26" ht="24.95" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -5258,7 +5281,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="25" customHeight="1">
+    <row r="68" spans="1:26" ht="24.95" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -5292,7 +5315,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="25" customHeight="1">
+    <row r="69" spans="1:26" ht="24.95" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -5326,7 +5349,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="25" customHeight="1">
+    <row r="70" spans="1:26" ht="24.95" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -5360,7 +5383,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="25" customHeight="1">
+    <row r="71" spans="1:26" ht="24.95" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -5394,7 +5417,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="25" customHeight="1">
+    <row r="72" spans="1:26" ht="24.95" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -5428,7 +5451,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="25" customHeight="1">
+    <row r="73" spans="1:26" ht="24.95" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -5462,7 +5485,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="25" customHeight="1">
+    <row r="74" spans="1:26" ht="24.95" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -5496,7 +5519,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="25" customHeight="1">
+    <row r="75" spans="1:26" ht="24.95" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -5530,7 +5553,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="25" customHeight="1">
+    <row r="76" spans="1:26" ht="24.95" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -5564,7 +5587,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="25" customHeight="1">
+    <row r="77" spans="1:26" ht="24.95" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -5598,7 +5621,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="25" customHeight="1">
+    <row r="78" spans="1:26" ht="24.95" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -5632,7 +5655,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="25" customHeight="1">
+    <row r="79" spans="1:26" ht="24.95" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -5666,7 +5689,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="25" customHeight="1">
+    <row r="80" spans="1:26" ht="24.95" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -5700,7 +5723,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="25" customHeight="1">
+    <row r="81" spans="1:26" ht="24.95" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -5734,7 +5757,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="25" customHeight="1">
+    <row r="82" spans="1:26" ht="24.95" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -5768,7 +5791,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="25" customHeight="1">
+    <row r="83" spans="1:26" ht="24.95" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -5802,7 +5825,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="25" customHeight="1">
+    <row r="84" spans="1:26" ht="24.95" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -5836,7 +5859,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="25" customHeight="1">
+    <row r="85" spans="1:26" ht="24.95" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -5870,7 +5893,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="25" customHeight="1">
+    <row r="86" spans="1:26" ht="24.95" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -5904,7 +5927,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="25" customHeight="1">
+    <row r="87" spans="1:26" ht="24.95" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -5938,7 +5961,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="25" customHeight="1">
+    <row r="88" spans="1:26" ht="24.95" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -5972,7 +5995,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="25" customHeight="1">
+    <row r="89" spans="1:26" ht="24.95" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -6006,7 +6029,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="25" customHeight="1">
+    <row r="90" spans="1:26" ht="24.95" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -6040,7 +6063,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="25" customHeight="1">
+    <row r="91" spans="1:26" ht="24.95" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -6074,7 +6097,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="25" customHeight="1">
+    <row r="92" spans="1:26" ht="24.95" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -6108,7 +6131,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="25" customHeight="1">
+    <row r="93" spans="1:26" ht="24.95" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -6142,7 +6165,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="25" customHeight="1">
+    <row r="94" spans="1:26" ht="24.95" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -6176,7 +6199,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="25" customHeight="1">
+    <row r="95" spans="1:26" ht="24.95" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -6210,7 +6233,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="25" customHeight="1">
+    <row r="96" spans="1:26" ht="24.95" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -6244,7 +6267,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="25" customHeight="1">
+    <row r="97" spans="1:26" ht="24.95" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -6278,7 +6301,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="25" customHeight="1">
+    <row r="98" spans="1:26" ht="24.95" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -6312,7 +6335,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="25" customHeight="1">
+    <row r="99" spans="1:26" ht="24.95" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -6346,7 +6369,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="25" customHeight="1">
+    <row r="100" spans="1:26" ht="24.95" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -6380,7 +6403,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="25" customHeight="1">
+    <row r="101" spans="1:26" ht="24.95" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -6414,7 +6437,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="25" customHeight="1">
+    <row r="102" spans="1:26" ht="24.95" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -6448,7 +6471,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="25" customHeight="1">
+    <row r="103" spans="1:26" ht="24.95" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -6482,7 +6505,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="25" customHeight="1">
+    <row r="104" spans="1:26" ht="24.95" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -10652,14 +10675,19 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:26" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>24</v>
       </c>
@@ -10683,7 +10711,7 @@
       <c r="G2" s="61"/>
       <c r="H2" s="62"/>
     </row>
-    <row r="3" spans="1:26" ht="25" customHeight="1">
+    <row r="3" spans="1:26" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -10693,7 +10721,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="14.1">
+    <row r="4" spans="1:26" ht="15">
       <c r="A4" s="23" t="s">
         <v>26</v>
       </c>
@@ -10987,7 +11015,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="25" customHeight="1">
+    <row r="11" spans="1:26" ht="24.95" customHeight="1">
       <c r="A11" s="29">
         <v>46278</v>
       </c>
@@ -11027,7 +11055,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="25" customHeight="1">
+    <row r="12" spans="1:26" ht="24.95" customHeight="1">
       <c r="A12" s="29">
         <v>46278</v>
       </c>
@@ -11067,7 +11095,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="25" customHeight="1">
+    <row r="13" spans="1:26" ht="24.95" customHeight="1">
       <c r="A13" s="29">
         <v>46278</v>
       </c>
@@ -11107,7 +11135,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="25" customHeight="1">
+    <row r="14" spans="1:26" ht="24.95" customHeight="1">
       <c r="A14" s="29">
         <v>46284</v>
       </c>
@@ -11147,7 +11175,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="25" customHeight="1">
+    <row r="15" spans="1:26" ht="24.95" customHeight="1">
       <c r="A15" s="28">
         <v>46284</v>
       </c>
@@ -11187,7 +11215,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="25" customHeight="1">
+    <row r="16" spans="1:26" ht="24.95" customHeight="1">
       <c r="A16" s="29">
         <v>46284</v>
       </c>
@@ -11227,7 +11255,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="25" customHeight="1">
+    <row r="17" spans="1:26" ht="24.95" customHeight="1">
       <c r="A17" s="28">
         <v>46285</v>
       </c>
@@ -11267,7 +11295,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="25" customHeight="1">
+    <row r="18" spans="1:26" ht="24.95" customHeight="1">
       <c r="A18" s="29">
         <v>46285</v>
       </c>
@@ -11307,7 +11335,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="25" customHeight="1">
+    <row r="19" spans="1:26" ht="24.95" customHeight="1">
       <c r="A19" s="28">
         <v>46285</v>
       </c>
@@ -11347,14 +11375,24 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="25" customHeight="1">
-      <c r="A20" s="29"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
+    <row r="20" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A20" s="29">
+        <v>46291</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>57</v>
+      </c>
       <c r="E20" s="18"/>
       <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="G20" s="17" t="s">
+        <v>212</v>
+      </c>
       <c r="H20" s="19"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -11375,14 +11413,24 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="25" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
+    <row r="21" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A21" s="28">
+        <v>46291</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>57</v>
+      </c>
       <c r="E21" s="26"/>
       <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
+      <c r="G21" s="25" t="s">
+        <v>212</v>
+      </c>
       <c r="H21" s="27"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -11403,14 +11451,24 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="25" customHeight="1">
-      <c r="A22" s="29"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
+    <row r="22" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A22" s="29">
+        <v>46291</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>57</v>
+      </c>
       <c r="E22" s="18"/>
       <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+      <c r="G22" s="17" t="s">
+        <v>212</v>
+      </c>
       <c r="H22" s="19"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -11431,14 +11489,26 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="25" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="26"/>
+    <row r="23" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A23" s="28">
+        <v>46292</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="26">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
+      <c r="G23" s="25" t="s">
+        <v>213</v>
+      </c>
       <c r="H23" s="27"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -11459,14 +11529,26 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="25" customHeight="1">
-      <c r="A24" s="29"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="18"/>
+    <row r="24" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A24" s="29">
+        <v>46292</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="18">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
+      <c r="G24" s="17" t="s">
+        <v>214</v>
+      </c>
       <c r="H24" s="19"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -11487,14 +11569,26 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="25" customHeight="1">
-      <c r="A25" s="28"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="26"/>
+    <row r="25" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A25" s="28">
+        <v>46292</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="26">
+        <v>0.52083333333333337</v>
+      </c>
       <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
+      <c r="G25" s="25" t="s">
+        <v>214</v>
+      </c>
       <c r="H25" s="27"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -11515,7 +11609,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="25" customHeight="1">
+    <row r="26" spans="1:26" ht="24.95" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -11543,7 +11637,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="25" customHeight="1">
+    <row r="27" spans="1:26" ht="24.95" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -11571,7 +11665,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="25" customHeight="1">
+    <row r="28" spans="1:26" ht="24.95" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -11599,7 +11693,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="25" customHeight="1">
+    <row r="29" spans="1:26" ht="24.95" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -11627,7 +11721,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="25" customHeight="1">
+    <row r="30" spans="1:26" ht="24.95" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -11655,7 +11749,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="25" customHeight="1">
+    <row r="31" spans="1:26" ht="24.95" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -11683,7 +11777,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="25" customHeight="1">
+    <row r="32" spans="1:26" ht="24.95" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -11711,7 +11805,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="25" customHeight="1">
+    <row r="33" spans="1:26" ht="24.95" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -11739,7 +11833,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="25" customHeight="1">
+    <row r="34" spans="1:26" ht="24.95" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -11767,7 +11861,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="25" customHeight="1">
+    <row r="35" spans="1:26" ht="24.95" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -11795,7 +11889,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="25" customHeight="1">
+    <row r="36" spans="1:26" ht="24.95" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -11823,7 +11917,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="25" customHeight="1">
+    <row r="37" spans="1:26" ht="24.95" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -11851,7 +11945,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="25" customHeight="1">
+    <row r="38" spans="1:26" ht="24.95" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -11879,7 +11973,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="25" customHeight="1">
+    <row r="39" spans="1:26" ht="24.95" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -11907,7 +12001,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="25" customHeight="1">
+    <row r="40" spans="1:26" ht="24.95" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -11935,7 +12029,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="25" customHeight="1">
+    <row r="41" spans="1:26" ht="24.95" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -11963,7 +12057,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="25" customHeight="1">
+    <row r="42" spans="1:26" ht="24.95" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -11991,7 +12085,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="25" customHeight="1">
+    <row r="43" spans="1:26" ht="24.95" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -12019,7 +12113,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="25" customHeight="1">
+    <row r="44" spans="1:26" ht="24.95" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -12047,7 +12141,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="25" customHeight="1">
+    <row r="45" spans="1:26" ht="24.95" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -12075,7 +12169,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="25" customHeight="1">
+    <row r="46" spans="1:26" ht="24.95" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -12103,7 +12197,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="25" customHeight="1">
+    <row r="47" spans="1:26" ht="24.95" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -12131,7 +12225,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="25" customHeight="1">
+    <row r="48" spans="1:26" ht="24.95" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -12159,7 +12253,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="25" customHeight="1">
+    <row r="49" spans="1:26" ht="24.95" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -12187,7 +12281,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="25" customHeight="1">
+    <row r="50" spans="1:26" ht="24.95" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -12215,7 +12309,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="25" customHeight="1">
+    <row r="51" spans="1:26" ht="24.95" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -12243,7 +12337,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="25" customHeight="1">
+    <row r="52" spans="1:26" ht="24.95" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -12271,7 +12365,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="25" customHeight="1">
+    <row r="53" spans="1:26" ht="24.95" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -12299,7 +12393,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="25" customHeight="1">
+    <row r="54" spans="1:26" ht="24.95" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -12327,7 +12421,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="25" customHeight="1">
+    <row r="55" spans="1:26" ht="24.95" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -12355,7 +12449,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="25" customHeight="1">
+    <row r="56" spans="1:26" ht="24.95" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -12383,7 +12477,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="25" customHeight="1">
+    <row r="57" spans="1:26" ht="24.95" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -12411,7 +12505,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="25" customHeight="1">
+    <row r="58" spans="1:26" ht="24.95" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -12439,7 +12533,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="25" customHeight="1">
+    <row r="59" spans="1:26" ht="24.95" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -12467,7 +12561,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="25" customHeight="1">
+    <row r="60" spans="1:26" ht="24.95" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -12495,7 +12589,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="25" customHeight="1">
+    <row r="61" spans="1:26" ht="24.95" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -12523,7 +12617,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="25" customHeight="1">
+    <row r="62" spans="1:26" ht="24.95" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -12551,7 +12645,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="25" customHeight="1">
+    <row r="63" spans="1:26" ht="24.95" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -12579,7 +12673,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="25" customHeight="1">
+    <row r="64" spans="1:26" ht="24.95" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -12607,7 +12701,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="25" customHeight="1">
+    <row r="65" spans="1:26" ht="24.95" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -12635,7 +12729,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="25" customHeight="1">
+    <row r="66" spans="1:26" ht="24.95" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -12663,7 +12757,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="25" customHeight="1">
+    <row r="67" spans="1:26" ht="24.95" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -12691,7 +12785,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="25" customHeight="1">
+    <row r="68" spans="1:26" ht="24.95" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -12719,7 +12813,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="25" customHeight="1">
+    <row r="69" spans="1:26" ht="24.95" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -12747,7 +12841,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="25" customHeight="1">
+    <row r="70" spans="1:26" ht="24.95" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -12775,7 +12869,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="25" customHeight="1">
+    <row r="71" spans="1:26" ht="24.95" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -12803,7 +12897,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="25" customHeight="1">
+    <row r="72" spans="1:26" ht="24.95" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -12831,7 +12925,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="25" customHeight="1">
+    <row r="73" spans="1:26" ht="24.95" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -12859,7 +12953,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="25" customHeight="1">
+    <row r="74" spans="1:26" ht="24.95" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -12887,7 +12981,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="25" customHeight="1">
+    <row r="75" spans="1:26" ht="24.95" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -12915,7 +13009,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="25" customHeight="1">
+    <row r="76" spans="1:26" ht="24.95" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -12943,7 +13037,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="25" customHeight="1">
+    <row r="77" spans="1:26" ht="24.95" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -12971,7 +13065,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="25" customHeight="1">
+    <row r="78" spans="1:26" ht="24.95" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -12999,7 +13093,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="25" customHeight="1">
+    <row r="79" spans="1:26" ht="24.95" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -13027,7 +13121,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="25" customHeight="1">
+    <row r="80" spans="1:26" ht="24.95" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -13055,7 +13149,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="25" customHeight="1">
+    <row r="81" spans="1:26" ht="24.95" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -13083,7 +13177,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="25" customHeight="1">
+    <row r="82" spans="1:26" ht="24.95" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -13111,7 +13205,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="25" customHeight="1">
+    <row r="83" spans="1:26" ht="24.95" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -13139,7 +13233,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="25" customHeight="1">
+    <row r="84" spans="1:26" ht="24.95" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -13167,7 +13261,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="25" customHeight="1">
+    <row r="85" spans="1:26" ht="24.95" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -13195,7 +13289,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="25" customHeight="1">
+    <row r="86" spans="1:26" ht="24.95" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -13223,7 +13317,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="25" customHeight="1">
+    <row r="87" spans="1:26" ht="24.95" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -13251,7 +13345,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="25" customHeight="1">
+    <row r="88" spans="1:26" ht="24.95" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -13279,7 +13373,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="25" customHeight="1">
+    <row r="89" spans="1:26" ht="24.95" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -13307,7 +13401,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="25" customHeight="1">
+    <row r="90" spans="1:26" ht="24.95" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -13335,7 +13429,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="25" customHeight="1">
+    <row r="91" spans="1:26" ht="24.95" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -13363,7 +13457,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="25" customHeight="1">
+    <row r="92" spans="1:26" ht="24.95" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -13391,7 +13485,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="25" customHeight="1">
+    <row r="93" spans="1:26" ht="24.95" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -13419,7 +13513,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="25" customHeight="1">
+    <row r="94" spans="1:26" ht="24.95" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -13447,7 +13541,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="25" customHeight="1">
+    <row r="95" spans="1:26" ht="24.95" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -13475,7 +13569,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="25" customHeight="1">
+    <row r="96" spans="1:26" ht="24.95" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -13503,7 +13597,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="25" customHeight="1">
+    <row r="97" spans="1:26" ht="24.95" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -13531,7 +13625,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="25" customHeight="1">
+    <row r="98" spans="1:26" ht="24.95" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -13559,7 +13653,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="25" customHeight="1">
+    <row r="99" spans="1:26" ht="24.95" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -13587,7 +13681,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="25" customHeight="1">
+    <row r="100" spans="1:26" ht="24.95" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -13615,7 +13709,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="25" customHeight="1">
+    <row r="101" spans="1:26" ht="24.95" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -13643,7 +13737,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="25" customHeight="1">
+    <row r="102" spans="1:26" ht="24.95" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -13671,7 +13765,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="25" customHeight="1">
+    <row r="103" spans="1:26" ht="24.95" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -13699,7 +13793,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="25" customHeight="1">
+    <row r="104" spans="1:26" ht="24.95" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -17821,13 +17915,13 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D104">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>D5="Present"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>D5="Late"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="9" priority="3">
       <formula>D5="Absent"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17916,14 +18010,14 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:6" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>40</v>
       </c>
@@ -17943,7 +18037,7 @@
       <c r="E2" s="61"/>
       <c r="F2" s="62"/>
     </row>
-    <row r="3" spans="1:6" ht="25" customHeight="1">
+    <row r="3" spans="1:6" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -17951,7 +18045,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="4"/>
     </row>
-    <row r="4" spans="1:6" ht="38.049999999999997" customHeight="1">
+    <row r="4" spans="1:6" ht="38.1" customHeight="1">
       <c r="A4" s="23" t="s">
         <v>42</v>
       </c>
@@ -17971,7 +18065,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="25" customHeight="1">
+    <row r="5" spans="1:6" ht="24.95" customHeight="1">
       <c r="A5" s="33" t="s">
         <v>32</v>
       </c>
@@ -17991,7 +18085,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="25" customHeight="1">
+    <row r="6" spans="1:6" ht="24.95" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>37</v>
       </c>
@@ -18011,7 +18105,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="25" customHeight="1">
+    <row r="7" spans="1:6" ht="24.95" customHeight="1">
       <c r="A7" s="33" t="s">
         <v>38</v>
       </c>
@@ -18031,7 +18125,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="25" customHeight="1">
+    <row r="8" spans="1:6" ht="24.95" customHeight="1">
       <c r="A8" s="31"/>
       <c r="B8" s="17" t="s">
         <v>57</v>
@@ -18049,7 +18143,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="25" customHeight="1">
+    <row r="9" spans="1:6" ht="24.95" customHeight="1">
       <c r="A9" s="33"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -18061,7 +18155,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="25" customHeight="1">
+    <row r="10" spans="1:6" ht="24.95" customHeight="1">
       <c r="A10" s="31"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -18071,7 +18165,7 @@
       <c r="E10" s="17"/>
       <c r="F10" s="19"/>
     </row>
-    <row r="11" spans="1:6" ht="25" customHeight="1">
+    <row r="11" spans="1:6" ht="24.95" customHeight="1">
       <c r="A11" s="33"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -18081,7 +18175,7 @@
       <c r="E11" s="25"/>
       <c r="F11" s="27"/>
     </row>
-    <row r="12" spans="1:6" ht="25" customHeight="1">
+    <row r="12" spans="1:6" ht="24.95" customHeight="1">
       <c r="A12" s="31"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -18091,7 +18185,7 @@
       <c r="E12" s="17"/>
       <c r="F12" s="19"/>
     </row>
-    <row r="13" spans="1:6" ht="25" customHeight="1">
+    <row r="13" spans="1:6" ht="24.95" customHeight="1">
       <c r="A13" s="34"/>
       <c r="B13" s="35"/>
       <c r="C13" s="35"/>
@@ -18116,7 +18210,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
@@ -18124,7 +18218,7 @@
     <col min="4" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:8" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>62</v>
       </c>
@@ -18148,7 +18242,7 @@
       <c r="G2" s="61"/>
       <c r="H2" s="62"/>
     </row>
-    <row r="3" spans="1:8" ht="25" customHeight="1">
+    <row r="3" spans="1:8" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18158,7 +18252,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="38.049999999999997" customHeight="1">
+    <row r="4" spans="1:8" ht="38.1" customHeight="1">
       <c r="A4" s="23" t="s">
         <v>64</v>
       </c>
@@ -18317,7 +18411,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
     <col min="5" max="6" width="30" customWidth="1"/>
@@ -18325,7 +18419,7 @@
     <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:8" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>42</v>
       </c>
@@ -18349,7 +18443,7 @@
       <c r="G2" s="61"/>
       <c r="H2" s="62"/>
     </row>
-    <row r="3" spans="1:8" ht="25" customHeight="1">
+    <row r="3" spans="1:8" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18359,7 +18453,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" ht="38.049999999999997" customHeight="1">
+    <row r="4" spans="1:8" ht="38.1" customHeight="1">
       <c r="A4" s="23" t="s">
         <v>87</v>
       </c>
@@ -18385,7 +18479,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="44.05" customHeight="1">
+    <row r="5" spans="1:8" ht="44.1" customHeight="1">
       <c r="A5" s="37" t="s">
         <v>92</v>
       </c>
@@ -18405,7 +18499,7 @@
       <c r="G5" s="43"/>
       <c r="H5" s="27"/>
     </row>
-    <row r="6" spans="1:8" ht="44.05" customHeight="1">
+    <row r="6" spans="1:8" ht="44.1" customHeight="1">
       <c r="A6" s="38" t="s">
         <v>95</v>
       </c>
@@ -18425,7 +18519,7 @@
       <c r="G6" s="44"/>
       <c r="H6" s="19"/>
     </row>
-    <row r="7" spans="1:8" ht="44.05" customHeight="1">
+    <row r="7" spans="1:8" ht="44.1" customHeight="1">
       <c r="A7" s="37" t="s">
         <v>96</v>
       </c>
@@ -18445,7 +18539,7 @@
       <c r="G7" s="43"/>
       <c r="H7" s="27"/>
     </row>
-    <row r="8" spans="1:8" ht="25" customHeight="1">
+    <row r="8" spans="1:8" ht="24.95" customHeight="1">
       <c r="A8" s="38"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -18455,7 +18549,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="19"/>
     </row>
-    <row r="9" spans="1:8" ht="25" customHeight="1">
+    <row r="9" spans="1:8" ht="24.95" customHeight="1">
       <c r="A9" s="37"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -18465,7 +18559,7 @@
       <c r="G9" s="43"/>
       <c r="H9" s="27"/>
     </row>
-    <row r="10" spans="1:8" ht="25" customHeight="1">
+    <row r="10" spans="1:8" ht="24.95" customHeight="1">
       <c r="A10" s="38"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -18475,7 +18569,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="19"/>
     </row>
-    <row r="11" spans="1:8" ht="25" customHeight="1">
+    <row r="11" spans="1:8" ht="24.95" customHeight="1">
       <c r="A11" s="37"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -18485,7 +18579,7 @@
       <c r="G11" s="43"/>
       <c r="H11" s="27"/>
     </row>
-    <row r="12" spans="1:8" ht="25" customHeight="1">
+    <row r="12" spans="1:8" ht="24.95" customHeight="1">
       <c r="A12" s="38"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -18495,7 +18589,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="19"/>
     </row>
-    <row r="13" spans="1:8" ht="25" customHeight="1">
+    <row r="13" spans="1:8" ht="24.95" customHeight="1">
       <c r="A13" s="37"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -18505,7 +18599,7 @@
       <c r="G13" s="43"/>
       <c r="H13" s="27"/>
     </row>
-    <row r="14" spans="1:8" ht="25" customHeight="1">
+    <row r="14" spans="1:8" ht="24.95" customHeight="1">
       <c r="A14" s="38"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -18515,7 +18609,7 @@
       <c r="G14" s="44"/>
       <c r="H14" s="19"/>
     </row>
-    <row r="15" spans="1:8" ht="25" customHeight="1">
+    <row r="15" spans="1:8" ht="24.95" customHeight="1">
       <c r="A15" s="37"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -18525,7 +18619,7 @@
       <c r="G15" s="43"/>
       <c r="H15" s="27"/>
     </row>
-    <row r="16" spans="1:8" ht="25" customHeight="1">
+    <row r="16" spans="1:8" ht="24.95" customHeight="1">
       <c r="A16" s="38"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -18535,7 +18629,7 @@
       <c r="G16" s="44"/>
       <c r="H16" s="19"/>
     </row>
-    <row r="17" spans="1:8" ht="25" customHeight="1">
+    <row r="17" spans="1:8" ht="24.95" customHeight="1">
       <c r="A17" s="37"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -18545,7 +18639,7 @@
       <c r="G17" s="43"/>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="25" customHeight="1">
+    <row r="18" spans="1:8" ht="24.95" customHeight="1">
       <c r="A18" s="38"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -18555,7 +18649,7 @@
       <c r="G18" s="44"/>
       <c r="H18" s="19"/>
     </row>
-    <row r="19" spans="1:8" ht="25" customHeight="1">
+    <row r="19" spans="1:8" ht="24.95" customHeight="1">
       <c r="A19" s="37"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -18565,7 +18659,7 @@
       <c r="G19" s="43"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="25" customHeight="1">
+    <row r="20" spans="1:8" ht="24.95" customHeight="1">
       <c r="A20" s="38"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -18575,7 +18669,7 @@
       <c r="G20" s="44"/>
       <c r="H20" s="19"/>
     </row>
-    <row r="21" spans="1:8" ht="25" customHeight="1">
+    <row r="21" spans="1:8" ht="24.95" customHeight="1">
       <c r="A21" s="37"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -18585,7 +18679,7 @@
       <c r="G21" s="43"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="25" customHeight="1">
+    <row r="22" spans="1:8" ht="24.95" customHeight="1">
       <c r="A22" s="38"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -18595,7 +18689,7 @@
       <c r="G22" s="44"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="25" customHeight="1">
+    <row r="23" spans="1:8" ht="24.95" customHeight="1">
       <c r="A23" s="37"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -18605,7 +18699,7 @@
       <c r="G23" s="43"/>
       <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:8" ht="25" customHeight="1">
+    <row r="24" spans="1:8" ht="24.95" customHeight="1">
       <c r="A24" s="38"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -18615,7 +18709,7 @@
       <c r="G24" s="44"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" ht="25" customHeight="1">
+    <row r="25" spans="1:8" ht="24.95" customHeight="1">
       <c r="A25" s="37"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -18625,7 +18719,7 @@
       <c r="G25" s="43"/>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" ht="25" customHeight="1">
+    <row r="26" spans="1:8" ht="24.95" customHeight="1">
       <c r="A26" s="38"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -18635,7 +18729,7 @@
       <c r="G26" s="44"/>
       <c r="H26" s="19"/>
     </row>
-    <row r="27" spans="1:8" ht="25" customHeight="1">
+    <row r="27" spans="1:8" ht="24.95" customHeight="1">
       <c r="A27" s="37"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -18645,7 +18739,7 @@
       <c r="G27" s="43"/>
       <c r="H27" s="27"/>
     </row>
-    <row r="28" spans="1:8" ht="25" customHeight="1">
+    <row r="28" spans="1:8" ht="24.95" customHeight="1">
       <c r="A28" s="38"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -18655,7 +18749,7 @@
       <c r="G28" s="44"/>
       <c r="H28" s="19"/>
     </row>
-    <row r="29" spans="1:8" ht="25" customHeight="1">
+    <row r="29" spans="1:8" ht="24.95" customHeight="1">
       <c r="A29" s="37"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -18665,7 +18759,7 @@
       <c r="G29" s="43"/>
       <c r="H29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="25" customHeight="1">
+    <row r="30" spans="1:8" ht="24.95" customHeight="1">
       <c r="A30" s="38"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -18675,7 +18769,7 @@
       <c r="G30" s="44"/>
       <c r="H30" s="19"/>
     </row>
-    <row r="31" spans="1:8" ht="25" customHeight="1">
+    <row r="31" spans="1:8" ht="24.95" customHeight="1">
       <c r="A31" s="37"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -18685,7 +18779,7 @@
       <c r="G31" s="43"/>
       <c r="H31" s="27"/>
     </row>
-    <row r="32" spans="1:8" ht="25" customHeight="1">
+    <row r="32" spans="1:8" ht="24.95" customHeight="1">
       <c r="A32" s="38"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -18695,7 +18789,7 @@
       <c r="G32" s="44"/>
       <c r="H32" s="19"/>
     </row>
-    <row r="33" spans="1:8" ht="25" customHeight="1">
+    <row r="33" spans="1:8" ht="24.95" customHeight="1">
       <c r="A33" s="37"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -18705,7 +18799,7 @@
       <c r="G33" s="43"/>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:8" ht="25" customHeight="1">
+    <row r="34" spans="1:8" ht="24.95" customHeight="1">
       <c r="A34" s="38"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -18715,7 +18809,7 @@
       <c r="G34" s="44"/>
       <c r="H34" s="19"/>
     </row>
-    <row r="35" spans="1:8" ht="25" customHeight="1">
+    <row r="35" spans="1:8" ht="24.95" customHeight="1">
       <c r="A35" s="37"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -18725,7 +18819,7 @@
       <c r="G35" s="43"/>
       <c r="H35" s="27"/>
     </row>
-    <row r="36" spans="1:8" ht="25" customHeight="1">
+    <row r="36" spans="1:8" ht="24.95" customHeight="1">
       <c r="A36" s="38"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -18735,7 +18829,7 @@
       <c r="G36" s="44"/>
       <c r="H36" s="19"/>
     </row>
-    <row r="37" spans="1:8" ht="25" customHeight="1">
+    <row r="37" spans="1:8" ht="24.95" customHeight="1">
       <c r="A37" s="37"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -18745,7 +18839,7 @@
       <c r="G37" s="43"/>
       <c r="H37" s="27"/>
     </row>
-    <row r="38" spans="1:8" ht="25" customHeight="1">
+    <row r="38" spans="1:8" ht="24.95" customHeight="1">
       <c r="A38" s="38"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -18755,7 +18849,7 @@
       <c r="G38" s="44"/>
       <c r="H38" s="19"/>
     </row>
-    <row r="39" spans="1:8" ht="25" customHeight="1">
+    <row r="39" spans="1:8" ht="24.95" customHeight="1">
       <c r="A39" s="37"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -18765,7 +18859,7 @@
       <c r="G39" s="43"/>
       <c r="H39" s="27"/>
     </row>
-    <row r="40" spans="1:8" ht="25" customHeight="1">
+    <row r="40" spans="1:8" ht="24.95" customHeight="1">
       <c r="A40" s="38"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -18775,7 +18869,7 @@
       <c r="G40" s="44"/>
       <c r="H40" s="19"/>
     </row>
-    <row r="41" spans="1:8" ht="25" customHeight="1">
+    <row r="41" spans="1:8" ht="24.95" customHeight="1">
       <c r="A41" s="37"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -18785,7 +18879,7 @@
       <c r="G41" s="43"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:8" ht="25" customHeight="1">
+    <row r="42" spans="1:8" ht="24.95" customHeight="1">
       <c r="A42" s="38"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -18795,7 +18889,7 @@
       <c r="G42" s="44"/>
       <c r="H42" s="19"/>
     </row>
-    <row r="43" spans="1:8" ht="25" customHeight="1">
+    <row r="43" spans="1:8" ht="24.95" customHeight="1">
       <c r="A43" s="37"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -18805,7 +18899,7 @@
       <c r="G43" s="43"/>
       <c r="H43" s="27"/>
     </row>
-    <row r="44" spans="1:8" ht="25" customHeight="1">
+    <row r="44" spans="1:8" ht="24.95" customHeight="1">
       <c r="A44" s="38"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -18815,7 +18909,7 @@
       <c r="G44" s="44"/>
       <c r="H44" s="19"/>
     </row>
-    <row r="45" spans="1:8" ht="25" customHeight="1">
+    <row r="45" spans="1:8" ht="24.95" customHeight="1">
       <c r="A45" s="37"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -18825,7 +18919,7 @@
       <c r="G45" s="43"/>
       <c r="H45" s="27"/>
     </row>
-    <row r="46" spans="1:8" ht="25" customHeight="1">
+    <row r="46" spans="1:8" ht="24.95" customHeight="1">
       <c r="A46" s="38"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -18835,7 +18929,7 @@
       <c r="G46" s="44"/>
       <c r="H46" s="19"/>
     </row>
-    <row r="47" spans="1:8" ht="25" customHeight="1">
+    <row r="47" spans="1:8" ht="24.95" customHeight="1">
       <c r="A47" s="37"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -18845,7 +18939,7 @@
       <c r="G47" s="43"/>
       <c r="H47" s="27"/>
     </row>
-    <row r="48" spans="1:8" ht="25" customHeight="1">
+    <row r="48" spans="1:8" ht="24.95" customHeight="1">
       <c r="A48" s="38"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -18855,7 +18949,7 @@
       <c r="G48" s="44"/>
       <c r="H48" s="19"/>
     </row>
-    <row r="49" spans="1:8" ht="25" customHeight="1">
+    <row r="49" spans="1:8" ht="24.95" customHeight="1">
       <c r="A49" s="37"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -18865,7 +18959,7 @@
       <c r="G49" s="43"/>
       <c r="H49" s="27"/>
     </row>
-    <row r="50" spans="1:8" ht="25" customHeight="1">
+    <row r="50" spans="1:8" ht="24.95" customHeight="1">
       <c r="A50" s="39"/>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -18898,13 +18992,13 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
     <col min="5" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:26" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>191</v>
       </c>
@@ -18932,7 +19026,7 @@
       <c r="I2" s="61"/>
       <c r="J2" s="62"/>
     </row>
-    <row r="3" spans="1:26" ht="25" customHeight="1">
+    <row r="3" spans="1:26" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18944,7 +19038,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="14.1">
+    <row r="4" spans="1:26" ht="15">
       <c r="A4" s="23" t="s">
         <v>26</v>
       </c>
@@ -18992,7 +19086,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="44.05" customHeight="1">
+    <row r="5" spans="1:26" ht="44.1" customHeight="1">
       <c r="A5" s="28"/>
       <c r="B5" s="25"/>
       <c r="C5" s="26"/>
@@ -19020,7 +19114,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="44.05" customHeight="1">
+    <row r="6" spans="1:26" ht="44.1" customHeight="1">
       <c r="A6" s="29"/>
       <c r="B6" s="17"/>
       <c r="C6" s="18"/>
@@ -19048,7 +19142,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="44.05" customHeight="1">
+    <row r="7" spans="1:26" ht="44.1" customHeight="1">
       <c r="A7" s="28"/>
       <c r="B7" s="25"/>
       <c r="C7" s="26"/>
@@ -19076,7 +19170,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="25" customHeight="1">
+    <row r="8" spans="1:26" ht="24.95" customHeight="1">
       <c r="A8" s="29"/>
       <c r="B8" s="17"/>
       <c r="C8" s="18"/>
@@ -19104,7 +19198,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="25" customHeight="1">
+    <row r="9" spans="1:26" ht="24.95" customHeight="1">
       <c r="A9" s="28"/>
       <c r="B9" s="25"/>
       <c r="C9" s="26"/>
@@ -19132,7 +19226,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="25" customHeight="1">
+    <row r="10" spans="1:26" ht="24.95" customHeight="1">
       <c r="A10" s="29"/>
       <c r="B10" s="17"/>
       <c r="C10" s="18"/>
@@ -19160,7 +19254,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="25" customHeight="1">
+    <row r="11" spans="1:26" ht="24.95" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="25"/>
       <c r="C11" s="26"/>
@@ -19188,7 +19282,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="25" customHeight="1">
+    <row r="12" spans="1:26" ht="24.95" customHeight="1">
       <c r="A12" s="29"/>
       <c r="B12" s="17"/>
       <c r="C12" s="18"/>
@@ -19216,7 +19310,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="25" customHeight="1">
+    <row r="13" spans="1:26" ht="24.95" customHeight="1">
       <c r="A13" s="28"/>
       <c r="B13" s="25"/>
       <c r="C13" s="26"/>
@@ -19244,7 +19338,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="25" customHeight="1">
+    <row r="14" spans="1:26" ht="24.95" customHeight="1">
       <c r="A14" s="29"/>
       <c r="B14" s="17"/>
       <c r="C14" s="18"/>
@@ -19272,7 +19366,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="25" customHeight="1">
+    <row r="15" spans="1:26" ht="24.95" customHeight="1">
       <c r="A15" s="28"/>
       <c r="B15" s="25"/>
       <c r="C15" s="26"/>
@@ -19300,7 +19394,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="25" customHeight="1">
+    <row r="16" spans="1:26" ht="24.95" customHeight="1">
       <c r="A16" s="29"/>
       <c r="B16" s="17"/>
       <c r="C16" s="18"/>
@@ -19328,7 +19422,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="25" customHeight="1">
+    <row r="17" spans="1:26" ht="24.95" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="25"/>
       <c r="C17" s="26"/>
@@ -19356,7 +19450,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="25" customHeight="1">
+    <row r="18" spans="1:26" ht="24.95" customHeight="1">
       <c r="A18" s="29"/>
       <c r="B18" s="17"/>
       <c r="C18" s="18"/>
@@ -19384,7 +19478,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="25" customHeight="1">
+    <row r="19" spans="1:26" ht="24.95" customHeight="1">
       <c r="A19" s="28"/>
       <c r="B19" s="25"/>
       <c r="C19" s="26"/>
@@ -19412,7 +19506,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="25" customHeight="1">
+    <row r="20" spans="1:26" ht="24.95" customHeight="1">
       <c r="A20" s="29"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -19440,7 +19534,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="25" customHeight="1">
+    <row r="21" spans="1:26" ht="24.95" customHeight="1">
       <c r="A21" s="28"/>
       <c r="B21" s="25"/>
       <c r="C21" s="26"/>
@@ -19468,7 +19562,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="25" customHeight="1">
+    <row r="22" spans="1:26" ht="24.95" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -19496,7 +19590,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="25" customHeight="1">
+    <row r="23" spans="1:26" ht="24.95" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="25"/>
       <c r="C23" s="26"/>
@@ -19524,7 +19618,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="25" customHeight="1">
+    <row r="24" spans="1:26" ht="24.95" customHeight="1">
       <c r="A24" s="29"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -19552,7 +19646,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="25" customHeight="1">
+    <row r="25" spans="1:26" ht="24.95" customHeight="1">
       <c r="A25" s="28"/>
       <c r="B25" s="25"/>
       <c r="C25" s="26"/>
@@ -19580,7 +19674,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="25" customHeight="1">
+    <row r="26" spans="1:26" ht="24.95" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -19608,7 +19702,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="25" customHeight="1">
+    <row r="27" spans="1:26" ht="24.95" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="26"/>
@@ -19636,7 +19730,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="25" customHeight="1">
+    <row r="28" spans="1:26" ht="24.95" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -19664,7 +19758,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="25" customHeight="1">
+    <row r="29" spans="1:26" ht="24.95" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="26"/>
@@ -19692,7 +19786,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="25" customHeight="1">
+    <row r="30" spans="1:26" ht="24.95" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="18"/>
@@ -19720,7 +19814,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="25" customHeight="1">
+    <row r="31" spans="1:26" ht="24.95" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="26"/>
@@ -19748,7 +19842,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="25" customHeight="1">
+    <row r="32" spans="1:26" ht="24.95" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="18"/>
@@ -19776,7 +19870,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="25" customHeight="1">
+    <row r="33" spans="1:26" ht="24.95" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="26"/>
@@ -19804,7 +19898,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="25" customHeight="1">
+    <row r="34" spans="1:26" ht="24.95" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="18"/>
@@ -19832,7 +19926,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="25" customHeight="1">
+    <row r="35" spans="1:26" ht="24.95" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="26"/>
@@ -19860,7 +19954,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="25" customHeight="1">
+    <row r="36" spans="1:26" ht="24.95" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="18"/>
@@ -19888,7 +19982,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="25" customHeight="1">
+    <row r="37" spans="1:26" ht="24.95" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="26"/>
@@ -19916,7 +20010,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="25" customHeight="1">
+    <row r="38" spans="1:26" ht="24.95" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="18"/>
@@ -19944,7 +20038,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="25" customHeight="1">
+    <row r="39" spans="1:26" ht="24.95" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="26"/>
@@ -19972,7 +20066,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="25" customHeight="1">
+    <row r="40" spans="1:26" ht="24.95" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="18"/>
@@ -20000,7 +20094,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="25" customHeight="1">
+    <row r="41" spans="1:26" ht="24.95" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="26"/>
@@ -20028,7 +20122,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="25" customHeight="1">
+    <row r="42" spans="1:26" ht="24.95" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="18"/>
@@ -20056,7 +20150,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="25" customHeight="1">
+    <row r="43" spans="1:26" ht="24.95" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="26"/>
@@ -20084,7 +20178,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="25" customHeight="1">
+    <row r="44" spans="1:26" ht="24.95" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="18"/>
@@ -20112,7 +20206,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="25" customHeight="1">
+    <row r="45" spans="1:26" ht="24.95" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="26"/>
@@ -20140,7 +20234,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="25" customHeight="1">
+    <row r="46" spans="1:26" ht="24.95" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="18"/>
@@ -20168,7 +20262,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="25" customHeight="1">
+    <row r="47" spans="1:26" ht="24.95" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="26"/>
@@ -20196,7 +20290,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="25" customHeight="1">
+    <row r="48" spans="1:26" ht="24.95" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="18"/>
@@ -20224,7 +20318,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="25" customHeight="1">
+    <row r="49" spans="1:26" ht="24.95" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="26"/>
@@ -20252,7 +20346,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="25" customHeight="1">
+    <row r="50" spans="1:26" ht="24.95" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="18"/>
@@ -20280,7 +20374,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="25" customHeight="1">
+    <row r="51" spans="1:26" ht="24.95" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="26"/>
@@ -20308,7 +20402,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="25" customHeight="1">
+    <row r="52" spans="1:26" ht="24.95" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="18"/>
@@ -20336,7 +20430,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="25" customHeight="1">
+    <row r="53" spans="1:26" ht="24.95" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="26"/>
@@ -20364,7 +20458,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="25" customHeight="1">
+    <row r="54" spans="1:26" ht="24.95" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="18"/>
@@ -20392,7 +20486,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="25" customHeight="1">
+    <row r="55" spans="1:26" ht="24.95" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="26"/>
@@ -20420,7 +20514,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="25" customHeight="1">
+    <row r="56" spans="1:26" ht="24.95" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="18"/>
@@ -20448,7 +20542,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="25" customHeight="1">
+    <row r="57" spans="1:26" ht="24.95" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="26"/>
@@ -20476,7 +20570,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="25" customHeight="1">
+    <row r="58" spans="1:26" ht="24.95" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="18"/>
@@ -20504,7 +20598,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="25" customHeight="1">
+    <row r="59" spans="1:26" ht="24.95" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="26"/>
@@ -20532,7 +20626,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="25" customHeight="1">
+    <row r="60" spans="1:26" ht="24.95" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="18"/>
@@ -20560,7 +20654,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="25" customHeight="1">
+    <row r="61" spans="1:26" ht="24.95" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="26"/>
@@ -20588,7 +20682,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="25" customHeight="1">
+    <row r="62" spans="1:26" ht="24.95" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="18"/>
@@ -20616,7 +20710,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="25" customHeight="1">
+    <row r="63" spans="1:26" ht="24.95" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="26"/>
@@ -20644,7 +20738,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="25" customHeight="1">
+    <row r="64" spans="1:26" ht="24.95" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="18"/>
@@ -20672,7 +20766,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="25" customHeight="1">
+    <row r="65" spans="1:26" ht="24.95" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="26"/>
@@ -20700,7 +20794,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="25" customHeight="1">
+    <row r="66" spans="1:26" ht="24.95" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="18"/>
@@ -20728,7 +20822,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="25" customHeight="1">
+    <row r="67" spans="1:26" ht="24.95" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="26"/>
@@ -20756,7 +20850,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="25" customHeight="1">
+    <row r="68" spans="1:26" ht="24.95" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="18"/>
@@ -20784,7 +20878,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="25" customHeight="1">
+    <row r="69" spans="1:26" ht="24.95" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="26"/>
@@ -20812,7 +20906,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="25" customHeight="1">
+    <row r="70" spans="1:26" ht="24.95" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="18"/>
@@ -20840,7 +20934,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="25" customHeight="1">
+    <row r="71" spans="1:26" ht="24.95" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="26"/>
@@ -20868,7 +20962,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="25" customHeight="1">
+    <row r="72" spans="1:26" ht="24.95" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="18"/>
@@ -20896,7 +20990,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="25" customHeight="1">
+    <row r="73" spans="1:26" ht="24.95" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="26"/>
@@ -20924,7 +21018,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="25" customHeight="1">
+    <row r="74" spans="1:26" ht="24.95" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="18"/>
@@ -20952,7 +21046,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="25" customHeight="1">
+    <row r="75" spans="1:26" ht="24.95" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="26"/>
@@ -20980,7 +21074,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="25" customHeight="1">
+    <row r="76" spans="1:26" ht="24.95" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="18"/>
@@ -21008,7 +21102,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="25" customHeight="1">
+    <row r="77" spans="1:26" ht="24.95" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="26"/>
@@ -21036,7 +21130,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="25" customHeight="1">
+    <row r="78" spans="1:26" ht="24.95" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="18"/>
@@ -21064,7 +21158,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="25" customHeight="1">
+    <row r="79" spans="1:26" ht="24.95" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="26"/>
@@ -21092,7 +21186,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="25" customHeight="1">
+    <row r="80" spans="1:26" ht="24.95" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="18"/>
@@ -21120,7 +21214,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="25" customHeight="1">
+    <row r="81" spans="1:26" ht="24.95" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="26"/>
@@ -21148,7 +21242,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="25" customHeight="1">
+    <row r="82" spans="1:26" ht="24.95" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="18"/>
@@ -21176,7 +21270,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="25" customHeight="1">
+    <row r="83" spans="1:26" ht="24.95" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="26"/>
@@ -21204,7 +21298,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="25" customHeight="1">
+    <row r="84" spans="1:26" ht="24.95" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="18"/>
@@ -21232,7 +21326,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="25" customHeight="1">
+    <row r="85" spans="1:26" ht="24.95" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="26"/>
@@ -21260,7 +21354,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="25" customHeight="1">
+    <row r="86" spans="1:26" ht="24.95" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
@@ -21288,7 +21382,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="25" customHeight="1">
+    <row r="87" spans="1:26" ht="24.95" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="26"/>
@@ -21316,7 +21410,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="25" customHeight="1">
+    <row r="88" spans="1:26" ht="24.95" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="18"/>
@@ -21344,7 +21438,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="25" customHeight="1">
+    <row r="89" spans="1:26" ht="24.95" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="26"/>
@@ -21372,7 +21466,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="25" customHeight="1">
+    <row r="90" spans="1:26" ht="24.95" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="18"/>
@@ -21400,7 +21494,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="25" customHeight="1">
+    <row r="91" spans="1:26" ht="24.95" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="26"/>
@@ -21428,7 +21522,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="25" customHeight="1">
+    <row r="92" spans="1:26" ht="24.95" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="18"/>
@@ -21456,7 +21550,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="25" customHeight="1">
+    <row r="93" spans="1:26" ht="24.95" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="26"/>
@@ -21484,7 +21578,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="25" customHeight="1">
+    <row r="94" spans="1:26" ht="24.95" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="18"/>
@@ -21512,7 +21606,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="25" customHeight="1">
+    <row r="95" spans="1:26" ht="24.95" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="26"/>
@@ -21540,7 +21634,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="25" customHeight="1">
+    <row r="96" spans="1:26" ht="24.95" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="18"/>
@@ -21568,7 +21662,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="25" customHeight="1">
+    <row r="97" spans="1:26" ht="24.95" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="26"/>
@@ -21596,7 +21690,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="25" customHeight="1">
+    <row r="98" spans="1:26" ht="24.95" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="18"/>
@@ -21624,7 +21718,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="25" customHeight="1">
+    <row r="99" spans="1:26" ht="24.95" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="26"/>
@@ -21652,7 +21746,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="25" customHeight="1">
+    <row r="100" spans="1:26" ht="24.95" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="18"/>
@@ -21680,7 +21774,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="25" customHeight="1">
+    <row r="101" spans="1:26" ht="24.95" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="26"/>
@@ -21708,7 +21802,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="25" customHeight="1">
+    <row r="102" spans="1:26" ht="24.95" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="18"/>
@@ -21736,7 +21830,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="25" customHeight="1">
+    <row r="103" spans="1:26" ht="24.95" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="26"/>
@@ -21764,7 +21858,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="25" customHeight="1">
+    <row r="104" spans="1:26" ht="24.95" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="21"/>
@@ -25886,13 +25980,13 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I104">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>I5="Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>I5="Partly"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>I5="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25932,17 +26026,20 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="20" customWidth="1"/>
-    <col min="8" max="9" width="36" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:26" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>97</v>
       </c>
@@ -25968,7 +26065,7 @@
       <c r="H2" s="61"/>
       <c r="I2" s="62"/>
     </row>
-    <row r="3" spans="1:26" ht="25" customHeight="1">
+    <row r="3" spans="1:26" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -25979,32 +26076,32 @@
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="28.2">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:26" ht="15">
+      <c r="A4" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="68" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="69" t="s">
         <v>103</v>
       </c>
       <c r="J4" s="1"/>
@@ -26159,7 +26256,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="25" customHeight="1">
+    <row r="8" spans="1:26" ht="24.95" customHeight="1">
       <c r="A8" s="28">
         <v>46277</v>
       </c>
@@ -26205,7 +26302,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="25" customHeight="1">
+    <row r="9" spans="1:26" ht="24.95" customHeight="1">
       <c r="A9" s="28">
         <v>46277</v>
       </c>
@@ -26249,7 +26346,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="25" customHeight="1">
+    <row r="10" spans="1:26" ht="24.95" customHeight="1">
       <c r="A10" s="28">
         <v>46277</v>
       </c>
@@ -26295,7 +26392,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="25" customHeight="1">
+    <row r="11" spans="1:26" ht="24.95" customHeight="1">
       <c r="A11" s="28">
         <v>46278</v>
       </c>
@@ -26341,7 +26438,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="25" customHeight="1">
+    <row r="12" spans="1:26" ht="24.95" customHeight="1">
       <c r="A12" s="28">
         <v>46278</v>
       </c>
@@ -26387,7 +26484,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="25" customHeight="1">
+    <row r="13" spans="1:26" ht="24.95" customHeight="1">
       <c r="A13" s="28">
         <v>46278</v>
       </c>
@@ -26433,7 +26530,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="25" customHeight="1">
+    <row r="14" spans="1:26" ht="24.95" customHeight="1">
       <c r="A14" s="29">
         <v>46284</v>
       </c>
@@ -26479,7 +26576,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="25" customHeight="1">
+    <row r="15" spans="1:26" ht="24.95" customHeight="1">
       <c r="A15" s="28">
         <v>46284</v>
       </c>
@@ -26525,7 +26622,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="25" customHeight="1">
+    <row r="16" spans="1:26" ht="24.95" customHeight="1">
       <c r="A16" s="29">
         <v>46284</v>
       </c>
@@ -26569,7 +26666,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="25" customHeight="1">
+    <row r="17" spans="1:26" ht="24.95" customHeight="1">
       <c r="A17" s="28">
         <v>46285</v>
       </c>
@@ -26611,7 +26708,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="25" customHeight="1">
+    <row r="18" spans="1:26" ht="24.95" customHeight="1">
       <c r="A18" s="29">
         <v>46285</v>
       </c>
@@ -26653,7 +26750,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="25" customHeight="1">
+    <row r="19" spans="1:26" ht="24.95" customHeight="1">
       <c r="A19" s="28">
         <v>46285</v>
       </c>
@@ -26695,15 +26792,31 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="25" customHeight="1">
-      <c r="A20" s="29"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
+    <row r="20" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A20" s="29">
+        <v>46291</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="17">
+        <v>542</v>
+      </c>
+      <c r="E20" s="40">
+        <v>0</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>57</v>
+      </c>
       <c r="I20" s="19"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -26723,15 +26836,31 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="25" customHeight="1">
-      <c r="A21" s="28"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
+    <row r="21" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A21" s="28">
+        <v>46291</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="25">
+        <v>450</v>
+      </c>
+      <c r="E21" s="42">
+        <v>0</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>57</v>
+      </c>
       <c r="I21" s="27"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -26751,15 +26880,31 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="25" customHeight="1">
-      <c r="A22" s="29"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="40"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
+    <row r="22" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A22" s="29">
+        <v>46291</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="17">
+        <v>426</v>
+      </c>
+      <c r="E22" s="40">
+        <v>0</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>57</v>
+      </c>
       <c r="I22" s="19"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -26779,13 +26924,25 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="25" customHeight="1">
-      <c r="A23" s="28"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="25"/>
+    <row r="23" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A23" s="28">
+        <v>46292</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="25">
+        <v>426</v>
+      </c>
+      <c r="E23" s="42">
+        <v>1</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>61</v>
+      </c>
       <c r="G23" s="25"/>
       <c r="H23" s="25"/>
       <c r="I23" s="27"/>
@@ -26807,13 +26964,25 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="25" customHeight="1">
-      <c r="A24" s="29"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="17"/>
+    <row r="24" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A24" s="29">
+        <v>46292</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="17">
+        <v>450</v>
+      </c>
+      <c r="E24" s="40">
+        <v>0.5</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>56</v>
+      </c>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
       <c r="I24" s="19"/>
@@ -26835,13 +27004,25 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="25" customHeight="1">
-      <c r="A25" s="28"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="25"/>
+    <row r="25" spans="1:26" ht="24.95" customHeight="1">
+      <c r="A25" s="28">
+        <v>46292</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="25">
+        <v>542</v>
+      </c>
+      <c r="E25" s="42">
+        <v>0.5</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>56</v>
+      </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="27"/>
@@ -26863,7 +27044,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="25" customHeight="1">
+    <row r="26" spans="1:26" ht="24.95" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -26891,7 +27072,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="25" customHeight="1">
+    <row r="27" spans="1:26" ht="24.95" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -26919,7 +27100,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="25" customHeight="1">
+    <row r="28" spans="1:26" ht="24.95" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -26947,7 +27128,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="25" customHeight="1">
+    <row r="29" spans="1:26" ht="24.95" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -26975,7 +27156,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="25" customHeight="1">
+    <row r="30" spans="1:26" ht="24.95" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -27003,7 +27184,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="25" customHeight="1">
+    <row r="31" spans="1:26" ht="24.95" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -27031,7 +27212,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="25" customHeight="1">
+    <row r="32" spans="1:26" ht="24.95" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -27059,7 +27240,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="25" customHeight="1">
+    <row r="33" spans="1:26" ht="24.95" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -27087,7 +27268,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="25" customHeight="1">
+    <row r="34" spans="1:26" ht="24.95" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -27115,7 +27296,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="25" customHeight="1">
+    <row r="35" spans="1:26" ht="24.95" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -27143,7 +27324,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="25" customHeight="1">
+    <row r="36" spans="1:26" ht="24.95" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -27171,7 +27352,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="25" customHeight="1">
+    <row r="37" spans="1:26" ht="24.95" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -27199,7 +27380,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="25" customHeight="1">
+    <row r="38" spans="1:26" ht="24.95" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -27227,7 +27408,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="25" customHeight="1">
+    <row r="39" spans="1:26" ht="24.95" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -27255,7 +27436,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="25" customHeight="1">
+    <row r="40" spans="1:26" ht="24.95" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -27283,7 +27464,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="25" customHeight="1">
+    <row r="41" spans="1:26" ht="24.95" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -27311,7 +27492,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="25" customHeight="1">
+    <row r="42" spans="1:26" ht="24.95" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -27339,7 +27520,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="25" customHeight="1">
+    <row r="43" spans="1:26" ht="24.95" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -27367,7 +27548,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="25" customHeight="1">
+    <row r="44" spans="1:26" ht="24.95" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -27395,7 +27576,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="25" customHeight="1">
+    <row r="45" spans="1:26" ht="24.95" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -27423,7 +27604,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="25" customHeight="1">
+    <row r="46" spans="1:26" ht="24.95" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -27451,7 +27632,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="25" customHeight="1">
+    <row r="47" spans="1:26" ht="24.95" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -27479,7 +27660,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="25" customHeight="1">
+    <row r="48" spans="1:26" ht="24.95" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -27507,7 +27688,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="25" customHeight="1">
+    <row r="49" spans="1:26" ht="24.95" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -27535,7 +27716,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="25" customHeight="1">
+    <row r="50" spans="1:26" ht="24.95" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -27563,7 +27744,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="25" customHeight="1">
+    <row r="51" spans="1:26" ht="24.95" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -27591,7 +27772,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="25" customHeight="1">
+    <row r="52" spans="1:26" ht="24.95" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -27619,7 +27800,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="25" customHeight="1">
+    <row r="53" spans="1:26" ht="24.95" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -27647,7 +27828,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="25" customHeight="1">
+    <row r="54" spans="1:26" ht="24.95" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -27675,7 +27856,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="25" customHeight="1">
+    <row r="55" spans="1:26" ht="24.95" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -27703,7 +27884,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="25" customHeight="1">
+    <row r="56" spans="1:26" ht="24.95" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -27731,7 +27912,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="25" customHeight="1">
+    <row r="57" spans="1:26" ht="24.95" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -27759,7 +27940,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="25" customHeight="1">
+    <row r="58" spans="1:26" ht="24.95" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -27787,7 +27968,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="25" customHeight="1">
+    <row r="59" spans="1:26" ht="24.95" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -27815,7 +27996,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="25" customHeight="1">
+    <row r="60" spans="1:26" ht="24.95" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -27843,7 +28024,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="25" customHeight="1">
+    <row r="61" spans="1:26" ht="24.95" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -27871,7 +28052,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="25" customHeight="1">
+    <row r="62" spans="1:26" ht="24.95" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -27899,7 +28080,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="25" customHeight="1">
+    <row r="63" spans="1:26" ht="24.95" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -27927,7 +28108,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="25" customHeight="1">
+    <row r="64" spans="1:26" ht="24.95" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -27955,7 +28136,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="25" customHeight="1">
+    <row r="65" spans="1:26" ht="24.95" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -27983,7 +28164,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="25" customHeight="1">
+    <row r="66" spans="1:26" ht="24.95" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -28011,7 +28192,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="25" customHeight="1">
+    <row r="67" spans="1:26" ht="24.95" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -28039,7 +28220,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="25" customHeight="1">
+    <row r="68" spans="1:26" ht="24.95" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -28067,7 +28248,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="25" customHeight="1">
+    <row r="69" spans="1:26" ht="24.95" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -28095,7 +28276,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="25" customHeight="1">
+    <row r="70" spans="1:26" ht="24.95" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -28123,7 +28304,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="25" customHeight="1">
+    <row r="71" spans="1:26" ht="24.95" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -28151,7 +28332,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="25" customHeight="1">
+    <row r="72" spans="1:26" ht="24.95" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -28179,7 +28360,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="25" customHeight="1">
+    <row r="73" spans="1:26" ht="24.95" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -28207,7 +28388,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="25" customHeight="1">
+    <row r="74" spans="1:26" ht="24.95" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -28235,7 +28416,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="25" customHeight="1">
+    <row r="75" spans="1:26" ht="24.95" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -28263,7 +28444,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="25" customHeight="1">
+    <row r="76" spans="1:26" ht="24.95" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -28291,7 +28472,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="25" customHeight="1">
+    <row r="77" spans="1:26" ht="24.95" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -28319,7 +28500,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="25" customHeight="1">
+    <row r="78" spans="1:26" ht="24.95" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -28347,7 +28528,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="25" customHeight="1">
+    <row r="79" spans="1:26" ht="24.95" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -28375,7 +28556,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="25" customHeight="1">
+    <row r="80" spans="1:26" ht="24.95" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -28403,7 +28584,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="25" customHeight="1">
+    <row r="81" spans="1:26" ht="24.95" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -28431,7 +28612,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="25" customHeight="1">
+    <row r="82" spans="1:26" ht="24.95" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -28459,7 +28640,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="25" customHeight="1">
+    <row r="83" spans="1:26" ht="24.95" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -28487,7 +28668,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="25" customHeight="1">
+    <row r="84" spans="1:26" ht="24.95" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -28515,7 +28696,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="25" customHeight="1">
+    <row r="85" spans="1:26" ht="24.95" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -28543,7 +28724,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="25" customHeight="1">
+    <row r="86" spans="1:26" ht="24.95" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -28571,7 +28752,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="25" customHeight="1">
+    <row r="87" spans="1:26" ht="24.95" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -28599,7 +28780,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="25" customHeight="1">
+    <row r="88" spans="1:26" ht="24.95" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -28627,7 +28808,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="25" customHeight="1">
+    <row r="89" spans="1:26" ht="24.95" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -28655,7 +28836,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="25" customHeight="1">
+    <row r="90" spans="1:26" ht="24.95" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -28683,7 +28864,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="25" customHeight="1">
+    <row r="91" spans="1:26" ht="24.95" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -28711,7 +28892,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="25" customHeight="1">
+    <row r="92" spans="1:26" ht="24.95" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -28739,7 +28920,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="25" customHeight="1">
+    <row r="93" spans="1:26" ht="24.95" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -28767,7 +28948,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="25" customHeight="1">
+    <row r="94" spans="1:26" ht="24.95" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -28795,7 +28976,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="25" customHeight="1">
+    <row r="95" spans="1:26" ht="24.95" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -28823,7 +29004,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="25" customHeight="1">
+    <row r="96" spans="1:26" ht="24.95" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -28851,7 +29032,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="25" customHeight="1">
+    <row r="97" spans="1:26" ht="24.95" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -28879,7 +29060,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="25" customHeight="1">
+    <row r="98" spans="1:26" ht="24.95" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -28907,7 +29088,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="25" customHeight="1">
+    <row r="99" spans="1:26" ht="24.95" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -28935,7 +29116,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="25" customHeight="1">
+    <row r="100" spans="1:26" ht="24.95" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -28963,7 +29144,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="25" customHeight="1">
+    <row r="101" spans="1:26" ht="24.95" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -28991,7 +29172,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="25" customHeight="1">
+    <row r="102" spans="1:26" ht="24.95" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -29019,7 +29200,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="25" customHeight="1">
+    <row r="103" spans="1:26" ht="24.95" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -29047,7 +29228,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="25" customHeight="1">
+    <row r="104" spans="1:26" ht="24.95" customHeight="1">
       <c r="A104" s="29"/>
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
@@ -29075,7 +29256,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" spans="1:26" ht="25" customHeight="1">
+    <row r="105" spans="1:26" ht="24.95" customHeight="1">
       <c r="A105" s="28"/>
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
@@ -29103,7 +29284,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" spans="1:26" ht="25" customHeight="1">
+    <row r="106" spans="1:26" ht="24.95" customHeight="1">
       <c r="A106" s="29"/>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
@@ -29131,7 +29312,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" spans="1:26" ht="25" customHeight="1">
+    <row r="107" spans="1:26" ht="24.95" customHeight="1">
       <c r="A107" s="28"/>
       <c r="B107" s="25"/>
       <c r="C107" s="25"/>
@@ -29159,7 +29340,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" spans="1:26" ht="25" customHeight="1">
+    <row r="108" spans="1:26" ht="24.95" customHeight="1">
       <c r="A108" s="29"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
@@ -29187,7 +29368,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" spans="1:26" ht="25" customHeight="1">
+    <row r="109" spans="1:26" ht="24.95" customHeight="1">
       <c r="A109" s="28"/>
       <c r="B109" s="25"/>
       <c r="C109" s="25"/>
@@ -29215,7 +29396,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" spans="1:26" ht="25" customHeight="1">
+    <row r="110" spans="1:26" ht="24.95" customHeight="1">
       <c r="A110" s="29"/>
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
@@ -29243,7 +29424,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" ht="25" customHeight="1">
+    <row r="111" spans="1:26" ht="24.95" customHeight="1">
       <c r="A111" s="28"/>
       <c r="B111" s="25"/>
       <c r="C111" s="25"/>
@@ -29271,7 +29452,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" spans="1:26" ht="25" customHeight="1">
+    <row r="112" spans="1:26" ht="24.95" customHeight="1">
       <c r="A112" s="29"/>
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
@@ -29299,7 +29480,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" spans="1:26" ht="25" customHeight="1">
+    <row r="113" spans="1:26" ht="24.95" customHeight="1">
       <c r="A113" s="28"/>
       <c r="B113" s="25"/>
       <c r="C113" s="25"/>
@@ -29327,7 +29508,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" spans="1:26" ht="25" customHeight="1">
+    <row r="114" spans="1:26" ht="24.95" customHeight="1">
       <c r="A114" s="29"/>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
@@ -29355,7 +29536,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115" spans="1:26" ht="25" customHeight="1">
+    <row r="115" spans="1:26" ht="24.95" customHeight="1">
       <c r="A115" s="28"/>
       <c r="B115" s="25"/>
       <c r="C115" s="25"/>
@@ -29383,7 +29564,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" spans="1:26" ht="25" customHeight="1">
+    <row r="116" spans="1:26" ht="24.95" customHeight="1">
       <c r="A116" s="29"/>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
@@ -29411,7 +29592,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" spans="1:26" ht="25" customHeight="1">
+    <row r="117" spans="1:26" ht="24.95" customHeight="1">
       <c r="A117" s="28"/>
       <c r="B117" s="25"/>
       <c r="C117" s="25"/>
@@ -29439,7 +29620,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" spans="1:26" ht="25" customHeight="1">
+    <row r="118" spans="1:26" ht="24.95" customHeight="1">
       <c r="A118" s="29"/>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
@@ -29467,7 +29648,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" spans="1:26" ht="25" customHeight="1">
+    <row r="119" spans="1:26" ht="24.95" customHeight="1">
       <c r="A119" s="28"/>
       <c r="B119" s="25"/>
       <c r="C119" s="25"/>
@@ -29495,7 +29676,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" spans="1:26" ht="25" customHeight="1">
+    <row r="120" spans="1:26" ht="24.95" customHeight="1">
       <c r="A120" s="29"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
@@ -29523,7 +29704,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" spans="1:26" ht="25" customHeight="1">
+    <row r="121" spans="1:26" ht="24.95" customHeight="1">
       <c r="A121" s="28"/>
       <c r="B121" s="25"/>
       <c r="C121" s="25"/>
@@ -29551,7 +29732,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" spans="1:26" ht="25" customHeight="1">
+    <row r="122" spans="1:26" ht="24.95" customHeight="1">
       <c r="A122" s="29"/>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
@@ -29579,7 +29760,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" spans="1:26" ht="25" customHeight="1">
+    <row r="123" spans="1:26" ht="24.95" customHeight="1">
       <c r="A123" s="28"/>
       <c r="B123" s="25"/>
       <c r="C123" s="25"/>
@@ -29607,7 +29788,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" spans="1:26" ht="25" customHeight="1">
+    <row r="124" spans="1:26" ht="24.95" customHeight="1">
       <c r="A124" s="29"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
@@ -29635,7 +29816,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" spans="1:26" ht="25" customHeight="1">
+    <row r="125" spans="1:26" ht="24.95" customHeight="1">
       <c r="A125" s="28"/>
       <c r="B125" s="25"/>
       <c r="C125" s="25"/>
@@ -29663,7 +29844,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" spans="1:26" ht="25" customHeight="1">
+    <row r="126" spans="1:26" ht="24.95" customHeight="1">
       <c r="A126" s="29"/>
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
@@ -29691,7 +29872,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" spans="1:26" ht="25" customHeight="1">
+    <row r="127" spans="1:26" ht="24.95" customHeight="1">
       <c r="A127" s="28"/>
       <c r="B127" s="25"/>
       <c r="C127" s="25"/>
@@ -29719,7 +29900,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" spans="1:26" ht="25" customHeight="1">
+    <row r="128" spans="1:26" ht="24.95" customHeight="1">
       <c r="A128" s="29"/>
       <c r="B128" s="17"/>
       <c r="C128" s="17"/>
@@ -29747,7 +29928,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129" spans="1:26" ht="25" customHeight="1">
+    <row r="129" spans="1:26" ht="24.95" customHeight="1">
       <c r="A129" s="28"/>
       <c r="B129" s="25"/>
       <c r="C129" s="25"/>
@@ -29775,7 +29956,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130" spans="1:26" ht="25" customHeight="1">
+    <row r="130" spans="1:26" ht="24.95" customHeight="1">
       <c r="A130" s="29"/>
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
@@ -29803,7 +29984,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131" spans="1:26" ht="25" customHeight="1">
+    <row r="131" spans="1:26" ht="24.95" customHeight="1">
       <c r="A131" s="28"/>
       <c r="B131" s="25"/>
       <c r="C131" s="25"/>
@@ -29831,7 +30012,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132" spans="1:26" ht="25" customHeight="1">
+    <row r="132" spans="1:26" ht="24.95" customHeight="1">
       <c r="A132" s="29"/>
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
@@ -29859,7 +30040,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133" spans="1:26" ht="25" customHeight="1">
+    <row r="133" spans="1:26" ht="24.95" customHeight="1">
       <c r="A133" s="28"/>
       <c r="B133" s="25"/>
       <c r="C133" s="25"/>
@@ -29887,7 +30068,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134" spans="1:26" ht="25" customHeight="1">
+    <row r="134" spans="1:26" ht="24.95" customHeight="1">
       <c r="A134" s="29"/>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
@@ -29915,7 +30096,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135" spans="1:26" ht="25" customHeight="1">
+    <row r="135" spans="1:26" ht="24.95" customHeight="1">
       <c r="A135" s="28"/>
       <c r="B135" s="25"/>
       <c r="C135" s="25"/>
@@ -29943,7 +30124,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136" spans="1:26" ht="25" customHeight="1">
+    <row r="136" spans="1:26" ht="24.95" customHeight="1">
       <c r="A136" s="29"/>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
@@ -29971,7 +30152,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" spans="1:26" ht="25" customHeight="1">
+    <row r="137" spans="1:26" ht="24.95" customHeight="1">
       <c r="A137" s="28"/>
       <c r="B137" s="25"/>
       <c r="C137" s="25"/>
@@ -29999,7 +30180,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" spans="1:26" ht="25" customHeight="1">
+    <row r="138" spans="1:26" ht="24.95" customHeight="1">
       <c r="A138" s="29"/>
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
@@ -30027,7 +30208,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" spans="1:26" ht="25" customHeight="1">
+    <row r="139" spans="1:26" ht="24.95" customHeight="1">
       <c r="A139" s="28"/>
       <c r="B139" s="25"/>
       <c r="C139" s="25"/>
@@ -30055,7 +30236,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="1:26" ht="25" customHeight="1">
+    <row r="140" spans="1:26" ht="24.95" customHeight="1">
       <c r="A140" s="29"/>
       <c r="B140" s="17"/>
       <c r="C140" s="17"/>
@@ -30083,7 +30264,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" spans="1:26" ht="25" customHeight="1">
+    <row r="141" spans="1:26" ht="24.95" customHeight="1">
       <c r="A141" s="28"/>
       <c r="B141" s="25"/>
       <c r="C141" s="25"/>
@@ -30111,7 +30292,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" spans="1:26" ht="25" customHeight="1">
+    <row r="142" spans="1:26" ht="24.95" customHeight="1">
       <c r="A142" s="29"/>
       <c r="B142" s="17"/>
       <c r="C142" s="17"/>
@@ -30139,7 +30320,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" spans="1:26" ht="25" customHeight="1">
+    <row r="143" spans="1:26" ht="24.95" customHeight="1">
       <c r="A143" s="28"/>
       <c r="B143" s="25"/>
       <c r="C143" s="25"/>
@@ -30167,7 +30348,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144" spans="1:26" ht="25" customHeight="1">
+    <row r="144" spans="1:26" ht="24.95" customHeight="1">
       <c r="A144" s="29"/>
       <c r="B144" s="17"/>
       <c r="C144" s="17"/>
@@ -30195,7 +30376,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145" spans="1:26" ht="25" customHeight="1">
+    <row r="145" spans="1:26" ht="24.95" customHeight="1">
       <c r="A145" s="28"/>
       <c r="B145" s="25"/>
       <c r="C145" s="25"/>
@@ -30223,7 +30404,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146" spans="1:26" ht="25" customHeight="1">
+    <row r="146" spans="1:26" ht="24.95" customHeight="1">
       <c r="A146" s="29"/>
       <c r="B146" s="17"/>
       <c r="C146" s="17"/>
@@ -30251,7 +30432,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147" spans="1:26" ht="25" customHeight="1">
+    <row r="147" spans="1:26" ht="24.95" customHeight="1">
       <c r="A147" s="28"/>
       <c r="B147" s="25"/>
       <c r="C147" s="25"/>
@@ -30279,7 +30460,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148" spans="1:26" ht="25" customHeight="1">
+    <row r="148" spans="1:26" ht="24.95" customHeight="1">
       <c r="A148" s="29"/>
       <c r="B148" s="17"/>
       <c r="C148" s="17"/>
@@ -30307,7 +30488,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149" spans="1:26" ht="25" customHeight="1">
+    <row r="149" spans="1:26" ht="24.95" customHeight="1">
       <c r="A149" s="28"/>
       <c r="B149" s="25"/>
       <c r="C149" s="25"/>
@@ -30335,7 +30516,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150" spans="1:26" ht="25" customHeight="1">
+    <row r="150" spans="1:26" ht="24.95" customHeight="1">
       <c r="A150" s="29"/>
       <c r="B150" s="17"/>
       <c r="C150" s="17"/>
@@ -30363,7 +30544,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151" spans="1:26" ht="25" customHeight="1">
+    <row r="151" spans="1:26" ht="24.95" customHeight="1">
       <c r="A151" s="28"/>
       <c r="B151" s="25"/>
       <c r="C151" s="25"/>
@@ -30391,7 +30572,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" spans="1:26" ht="25" customHeight="1">
+    <row r="152" spans="1:26" ht="24.95" customHeight="1">
       <c r="A152" s="29"/>
       <c r="B152" s="17"/>
       <c r="C152" s="17"/>
@@ -30419,7 +30600,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" spans="1:26" ht="25" customHeight="1">
+    <row r="153" spans="1:26" ht="24.95" customHeight="1">
       <c r="A153" s="28"/>
       <c r="B153" s="25"/>
       <c r="C153" s="25"/>
@@ -30447,7 +30628,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" spans="1:26" ht="25" customHeight="1">
+    <row r="154" spans="1:26" ht="24.95" customHeight="1">
       <c r="A154" s="29"/>
       <c r="B154" s="17"/>
       <c r="C154" s="17"/>
@@ -30475,7 +30656,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" spans="1:26" ht="25" customHeight="1">
+    <row r="155" spans="1:26" ht="24.95" customHeight="1">
       <c r="A155" s="28"/>
       <c r="B155" s="25"/>
       <c r="C155" s="25"/>
@@ -30503,7 +30684,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156" spans="1:26" ht="25" customHeight="1">
+    <row r="156" spans="1:26" ht="24.95" customHeight="1">
       <c r="A156" s="29"/>
       <c r="B156" s="17"/>
       <c r="C156" s="17"/>
@@ -30531,7 +30712,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157" spans="1:26" ht="25" customHeight="1">
+    <row r="157" spans="1:26" ht="24.95" customHeight="1">
       <c r="A157" s="28"/>
       <c r="B157" s="25"/>
       <c r="C157" s="25"/>
@@ -30559,7 +30740,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158" spans="1:26" ht="25" customHeight="1">
+    <row r="158" spans="1:26" ht="24.95" customHeight="1">
       <c r="A158" s="29"/>
       <c r="B158" s="17"/>
       <c r="C158" s="17"/>
@@ -30587,7 +30768,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" spans="1:26" ht="25" customHeight="1">
+    <row r="159" spans="1:26" ht="24.95" customHeight="1">
       <c r="A159" s="28"/>
       <c r="B159" s="25"/>
       <c r="C159" s="25"/>
@@ -30615,7 +30796,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160" spans="1:26" ht="25" customHeight="1">
+    <row r="160" spans="1:26" ht="24.95" customHeight="1">
       <c r="A160" s="29"/>
       <c r="B160" s="17"/>
       <c r="C160" s="17"/>
@@ -30643,7 +30824,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161" spans="1:26" ht="25" customHeight="1">
+    <row r="161" spans="1:26" ht="24.95" customHeight="1">
       <c r="A161" s="28"/>
       <c r="B161" s="25"/>
       <c r="C161" s="25"/>
@@ -30671,7 +30852,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" spans="1:26" ht="25" customHeight="1">
+    <row r="162" spans="1:26" ht="24.95" customHeight="1">
       <c r="A162" s="29"/>
       <c r="B162" s="17"/>
       <c r="C162" s="17"/>
@@ -30699,7 +30880,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" spans="1:26" ht="25" customHeight="1">
+    <row r="163" spans="1:26" ht="24.95" customHeight="1">
       <c r="A163" s="28"/>
       <c r="B163" s="25"/>
       <c r="C163" s="25"/>
@@ -30727,7 +30908,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" spans="1:26" ht="25" customHeight="1">
+    <row r="164" spans="1:26" ht="24.95" customHeight="1">
       <c r="A164" s="29"/>
       <c r="B164" s="17"/>
       <c r="C164" s="17"/>
@@ -30755,7 +30936,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" spans="1:26" ht="25" customHeight="1">
+    <row r="165" spans="1:26" ht="24.95" customHeight="1">
       <c r="A165" s="28"/>
       <c r="B165" s="25"/>
       <c r="C165" s="25"/>
@@ -30783,7 +30964,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166" spans="1:26" ht="25" customHeight="1">
+    <row r="166" spans="1:26" ht="24.95" customHeight="1">
       <c r="A166" s="29"/>
       <c r="B166" s="17"/>
       <c r="C166" s="17"/>
@@ -30811,7 +30992,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167" spans="1:26" ht="25" customHeight="1">
+    <row r="167" spans="1:26" ht="24.95" customHeight="1">
       <c r="A167" s="28"/>
       <c r="B167" s="25"/>
       <c r="C167" s="25"/>
@@ -30839,7 +31020,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168" spans="1:26" ht="25" customHeight="1">
+    <row r="168" spans="1:26" ht="24.95" customHeight="1">
       <c r="A168" s="29"/>
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
@@ -30867,7 +31048,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" spans="1:26" ht="25" customHeight="1">
+    <row r="169" spans="1:26" ht="24.95" customHeight="1">
       <c r="A169" s="28"/>
       <c r="B169" s="25"/>
       <c r="C169" s="25"/>
@@ -30895,7 +31076,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170" spans="1:26" ht="25" customHeight="1">
+    <row r="170" spans="1:26" ht="24.95" customHeight="1">
       <c r="A170" s="29"/>
       <c r="B170" s="17"/>
       <c r="C170" s="17"/>
@@ -30923,7 +31104,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171" spans="1:26" ht="25" customHeight="1">
+    <row r="171" spans="1:26" ht="24.95" customHeight="1">
       <c r="A171" s="28"/>
       <c r="B171" s="25"/>
       <c r="C171" s="25"/>
@@ -30951,7 +31132,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172" spans="1:26" ht="25" customHeight="1">
+    <row r="172" spans="1:26" ht="24.95" customHeight="1">
       <c r="A172" s="29"/>
       <c r="B172" s="17"/>
       <c r="C172" s="17"/>
@@ -30979,7 +31160,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173" spans="1:26" ht="25" customHeight="1">
+    <row r="173" spans="1:26" ht="24.95" customHeight="1">
       <c r="A173" s="28"/>
       <c r="B173" s="25"/>
       <c r="C173" s="25"/>
@@ -31007,7 +31188,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174" spans="1:26" ht="25" customHeight="1">
+    <row r="174" spans="1:26" ht="24.95" customHeight="1">
       <c r="A174" s="29"/>
       <c r="B174" s="17"/>
       <c r="C174" s="17"/>
@@ -31035,7 +31216,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175" spans="1:26" ht="25" customHeight="1">
+    <row r="175" spans="1:26" ht="24.95" customHeight="1">
       <c r="A175" s="28"/>
       <c r="B175" s="25"/>
       <c r="C175" s="25"/>
@@ -31063,7 +31244,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176" spans="1:26" ht="25" customHeight="1">
+    <row r="176" spans="1:26" ht="24.95" customHeight="1">
       <c r="A176" s="29"/>
       <c r="B176" s="17"/>
       <c r="C176" s="17"/>
@@ -31091,7 +31272,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177" spans="1:26" ht="25" customHeight="1">
+    <row r="177" spans="1:26" ht="24.95" customHeight="1">
       <c r="A177" s="28"/>
       <c r="B177" s="25"/>
       <c r="C177" s="25"/>
@@ -31119,7 +31300,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178" spans="1:26" ht="25" customHeight="1">
+    <row r="178" spans="1:26" ht="24.95" customHeight="1">
       <c r="A178" s="29"/>
       <c r="B178" s="17"/>
       <c r="C178" s="17"/>
@@ -31147,7 +31328,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179" spans="1:26" ht="25" customHeight="1">
+    <row r="179" spans="1:26" ht="24.95" customHeight="1">
       <c r="A179" s="28"/>
       <c r="B179" s="25"/>
       <c r="C179" s="25"/>
@@ -31175,7 +31356,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180" spans="1:26" ht="25" customHeight="1">
+    <row r="180" spans="1:26" ht="24.95" customHeight="1">
       <c r="A180" s="29"/>
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
@@ -31203,7 +31384,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181" spans="1:26" ht="25" customHeight="1">
+    <row r="181" spans="1:26" ht="24.95" customHeight="1">
       <c r="A181" s="28"/>
       <c r="B181" s="25"/>
       <c r="C181" s="25"/>
@@ -31231,7 +31412,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182" spans="1:26" ht="25" customHeight="1">
+    <row r="182" spans="1:26" ht="24.95" customHeight="1">
       <c r="A182" s="29"/>
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
@@ -31259,7 +31440,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183" spans="1:26" ht="25" customHeight="1">
+    <row r="183" spans="1:26" ht="24.95" customHeight="1">
       <c r="A183" s="28"/>
       <c r="B183" s="25"/>
       <c r="C183" s="25"/>
@@ -31287,7 +31468,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184" spans="1:26" ht="25" customHeight="1">
+    <row r="184" spans="1:26" ht="24.95" customHeight="1">
       <c r="A184" s="29"/>
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
@@ -31315,7 +31496,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185" spans="1:26" ht="25" customHeight="1">
+    <row r="185" spans="1:26" ht="24.95" customHeight="1">
       <c r="A185" s="28"/>
       <c r="B185" s="25"/>
       <c r="C185" s="25"/>
@@ -31343,7 +31524,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186" spans="1:26" ht="25" customHeight="1">
+    <row r="186" spans="1:26" ht="24.95" customHeight="1">
       <c r="A186" s="29"/>
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
@@ -31371,7 +31552,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187" spans="1:26" ht="25" customHeight="1">
+    <row r="187" spans="1:26" ht="24.95" customHeight="1">
       <c r="A187" s="28"/>
       <c r="B187" s="25"/>
       <c r="C187" s="25"/>
@@ -31399,7 +31580,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188" spans="1:26" ht="25" customHeight="1">
+    <row r="188" spans="1:26" ht="24.95" customHeight="1">
       <c r="A188" s="29"/>
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
@@ -31427,7 +31608,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189" spans="1:26" ht="25" customHeight="1">
+    <row r="189" spans="1:26" ht="24.95" customHeight="1">
       <c r="A189" s="28"/>
       <c r="B189" s="25"/>
       <c r="C189" s="25"/>
@@ -31455,7 +31636,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190" spans="1:26" ht="25" customHeight="1">
+    <row r="190" spans="1:26" ht="24.95" customHeight="1">
       <c r="A190" s="29"/>
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
@@ -31483,7 +31664,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191" spans="1:26" ht="25" customHeight="1">
+    <row r="191" spans="1:26" ht="24.95" customHeight="1">
       <c r="A191" s="28"/>
       <c r="B191" s="25"/>
       <c r="C191" s="25"/>
@@ -31511,7 +31692,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192" spans="1:26" ht="25" customHeight="1">
+    <row r="192" spans="1:26" ht="24.95" customHeight="1">
       <c r="A192" s="29"/>
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
@@ -31539,7 +31720,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193" spans="1:26" ht="25" customHeight="1">
+    <row r="193" spans="1:26" ht="24.95" customHeight="1">
       <c r="A193" s="28"/>
       <c r="B193" s="25"/>
       <c r="C193" s="25"/>
@@ -31567,7 +31748,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194" spans="1:26" ht="25" customHeight="1">
+    <row r="194" spans="1:26" ht="24.95" customHeight="1">
       <c r="A194" s="29"/>
       <c r="B194" s="17"/>
       <c r="C194" s="17"/>
@@ -31595,7 +31776,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195" spans="1:26" ht="25" customHeight="1">
+    <row r="195" spans="1:26" ht="24.95" customHeight="1">
       <c r="A195" s="28"/>
       <c r="B195" s="25"/>
       <c r="C195" s="25"/>
@@ -31623,7 +31804,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196" spans="1:26" ht="25" customHeight="1">
+    <row r="196" spans="1:26" ht="24.95" customHeight="1">
       <c r="A196" s="29"/>
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
@@ -31651,7 +31832,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197" spans="1:26" ht="25" customHeight="1">
+    <row r="197" spans="1:26" ht="24.95" customHeight="1">
       <c r="A197" s="28"/>
       <c r="B197" s="25"/>
       <c r="C197" s="25"/>
@@ -31679,7 +31860,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198" spans="1:26" ht="25" customHeight="1">
+    <row r="198" spans="1:26" ht="24.95" customHeight="1">
       <c r="A198" s="29"/>
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
@@ -31707,7 +31888,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199" spans="1:26" ht="25" customHeight="1">
+    <row r="199" spans="1:26" ht="24.95" customHeight="1">
       <c r="A199" s="28"/>
       <c r="B199" s="25"/>
       <c r="C199" s="25"/>
@@ -31735,7 +31916,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200" spans="1:26" ht="25" customHeight="1">
+    <row r="200" spans="1:26" ht="24.95" customHeight="1">
       <c r="A200" s="29"/>
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
@@ -31763,7 +31944,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201" spans="1:26" ht="25" customHeight="1">
+    <row r="201" spans="1:26" ht="24.95" customHeight="1">
       <c r="A201" s="28"/>
       <c r="B201" s="25"/>
       <c r="C201" s="25"/>
@@ -31791,7 +31972,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202" spans="1:26" ht="25" customHeight="1">
+    <row r="202" spans="1:26" ht="24.95" customHeight="1">
       <c r="A202" s="29"/>
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
@@ -31819,7 +32000,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203" spans="1:26" ht="25" customHeight="1">
+    <row r="203" spans="1:26" ht="24.95" customHeight="1">
       <c r="A203" s="28"/>
       <c r="B203" s="25"/>
       <c r="C203" s="25"/>
@@ -31847,7 +32028,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204" spans="1:26" ht="25" customHeight="1">
+    <row r="204" spans="1:26" ht="24.95" customHeight="1">
       <c r="A204" s="30"/>
       <c r="B204" s="20"/>
       <c r="C204" s="20"/>
@@ -33181,10 +33362,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G204">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>G5="Strong"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>G5="Needs Revision"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33230,7 +33411,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
@@ -33238,7 +33419,7 @@
     <col min="7" max="10" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:10" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>109</v>
       </c>
@@ -33266,7 +33447,7 @@
       <c r="I2" s="61"/>
       <c r="J2" s="62"/>
     </row>
-    <row r="3" spans="1:10" ht="25" customHeight="1">
+    <row r="3" spans="1:10" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -33278,7 +33459,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:10" ht="38.049999999999997" customHeight="1">
+    <row r="4" spans="1:10" ht="38.1" customHeight="1">
       <c r="A4" s="23" t="s">
         <v>111</v>
       </c>
@@ -33310,7 +33491,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="64" customHeight="1">
+    <row r="5" spans="1:10" ht="63.95" customHeight="1">
       <c r="A5" s="33" t="s">
         <v>47</v>
       </c>
@@ -33340,7 +33521,7 @@
       </c>
       <c r="J5" s="27"/>
     </row>
-    <row r="6" spans="1:10" ht="64" customHeight="1">
+    <row r="6" spans="1:10" ht="63.95" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>47</v>
       </c>
@@ -33370,7 +33551,7 @@
       </c>
       <c r="J6" s="19"/>
     </row>
-    <row r="7" spans="1:10" ht="64" customHeight="1">
+    <row r="7" spans="1:10" ht="63.95" customHeight="1">
       <c r="A7" s="33" t="s">
         <v>47</v>
       </c>
@@ -33400,7 +33581,7 @@
       </c>
       <c r="J7" s="27"/>
     </row>
-    <row r="8" spans="1:10" ht="64" customHeight="1">
+    <row r="8" spans="1:10" ht="63.95" customHeight="1">
       <c r="A8" s="31" t="s">
         <v>47</v>
       </c>
@@ -33430,7 +33611,7 @@
       </c>
       <c r="J8" s="19"/>
     </row>
-    <row r="9" spans="1:10" ht="64" customHeight="1">
+    <row r="9" spans="1:10" ht="63.95" customHeight="1">
       <c r="A9" s="33" t="s">
         <v>47</v>
       </c>
@@ -33460,7 +33641,7 @@
       </c>
       <c r="J9" s="27"/>
     </row>
-    <row r="10" spans="1:10" ht="64" customHeight="1">
+    <row r="10" spans="1:10" ht="63.95" customHeight="1">
       <c r="A10" s="31" t="s">
         <v>47</v>
       </c>
@@ -33490,7 +33671,7 @@
       </c>
       <c r="J10" s="19"/>
     </row>
-    <row r="11" spans="1:10" ht="64" customHeight="1">
+    <row r="11" spans="1:10" ht="63.95" customHeight="1">
       <c r="A11" s="33" t="s">
         <v>33</v>
       </c>
@@ -33520,7 +33701,7 @@
       </c>
       <c r="J11" s="27"/>
     </row>
-    <row r="12" spans="1:10" ht="64" customHeight="1">
+    <row r="12" spans="1:10" ht="63.95" customHeight="1">
       <c r="A12" s="31" t="s">
         <v>33</v>
       </c>
@@ -33550,7 +33731,7 @@
       </c>
       <c r="J12" s="19"/>
     </row>
-    <row r="13" spans="1:10" ht="64" customHeight="1">
+    <row r="13" spans="1:10" ht="63.95" customHeight="1">
       <c r="A13" s="33" t="s">
         <v>33</v>
       </c>
@@ -33580,7 +33761,7 @@
       </c>
       <c r="J13" s="27"/>
     </row>
-    <row r="14" spans="1:10" ht="64" customHeight="1">
+    <row r="14" spans="1:10" ht="63.95" customHeight="1">
       <c r="A14" s="31" t="s">
         <v>33</v>
       </c>
@@ -33610,7 +33791,7 @@
       </c>
       <c r="J14" s="19"/>
     </row>
-    <row r="15" spans="1:10" ht="64" customHeight="1">
+    <row r="15" spans="1:10" ht="63.95" customHeight="1">
       <c r="A15" s="33" t="s">
         <v>33</v>
       </c>
@@ -33640,7 +33821,7 @@
       </c>
       <c r="J15" s="27"/>
     </row>
-    <row r="16" spans="1:10" ht="64" customHeight="1">
+    <row r="16" spans="1:10" ht="63.95" customHeight="1">
       <c r="A16" s="32" t="s">
         <v>33</v>
       </c>
@@ -33688,7 +33869,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="4" width="30" customWidth="1"/>
@@ -33696,7 +33877,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="38.049999999999997" customHeight="1">
+    <row r="1" spans="1:26" ht="38.1" customHeight="1">
       <c r="A1" s="57" t="s">
         <v>176</v>
       </c>
@@ -33722,7 +33903,7 @@
       <c r="H2" s="61"/>
       <c r="I2" s="62"/>
     </row>
-    <row r="3" spans="1:26" ht="25" customHeight="1">
+    <row r="3" spans="1:26" ht="24.95" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -33733,7 +33914,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="14.1">
+    <row r="4" spans="1:26" ht="15">
       <c r="A4" s="23" t="s">
         <v>178</v>
       </c>
@@ -33779,7 +33960,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:26" ht="44.05" customHeight="1">
+    <row r="5" spans="1:26" ht="44.1" customHeight="1">
       <c r="A5" s="28"/>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -33807,7 +33988,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6" spans="1:26" ht="44.05" customHeight="1">
+    <row r="6" spans="1:26" ht="44.1" customHeight="1">
       <c r="A6" s="29"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -33835,7 +34016,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7" spans="1:26" ht="44.05" customHeight="1">
+    <row r="7" spans="1:26" ht="44.1" customHeight="1">
       <c r="A7" s="28"/>
       <c r="B7" s="25"/>
       <c r="C7" s="25"/>
@@ -33863,7 +34044,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="25" customHeight="1">
+    <row r="8" spans="1:26" ht="24.95" customHeight="1">
       <c r="A8" s="29"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -33891,7 +34072,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="25" customHeight="1">
+    <row r="9" spans="1:26" ht="24.95" customHeight="1">
       <c r="A9" s="28"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -33919,7 +34100,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="25" customHeight="1">
+    <row r="10" spans="1:26" ht="24.95" customHeight="1">
       <c r="A10" s="29"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -33947,7 +34128,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="25" customHeight="1">
+    <row r="11" spans="1:26" ht="24.95" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -33975,7 +34156,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="25" customHeight="1">
+    <row r="12" spans="1:26" ht="24.95" customHeight="1">
       <c r="A12" s="29"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -34003,7 +34184,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="25" customHeight="1">
+    <row r="13" spans="1:26" ht="24.95" customHeight="1">
       <c r="A13" s="28"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -34031,7 +34212,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="25" customHeight="1">
+    <row r="14" spans="1:26" ht="24.95" customHeight="1">
       <c r="A14" s="29"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -34059,7 +34240,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="25" customHeight="1">
+    <row r="15" spans="1:26" ht="24.95" customHeight="1">
       <c r="A15" s="28"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -34087,7 +34268,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="25" customHeight="1">
+    <row r="16" spans="1:26" ht="24.95" customHeight="1">
       <c r="A16" s="29"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -34115,7 +34296,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="25" customHeight="1">
+    <row r="17" spans="1:26" ht="24.95" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -34143,7 +34324,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="25" customHeight="1">
+    <row r="18" spans="1:26" ht="24.95" customHeight="1">
       <c r="A18" s="29"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -34171,7 +34352,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="25" customHeight="1">
+    <row r="19" spans="1:26" ht="24.95" customHeight="1">
       <c r="A19" s="28"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -34199,7 +34380,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="25" customHeight="1">
+    <row r="20" spans="1:26" ht="24.95" customHeight="1">
       <c r="A20" s="29"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -34227,7 +34408,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="25" customHeight="1">
+    <row r="21" spans="1:26" ht="24.95" customHeight="1">
       <c r="A21" s="28"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -34255,7 +34436,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="25" customHeight="1">
+    <row r="22" spans="1:26" ht="24.95" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -34283,7 +34464,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="25" customHeight="1">
+    <row r="23" spans="1:26" ht="24.95" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -34311,7 +34492,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="25" customHeight="1">
+    <row r="24" spans="1:26" ht="24.95" customHeight="1">
       <c r="A24" s="29"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -34339,7 +34520,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="25" customHeight="1">
+    <row r="25" spans="1:26" ht="24.95" customHeight="1">
       <c r="A25" s="28"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -34367,7 +34548,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="25" customHeight="1">
+    <row r="26" spans="1:26" ht="24.95" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -34395,7 +34576,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="25" customHeight="1">
+    <row r="27" spans="1:26" ht="24.95" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -34423,7 +34604,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="25" customHeight="1">
+    <row r="28" spans="1:26" ht="24.95" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -34451,7 +34632,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="25" customHeight="1">
+    <row r="29" spans="1:26" ht="24.95" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -34479,7 +34660,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="25" customHeight="1">
+    <row r="30" spans="1:26" ht="24.95" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -34507,7 +34688,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="25" customHeight="1">
+    <row r="31" spans="1:26" ht="24.95" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -34535,7 +34716,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="25" customHeight="1">
+    <row r="32" spans="1:26" ht="24.95" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -34563,7 +34744,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="25" customHeight="1">
+    <row r="33" spans="1:26" ht="24.95" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -34591,7 +34772,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="25" customHeight="1">
+    <row r="34" spans="1:26" ht="24.95" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -34619,7 +34800,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="25" customHeight="1">
+    <row r="35" spans="1:26" ht="24.95" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -34647,7 +34828,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="25" customHeight="1">
+    <row r="36" spans="1:26" ht="24.95" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -34675,7 +34856,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="25" customHeight="1">
+    <row r="37" spans="1:26" ht="24.95" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -34703,7 +34884,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="25" customHeight="1">
+    <row r="38" spans="1:26" ht="24.95" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -34731,7 +34912,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="25" customHeight="1">
+    <row r="39" spans="1:26" ht="24.95" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -34759,7 +34940,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="25" customHeight="1">
+    <row r="40" spans="1:26" ht="24.95" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -34787,7 +34968,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="25" customHeight="1">
+    <row r="41" spans="1:26" ht="24.95" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -34815,7 +34996,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="25" customHeight="1">
+    <row r="42" spans="1:26" ht="24.95" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -34843,7 +35024,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="25" customHeight="1">
+    <row r="43" spans="1:26" ht="24.95" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -34871,7 +35052,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="25" customHeight="1">
+    <row r="44" spans="1:26" ht="24.95" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -34899,7 +35080,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="25" customHeight="1">
+    <row r="45" spans="1:26" ht="24.95" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -34927,7 +35108,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="25" customHeight="1">
+    <row r="46" spans="1:26" ht="24.95" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -34955,7 +35136,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="25" customHeight="1">
+    <row r="47" spans="1:26" ht="24.95" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -34983,7 +35164,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="25" customHeight="1">
+    <row r="48" spans="1:26" ht="24.95" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -35011,7 +35192,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="25" customHeight="1">
+    <row r="49" spans="1:26" ht="24.95" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -35039,7 +35220,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="25" customHeight="1">
+    <row r="50" spans="1:26" ht="24.95" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -35067,7 +35248,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="25" customHeight="1">
+    <row r="51" spans="1:26" ht="24.95" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -35095,7 +35276,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="25" customHeight="1">
+    <row r="52" spans="1:26" ht="24.95" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -35123,7 +35304,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="25" customHeight="1">
+    <row r="53" spans="1:26" ht="24.95" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -35151,7 +35332,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="25" customHeight="1">
+    <row r="54" spans="1:26" ht="24.95" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -35179,7 +35360,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="25" customHeight="1">
+    <row r="55" spans="1:26" ht="24.95" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -35207,7 +35388,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="25" customHeight="1">
+    <row r="56" spans="1:26" ht="24.95" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -35235,7 +35416,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="25" customHeight="1">
+    <row r="57" spans="1:26" ht="24.95" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -35263,7 +35444,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="25" customHeight="1">
+    <row r="58" spans="1:26" ht="24.95" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -35291,7 +35472,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="25" customHeight="1">
+    <row r="59" spans="1:26" ht="24.95" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -35319,7 +35500,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="25" customHeight="1">
+    <row r="60" spans="1:26" ht="24.95" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -35347,7 +35528,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="25" customHeight="1">
+    <row r="61" spans="1:26" ht="24.95" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -35375,7 +35556,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="25" customHeight="1">
+    <row r="62" spans="1:26" ht="24.95" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -35403,7 +35584,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="25" customHeight="1">
+    <row r="63" spans="1:26" ht="24.95" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -35431,7 +35612,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="25" customHeight="1">
+    <row r="64" spans="1:26" ht="24.95" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -35459,7 +35640,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="25" customHeight="1">
+    <row r="65" spans="1:26" ht="24.95" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -35487,7 +35668,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="25" customHeight="1">
+    <row r="66" spans="1:26" ht="24.95" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -35515,7 +35696,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="25" customHeight="1">
+    <row r="67" spans="1:26" ht="24.95" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -35543,7 +35724,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="25" customHeight="1">
+    <row r="68" spans="1:26" ht="24.95" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -35571,7 +35752,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="25" customHeight="1">
+    <row r="69" spans="1:26" ht="24.95" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -35599,7 +35780,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="25" customHeight="1">
+    <row r="70" spans="1:26" ht="24.95" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -35627,7 +35808,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="25" customHeight="1">
+    <row r="71" spans="1:26" ht="24.95" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -35655,7 +35836,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="25" customHeight="1">
+    <row r="72" spans="1:26" ht="24.95" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -35683,7 +35864,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="25" customHeight="1">
+    <row r="73" spans="1:26" ht="24.95" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -35711,7 +35892,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="25" customHeight="1">
+    <row r="74" spans="1:26" ht="24.95" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -35739,7 +35920,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="25" customHeight="1">
+    <row r="75" spans="1:26" ht="24.95" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -35767,7 +35948,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="25" customHeight="1">
+    <row r="76" spans="1:26" ht="24.95" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -35795,7 +35976,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="25" customHeight="1">
+    <row r="77" spans="1:26" ht="24.95" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -35823,7 +36004,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="25" customHeight="1">
+    <row r="78" spans="1:26" ht="24.95" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -35851,7 +36032,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="25" customHeight="1">
+    <row r="79" spans="1:26" ht="24.95" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -35879,7 +36060,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="25" customHeight="1">
+    <row r="80" spans="1:26" ht="24.95" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -35907,7 +36088,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="25" customHeight="1">
+    <row r="81" spans="1:26" ht="24.95" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -35935,7 +36116,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="25" customHeight="1">
+    <row r="82" spans="1:26" ht="24.95" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -35963,7 +36144,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="25" customHeight="1">
+    <row r="83" spans="1:26" ht="24.95" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -35991,7 +36172,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="25" customHeight="1">
+    <row r="84" spans="1:26" ht="24.95" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -36019,7 +36200,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="25" customHeight="1">
+    <row r="85" spans="1:26" ht="24.95" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -36047,7 +36228,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="25" customHeight="1">
+    <row r="86" spans="1:26" ht="24.95" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -36075,7 +36256,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="25" customHeight="1">
+    <row r="87" spans="1:26" ht="24.95" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -36103,7 +36284,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="25" customHeight="1">
+    <row r="88" spans="1:26" ht="24.95" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -36131,7 +36312,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="25" customHeight="1">
+    <row r="89" spans="1:26" ht="24.95" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -36159,7 +36340,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="25" customHeight="1">
+    <row r="90" spans="1:26" ht="24.95" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -36187,7 +36368,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="25" customHeight="1">
+    <row r="91" spans="1:26" ht="24.95" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -36215,7 +36396,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="25" customHeight="1">
+    <row r="92" spans="1:26" ht="24.95" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -36243,7 +36424,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="25" customHeight="1">
+    <row r="93" spans="1:26" ht="24.95" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -36271,7 +36452,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="25" customHeight="1">
+    <row r="94" spans="1:26" ht="24.95" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -36299,7 +36480,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="25" customHeight="1">
+    <row r="95" spans="1:26" ht="24.95" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -36327,7 +36508,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="25" customHeight="1">
+    <row r="96" spans="1:26" ht="24.95" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -36355,7 +36536,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="25" customHeight="1">
+    <row r="97" spans="1:26" ht="24.95" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -36383,7 +36564,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="25" customHeight="1">
+    <row r="98" spans="1:26" ht="24.95" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -36411,7 +36592,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="25" customHeight="1">
+    <row r="99" spans="1:26" ht="24.95" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -36439,7 +36620,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="25" customHeight="1">
+    <row r="100" spans="1:26" ht="24.95" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -36467,7 +36648,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="25" customHeight="1">
+    <row r="101" spans="1:26" ht="24.95" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -36495,7 +36676,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="25" customHeight="1">
+    <row r="102" spans="1:26" ht="24.95" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -36523,7 +36704,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="25" customHeight="1">
+    <row r="103" spans="1:26" ht="24.95" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -36551,7 +36732,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="25" customHeight="1">
+    <row r="104" spans="1:26" ht="24.95" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -40673,13 +40854,13 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F104">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>F5="Completed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>F5="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>F5="Needs Revision"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/assets/deen/madrasa/class_manager.xlsx
+++ b/assets/deen/madrasa/class_manager.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SehhaDeveloper\src\l3\edu-journey\assets\deen\madrasa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23762FD4-9A74-4314-BEC6-78D28EF31F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0084AB57-9EAE-46E7-B5D2-804713402EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="215">
   <si>
     <t>Madrasa Class Dashboard</t>
   </si>
@@ -1043,6 +1043,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1073,23 +1082,11 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1178,6 +1175,9 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1260,10 +1260,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.51428571428571435</c:v>
+                  <c:v>0.57500000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.42857142857142855</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.79999999999999993</c:v>
@@ -1322,13 +1322,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>0.8571428571428571</c:v>
+                  <c:v>0.875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.7142857142857143</c:v>
+                  <c:v>0.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8571428571428571</c:v>
+                  <c:v>0.875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1553,7 +1553,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.51428571428571435</c:v>
+                  <c:v>0.57500000000000007</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -1830,7 +1830,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ProgressTable" displayName="ProgressTable" ref="A4:I204" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="ProgressTable" displayName="ProgressTable" ref="A4:I204" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A4:I204" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Date"/>
@@ -2098,52 +2098,52 @@
     <tabColor rgb="FF356BA2"/>
   </sheetPr>
   <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.234375" bestFit="1" customWidth="1"/>
     <col min="5" max="14" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="62"/>
     </row>
     <row r="2" spans="1:14" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>197</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="62"/>
-    </row>
-    <row r="3" spans="1:14" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="65"/>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2159,7 +2159,7 @@
       <c r="M3" s="3"/>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="25.5">
+    <row r="4" spans="1:14" ht="24.6">
       <c r="A4" s="48" t="s">
         <v>1</v>
       </c>
@@ -2191,13 +2191,13 @@
       <c r="M4" s="46"/>
       <c r="N4" s="47"/>
     </row>
-    <row r="5" spans="1:14" ht="26.25">
+    <row r="5" spans="1:14" ht="25.2">
       <c r="A5" s="2"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="51">
         <f>IF(COUNTIF(AttendanceTable[Student],$B$4)=0,"",(COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],$B$4))</f>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="E5" s="51" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],$B$4)=0,"",COUNTIFS(HomeworkTable[Student],$B$4,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],$B$4))</f>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="F5" s="51">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],$B$4,ProgressTable[Mastery %]))</f>
-        <v>0.51428571428571435</v>
+        <v>0.57500000000000007</v>
       </c>
       <c r="G5" s="51" t="str">
         <f>IF(COUNTIFS(AssessmentTable[Student],$B$4,AssessmentTable[Percentage],"&lt;&gt;")=0,"",AVERAGEIF(AssessmentTable[Student],$B$4,AssessmentTable[Percentage]))</f>
@@ -2213,11 +2213,11 @@
       </c>
       <c r="H5" s="52">
         <f>COUNTIF(AttendanceTable[Student],$B$4)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="52">
         <f>COUNTIF(ProgressTable[Student],$B$4)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -2225,7 +2225,7 @@
       <c r="M5" s="3"/>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" ht="15">
+    <row r="6" spans="1:14" ht="14.1">
       <c r="A6" s="15" t="s">
         <v>8</v>
       </c>
@@ -2246,7 +2246,7 @@
       <c r="M6" s="3"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="15">
+    <row r="7" spans="1:14" ht="14.1">
       <c r="A7" s="15" t="s">
         <v>9</v>
       </c>
@@ -2255,21 +2255,21 @@
         <v>11</v>
       </c>
       <c r="C7" s="3"/>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="66" t="s">
         <v>198</v>
       </c>
-      <c r="E7" s="63"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="15">
+    <row r="8" spans="1:14" ht="14.1">
       <c r="A8" s="15" t="s">
         <v>10</v>
       </c>
@@ -2290,7 +2290,7 @@
       <c r="M8" s="3"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" ht="24.95" customHeight="1">
+    <row r="9" spans="1:14" ht="25" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -2306,7 +2306,7 @@
       <c r="M9" s="3"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="24.95" customHeight="1">
+    <row r="10" spans="1:14" ht="25" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -2322,14 +2322,14 @@
       <c r="M10" s="3"/>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A11" s="64" t="s">
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="67" t="s">
         <v>199</v>
       </c>
-      <c r="B11" s="65"/>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -2340,7 +2340,7 @@
       <c r="M11" s="3"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="15">
+    <row r="12" spans="1:14" ht="14.1">
       <c r="A12" s="23" t="s">
         <v>8</v>
       </c>
@@ -2373,11 +2373,11 @@
       </c>
       <c r="B13" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A13,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A13,ProgressTable[Mastery %]))</f>
-        <v>0.51428571428571435</v>
+        <v>0.57500000000000007</v>
       </c>
       <c r="C13" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A13)=0,"",(COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A13,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A13))</f>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="D13" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A13)=0,"",COUNTIFS(HomeworkTable[Student],A13,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A13))</f>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="B14" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],A14,ProgressTable[Mastery %],"&lt;&gt;")=0,"",AVERAGEIF(ProgressTable[Student],A14,ProgressTable[Mastery %]))</f>
-        <v>0.42857142857142855</v>
+        <v>0.5</v>
       </c>
       <c r="C14" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A14)=0,"",(COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A14,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A14))</f>
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="D14" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A14)=0,"",COUNTIFS(HomeworkTable[Student],A14,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A14))</f>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C15" s="5">
         <f>IF(COUNTIF(AttendanceTable[Student],A15)=0,"",(COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Present")+COUNTIFS(AttendanceTable[Student],A15,AttendanceTable[Status],"Late"))/COUNTIF(AttendanceTable[Student],A15))</f>
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="D15" s="5" t="str">
         <f>IF(COUNTIF(HomeworkTable[Student],A15)=0,"",COUNTIFS(HomeworkTable[Student],A15,HomeworkTable[Status],"Completed")/COUNTIF(HomeworkTable[Student],A15))</f>
@@ -2459,7 +2459,7 @@
       <c r="M15" s="3"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="24.95" customHeight="1">
+    <row r="16" spans="1:14" ht="25" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -2475,7 +2475,7 @@
       <c r="M16" s="3"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="24.95" customHeight="1">
+    <row r="17" spans="1:14" ht="25" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -2491,7 +2491,7 @@
       <c r="M17" s="3"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="24.95" customHeight="1">
+    <row r="18" spans="1:14" ht="25" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -2507,7 +2507,7 @@
       <c r="M18" s="3"/>
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="1:14" ht="15">
+    <row r="19" spans="1:14" ht="14.1">
       <c r="A19" s="23" t="s">
         <v>200</v>
       </c>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B20" s="5">
         <f>IF(COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;")=0,"",SUMIFS(ProgressTable[Mastery %],ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20)/COUNTIFS(ProgressTable[Student],$B$4,ProgressTable[Topic Area],A20,ProgressTable[Mastery %],"&lt;&gt;"))</f>
-        <v>0.51428571428571435</v>
+        <v>0.57500000000000007</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="53" t="s">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="E20" s="3">
         <f>COUNTIFS(AttendanceTable[Student],$B$4,AttendanceTable[Status],D20)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2757,13 +2757,13 @@
       <c r="N29" s="4"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="66" t="s">
+      <c r="A30" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="B30" s="63"/>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
@@ -2775,11 +2775,11 @@
       <c r="N30" s="4"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="66"/>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
+      <c r="A31" s="69"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="66"/>
+      <c r="E31" s="66"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
@@ -2790,7 +2790,7 @@
       <c r="M31" s="3"/>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="1:14" ht="24.95" customHeight="1">
+    <row r="32" spans="1:14" ht="25" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2806,7 +2806,7 @@
       <c r="M32" s="3"/>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="1:14" ht="24.95" customHeight="1">
+    <row r="33" spans="1:14" ht="25" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2822,7 +2822,7 @@
       <c r="M33" s="3"/>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="1:14" ht="24.95" customHeight="1">
+    <row r="34" spans="1:14" ht="25" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2838,7 +2838,7 @@
       <c r="M34" s="3"/>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="1:14" ht="24.95" customHeight="1">
+    <row r="35" spans="1:14" ht="25" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2854,7 +2854,7 @@
       <c r="M35" s="3"/>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:14" ht="24.95" customHeight="1">
+    <row r="36" spans="1:14" ht="25" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2870,7 +2870,7 @@
       <c r="M36" s="3"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="1:14" ht="24.95" customHeight="1">
+    <row r="37" spans="1:14" ht="25" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2886,7 +2886,7 @@
       <c r="M37" s="3"/>
       <c r="N37" s="4"/>
     </row>
-    <row r="38" spans="1:14" ht="24.95" customHeight="1">
+    <row r="38" spans="1:14" ht="25" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2902,7 +2902,7 @@
       <c r="M38" s="3"/>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="1:14" ht="24.95" customHeight="1">
+    <row r="39" spans="1:14" ht="25" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2918,7 +2918,7 @@
       <c r="M39" s="3"/>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="1:14" ht="24.95" customHeight="1">
+    <row r="40" spans="1:14" ht="25" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2934,7 +2934,7 @@
       <c r="M40" s="3"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="1:14" ht="24.95" customHeight="1">
+    <row r="41" spans="1:14" ht="25" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2950,7 +2950,7 @@
       <c r="M41" s="3"/>
       <c r="N41" s="4"/>
     </row>
-    <row r="42" spans="1:14" ht="24.95" customHeight="1">
+    <row r="42" spans="1:14" ht="25" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2966,7 +2966,7 @@
       <c r="M42" s="3"/>
       <c r="N42" s="4"/>
     </row>
-    <row r="43" spans="1:14" ht="24.95" customHeight="1">
+    <row r="43" spans="1:14" ht="25" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2982,7 +2982,7 @@
       <c r="M43" s="3"/>
       <c r="N43" s="4"/>
     </row>
-    <row r="44" spans="1:14" ht="24.95" customHeight="1">
+    <row r="44" spans="1:14" ht="25" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2998,7 +2998,7 @@
       <c r="M44" s="3"/>
       <c r="N44" s="4"/>
     </row>
-    <row r="45" spans="1:14" ht="24.95" customHeight="1">
+    <row r="45" spans="1:14" ht="25" customHeight="1">
       <c r="A45" s="6"/>
       <c r="B45" s="7"/>
       <c r="C45" s="7"/>
@@ -3023,7 +3023,7 @@
     <mergeCell ref="A30:E31"/>
   </mergeCells>
   <conditionalFormatting sqref="A13:E15">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$A13=$B$4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3050,39 +3050,39 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="62"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="62"/>
-    </row>
-    <row r="3" spans="1:26" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3093,7 +3093,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="15">
+    <row r="4" spans="1:26" ht="14.1">
       <c r="A4" s="23" t="s">
         <v>26</v>
       </c>
@@ -3241,7 +3241,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="24.95" customHeight="1">
+    <row r="8" spans="1:26" ht="25" customHeight="1">
       <c r="A8" s="29"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -3275,7 +3275,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="24.95" customHeight="1">
+    <row r="9" spans="1:26" ht="25" customHeight="1">
       <c r="A9" s="28"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -3309,7 +3309,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="24.95" customHeight="1">
+    <row r="10" spans="1:26" ht="25" customHeight="1">
       <c r="A10" s="29"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -3343,7 +3343,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="24.95" customHeight="1">
+    <row r="11" spans="1:26" ht="25" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -3377,7 +3377,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="24.95" customHeight="1">
+    <row r="12" spans="1:26" ht="25" customHeight="1">
       <c r="A12" s="29"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -3411,7 +3411,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="24.95" customHeight="1">
+    <row r="13" spans="1:26" ht="25" customHeight="1">
       <c r="A13" s="28"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -3445,7 +3445,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="24.95" customHeight="1">
+    <row r="14" spans="1:26" ht="25" customHeight="1">
       <c r="A14" s="29"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -3479,7 +3479,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="24.95" customHeight="1">
+    <row r="15" spans="1:26" ht="25" customHeight="1">
       <c r="A15" s="28"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -3513,7 +3513,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="24.95" customHeight="1">
+    <row r="16" spans="1:26" ht="25" customHeight="1">
       <c r="A16" s="29"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -3547,7 +3547,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="24.95" customHeight="1">
+    <row r="17" spans="1:26" ht="25" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -3581,7 +3581,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="24.95" customHeight="1">
+    <row r="18" spans="1:26" ht="25" customHeight="1">
       <c r="A18" s="29"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -3615,7 +3615,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="24.95" customHeight="1">
+    <row r="19" spans="1:26" ht="25" customHeight="1">
       <c r="A19" s="28"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -3649,7 +3649,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="24.95" customHeight="1">
+    <row r="20" spans="1:26" ht="25" customHeight="1">
       <c r="A20" s="29"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -3683,7 +3683,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="24.95" customHeight="1">
+    <row r="21" spans="1:26" ht="25" customHeight="1">
       <c r="A21" s="28"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -3717,7 +3717,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="24.95" customHeight="1">
+    <row r="22" spans="1:26" ht="25" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -3751,7 +3751,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="24.95" customHeight="1">
+    <row r="23" spans="1:26" ht="25" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -3785,7 +3785,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="24.95" customHeight="1">
+    <row r="24" spans="1:26" ht="25" customHeight="1">
       <c r="A24" s="29"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -3819,7 +3819,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="24.95" customHeight="1">
+    <row r="25" spans="1:26" ht="25" customHeight="1">
       <c r="A25" s="28"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -3853,7 +3853,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="24.95" customHeight="1">
+    <row r="26" spans="1:26" ht="25" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -3887,7 +3887,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="24.95" customHeight="1">
+    <row r="27" spans="1:26" ht="25" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -3921,7 +3921,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="24.95" customHeight="1">
+    <row r="28" spans="1:26" ht="25" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -3955,7 +3955,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="24.95" customHeight="1">
+    <row r="29" spans="1:26" ht="25" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -3989,7 +3989,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="24.95" customHeight="1">
+    <row r="30" spans="1:26" ht="25" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -4023,7 +4023,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="24.95" customHeight="1">
+    <row r="31" spans="1:26" ht="25" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -4057,7 +4057,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="24.95" customHeight="1">
+    <row r="32" spans="1:26" ht="25" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -4091,7 +4091,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="24.95" customHeight="1">
+    <row r="33" spans="1:26" ht="25" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -4125,7 +4125,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="24.95" customHeight="1">
+    <row r="34" spans="1:26" ht="25" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -4159,7 +4159,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="24.95" customHeight="1">
+    <row r="35" spans="1:26" ht="25" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -4193,7 +4193,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="24.95" customHeight="1">
+    <row r="36" spans="1:26" ht="25" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -4227,7 +4227,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="24.95" customHeight="1">
+    <row r="37" spans="1:26" ht="25" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -4261,7 +4261,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="24.95" customHeight="1">
+    <row r="38" spans="1:26" ht="25" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -4295,7 +4295,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="24.95" customHeight="1">
+    <row r="39" spans="1:26" ht="25" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -4329,7 +4329,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="24.95" customHeight="1">
+    <row r="40" spans="1:26" ht="25" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -4363,7 +4363,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="24.95" customHeight="1">
+    <row r="41" spans="1:26" ht="25" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -4397,7 +4397,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="24.95" customHeight="1">
+    <row r="42" spans="1:26" ht="25" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -4431,7 +4431,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="24.95" customHeight="1">
+    <row r="43" spans="1:26" ht="25" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -4465,7 +4465,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="24.95" customHeight="1">
+    <row r="44" spans="1:26" ht="25" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -4499,7 +4499,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="24.95" customHeight="1">
+    <row r="45" spans="1:26" ht="25" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -4533,7 +4533,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="24.95" customHeight="1">
+    <row r="46" spans="1:26" ht="25" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -4567,7 +4567,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="24.95" customHeight="1">
+    <row r="47" spans="1:26" ht="25" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -4601,7 +4601,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="24.95" customHeight="1">
+    <row r="48" spans="1:26" ht="25" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -4635,7 +4635,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="24.95" customHeight="1">
+    <row r="49" spans="1:26" ht="25" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -4669,7 +4669,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="24.95" customHeight="1">
+    <row r="50" spans="1:26" ht="25" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -4703,7 +4703,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="24.95" customHeight="1">
+    <row r="51" spans="1:26" ht="25" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -4737,7 +4737,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="24.95" customHeight="1">
+    <row r="52" spans="1:26" ht="25" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -4771,7 +4771,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="24.95" customHeight="1">
+    <row r="53" spans="1:26" ht="25" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -4805,7 +4805,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="24.95" customHeight="1">
+    <row r="54" spans="1:26" ht="25" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -4839,7 +4839,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="24.95" customHeight="1">
+    <row r="55" spans="1:26" ht="25" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -4873,7 +4873,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="24.95" customHeight="1">
+    <row r="56" spans="1:26" ht="25" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -4907,7 +4907,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="24.95" customHeight="1">
+    <row r="57" spans="1:26" ht="25" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -4941,7 +4941,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="24.95" customHeight="1">
+    <row r="58" spans="1:26" ht="25" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -4975,7 +4975,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="24.95" customHeight="1">
+    <row r="59" spans="1:26" ht="25" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -5009,7 +5009,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="24.95" customHeight="1">
+    <row r="60" spans="1:26" ht="25" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -5043,7 +5043,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="24.95" customHeight="1">
+    <row r="61" spans="1:26" ht="25" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -5077,7 +5077,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="24.95" customHeight="1">
+    <row r="62" spans="1:26" ht="25" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -5111,7 +5111,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="24.95" customHeight="1">
+    <row r="63" spans="1:26" ht="25" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -5145,7 +5145,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="24.95" customHeight="1">
+    <row r="64" spans="1:26" ht="25" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -5179,7 +5179,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="24.95" customHeight="1">
+    <row r="65" spans="1:26" ht="25" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -5213,7 +5213,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="24.95" customHeight="1">
+    <row r="66" spans="1:26" ht="25" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -5247,7 +5247,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="24.95" customHeight="1">
+    <row r="67" spans="1:26" ht="25" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -5281,7 +5281,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="24.95" customHeight="1">
+    <row r="68" spans="1:26" ht="25" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -5315,7 +5315,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="24.95" customHeight="1">
+    <row r="69" spans="1:26" ht="25" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -5349,7 +5349,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="24.95" customHeight="1">
+    <row r="70" spans="1:26" ht="25" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -5383,7 +5383,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="24.95" customHeight="1">
+    <row r="71" spans="1:26" ht="25" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -5417,7 +5417,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="24.95" customHeight="1">
+    <row r="72" spans="1:26" ht="25" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -5451,7 +5451,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="24.95" customHeight="1">
+    <row r="73" spans="1:26" ht="25" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -5485,7 +5485,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="24.95" customHeight="1">
+    <row r="74" spans="1:26" ht="25" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -5519,7 +5519,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="24.95" customHeight="1">
+    <row r="75" spans="1:26" ht="25" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -5553,7 +5553,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="24.95" customHeight="1">
+    <row r="76" spans="1:26" ht="25" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -5587,7 +5587,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="24.95" customHeight="1">
+    <row r="77" spans="1:26" ht="25" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -5621,7 +5621,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="24.95" customHeight="1">
+    <row r="78" spans="1:26" ht="25" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -5655,7 +5655,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="24.95" customHeight="1">
+    <row r="79" spans="1:26" ht="25" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -5689,7 +5689,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="24.95" customHeight="1">
+    <row r="80" spans="1:26" ht="25" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -5723,7 +5723,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="24.95" customHeight="1">
+    <row r="81" spans="1:26" ht="25" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -5757,7 +5757,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="24.95" customHeight="1">
+    <row r="82" spans="1:26" ht="25" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -5791,7 +5791,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="24.95" customHeight="1">
+    <row r="83" spans="1:26" ht="25" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -5825,7 +5825,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="24.95" customHeight="1">
+    <row r="84" spans="1:26" ht="25" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -5859,7 +5859,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="24.95" customHeight="1">
+    <row r="85" spans="1:26" ht="25" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -5893,7 +5893,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="24.95" customHeight="1">
+    <row r="86" spans="1:26" ht="25" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -5927,7 +5927,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="24.95" customHeight="1">
+    <row r="87" spans="1:26" ht="25" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -5961,7 +5961,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="24.95" customHeight="1">
+    <row r="88" spans="1:26" ht="25" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -5995,7 +5995,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="24.95" customHeight="1">
+    <row r="89" spans="1:26" ht="25" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -6029,7 +6029,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="24.95" customHeight="1">
+    <row r="90" spans="1:26" ht="25" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -6063,7 +6063,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="24.95" customHeight="1">
+    <row r="91" spans="1:26" ht="25" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -6097,7 +6097,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="24.95" customHeight="1">
+    <row r="92" spans="1:26" ht="25" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -6131,7 +6131,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="24.95" customHeight="1">
+    <row r="93" spans="1:26" ht="25" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -6165,7 +6165,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="24.95" customHeight="1">
+    <row r="94" spans="1:26" ht="25" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -6199,7 +6199,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="24.95" customHeight="1">
+    <row r="95" spans="1:26" ht="25" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -6233,7 +6233,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="24.95" customHeight="1">
+    <row r="96" spans="1:26" ht="25" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -6267,7 +6267,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="24.95" customHeight="1">
+    <row r="97" spans="1:26" ht="25" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -6301,7 +6301,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="24.95" customHeight="1">
+    <row r="98" spans="1:26" ht="25" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -6335,7 +6335,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="24.95" customHeight="1">
+    <row r="99" spans="1:26" ht="25" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -6369,7 +6369,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="24.95" customHeight="1">
+    <row r="100" spans="1:26" ht="25" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -6403,7 +6403,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="24.95" customHeight="1">
+    <row r="101" spans="1:26" ht="25" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -6437,7 +6437,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="24.95" customHeight="1">
+    <row r="102" spans="1:26" ht="25" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -6471,7 +6471,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="24.95" customHeight="1">
+    <row r="103" spans="1:26" ht="25" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -6505,7 +6505,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="24.95" customHeight="1">
+    <row r="104" spans="1:26" ht="25" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -10675,43 +10675,43 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.234375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.76171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.47265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.47265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="62"/>
-    </row>
-    <row r="3" spans="1:26" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -10721,7 +10721,7 @@
       <c r="G3" s="3"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="15">
+    <row r="4" spans="1:26" ht="14.1">
       <c r="A4" s="23" t="s">
         <v>26</v>
       </c>
@@ -11015,7 +11015,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="24.95" customHeight="1">
+    <row r="11" spans="1:26" ht="25" customHeight="1">
       <c r="A11" s="29">
         <v>46278</v>
       </c>
@@ -11055,7 +11055,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="24.95" customHeight="1">
+    <row r="12" spans="1:26" ht="25" customHeight="1">
       <c r="A12" s="29">
         <v>46278</v>
       </c>
@@ -11095,7 +11095,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="24.95" customHeight="1">
+    <row r="13" spans="1:26" ht="25" customHeight="1">
       <c r="A13" s="29">
         <v>46278</v>
       </c>
@@ -11135,7 +11135,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="24.95" customHeight="1">
+    <row r="14" spans="1:26" ht="25" customHeight="1">
       <c r="A14" s="29">
         <v>46284</v>
       </c>
@@ -11175,7 +11175,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="24.95" customHeight="1">
+    <row r="15" spans="1:26" ht="25" customHeight="1">
       <c r="A15" s="28">
         <v>46284</v>
       </c>
@@ -11215,7 +11215,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="24.95" customHeight="1">
+    <row r="16" spans="1:26" ht="25" customHeight="1">
       <c r="A16" s="29">
         <v>46284</v>
       </c>
@@ -11255,7 +11255,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="24.95" customHeight="1">
+    <row r="17" spans="1:26" ht="25" customHeight="1">
       <c r="A17" s="28">
         <v>46285</v>
       </c>
@@ -11295,7 +11295,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="24.95" customHeight="1">
+    <row r="18" spans="1:26" ht="25" customHeight="1">
       <c r="A18" s="29">
         <v>46285</v>
       </c>
@@ -11335,7 +11335,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="24.95" customHeight="1">
+    <row r="19" spans="1:26" ht="25" customHeight="1">
       <c r="A19" s="28">
         <v>46285</v>
       </c>
@@ -11375,7 +11375,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="24.95" customHeight="1">
+    <row r="20" spans="1:26" ht="25" customHeight="1">
       <c r="A20" s="29">
         <v>46291</v>
       </c>
@@ -11413,7 +11413,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="24.95" customHeight="1">
+    <row r="21" spans="1:26" ht="25" customHeight="1">
       <c r="A21" s="28">
         <v>46291</v>
       </c>
@@ -11451,7 +11451,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="24.95" customHeight="1">
+    <row r="22" spans="1:26" ht="25" customHeight="1">
       <c r="A22" s="29">
         <v>46291</v>
       </c>
@@ -11489,7 +11489,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="24.95" customHeight="1">
+    <row r="23" spans="1:26" ht="25" customHeight="1">
       <c r="A23" s="28">
         <v>46292</v>
       </c>
@@ -11529,7 +11529,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="24.95" customHeight="1">
+    <row r="24" spans="1:26" ht="25" customHeight="1">
       <c r="A24" s="29">
         <v>46292</v>
       </c>
@@ -11569,7 +11569,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="24.95" customHeight="1">
+    <row r="25" spans="1:26" ht="25" customHeight="1">
       <c r="A25" s="28">
         <v>46292</v>
       </c>
@@ -11609,14 +11609,26 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="24.95" customHeight="1">
-      <c r="A26" s="29"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="18"/>
+    <row r="26" spans="1:26" ht="25" customHeight="1">
+      <c r="A26" s="29">
+        <v>46312</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="18">
+        <v>0.48680555555555555</v>
+      </c>
       <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+      <c r="G26" s="25" t="s">
+        <v>214</v>
+      </c>
       <c r="H26" s="19"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -11637,14 +11649,26 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="24.95" customHeight="1">
-      <c r="A27" s="28"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="26"/>
+    <row r="27" spans="1:26" ht="25" customHeight="1">
+      <c r="A27" s="28">
+        <v>46312</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="26">
+        <v>0.48680555555555555</v>
+      </c>
       <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
+      <c r="G27" s="25" t="s">
+        <v>214</v>
+      </c>
       <c r="H27" s="27"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -11665,14 +11689,26 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="24.95" customHeight="1">
-      <c r="A28" s="29"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="18"/>
+    <row r="28" spans="1:26" ht="25" customHeight="1">
+      <c r="A28" s="29">
+        <v>46312</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" s="18">
+        <v>0.48680555555555555</v>
+      </c>
       <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+      <c r="G28" s="25" t="s">
+        <v>214</v>
+      </c>
       <c r="H28" s="19"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -11693,7 +11729,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="24.95" customHeight="1">
+    <row r="29" spans="1:26" ht="25" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -11721,7 +11757,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="24.95" customHeight="1">
+    <row r="30" spans="1:26" ht="25" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -11749,7 +11785,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="24.95" customHeight="1">
+    <row r="31" spans="1:26" ht="25" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -11777,7 +11813,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="24.95" customHeight="1">
+    <row r="32" spans="1:26" ht="25" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -11805,7 +11841,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="24.95" customHeight="1">
+    <row r="33" spans="1:26" ht="25" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -11833,7 +11869,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="24.95" customHeight="1">
+    <row r="34" spans="1:26" ht="25" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -11861,7 +11897,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="24.95" customHeight="1">
+    <row r="35" spans="1:26" ht="25" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -11889,7 +11925,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="24.95" customHeight="1">
+    <row r="36" spans="1:26" ht="25" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -11917,7 +11953,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="24.95" customHeight="1">
+    <row r="37" spans="1:26" ht="25" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -11945,7 +11981,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="24.95" customHeight="1">
+    <row r="38" spans="1:26" ht="25" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -11973,7 +12009,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="24.95" customHeight="1">
+    <row r="39" spans="1:26" ht="25" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -12001,7 +12037,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="24.95" customHeight="1">
+    <row r="40" spans="1:26" ht="25" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -12029,7 +12065,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="24.95" customHeight="1">
+    <row r="41" spans="1:26" ht="25" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -12057,7 +12093,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="24.95" customHeight="1">
+    <row r="42" spans="1:26" ht="25" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -12085,7 +12121,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="24.95" customHeight="1">
+    <row r="43" spans="1:26" ht="25" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -12113,7 +12149,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="24.95" customHeight="1">
+    <row r="44" spans="1:26" ht="25" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -12141,7 +12177,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="24.95" customHeight="1">
+    <row r="45" spans="1:26" ht="25" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -12169,7 +12205,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="24.95" customHeight="1">
+    <row r="46" spans="1:26" ht="25" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -12197,7 +12233,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="24.95" customHeight="1">
+    <row r="47" spans="1:26" ht="25" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -12225,7 +12261,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="24.95" customHeight="1">
+    <row r="48" spans="1:26" ht="25" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -12253,7 +12289,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="24.95" customHeight="1">
+    <row r="49" spans="1:26" ht="25" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -12281,7 +12317,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="24.95" customHeight="1">
+    <row r="50" spans="1:26" ht="25" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -12309,7 +12345,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="24.95" customHeight="1">
+    <row r="51" spans="1:26" ht="25" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -12337,7 +12373,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="24.95" customHeight="1">
+    <row r="52" spans="1:26" ht="25" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -12365,7 +12401,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="24.95" customHeight="1">
+    <row r="53" spans="1:26" ht="25" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -12393,7 +12429,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="24.95" customHeight="1">
+    <row r="54" spans="1:26" ht="25" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -12421,7 +12457,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="24.95" customHeight="1">
+    <row r="55" spans="1:26" ht="25" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -12449,7 +12485,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="24.95" customHeight="1">
+    <row r="56" spans="1:26" ht="25" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -12477,7 +12513,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="24.95" customHeight="1">
+    <row r="57" spans="1:26" ht="25" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -12505,7 +12541,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="24.95" customHeight="1">
+    <row r="58" spans="1:26" ht="25" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -12533,7 +12569,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="24.95" customHeight="1">
+    <row r="59" spans="1:26" ht="25" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -12561,7 +12597,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="24.95" customHeight="1">
+    <row r="60" spans="1:26" ht="25" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -12589,7 +12625,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="24.95" customHeight="1">
+    <row r="61" spans="1:26" ht="25" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -12617,7 +12653,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="24.95" customHeight="1">
+    <row r="62" spans="1:26" ht="25" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -12645,7 +12681,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="24.95" customHeight="1">
+    <row r="63" spans="1:26" ht="25" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -12673,7 +12709,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="24.95" customHeight="1">
+    <row r="64" spans="1:26" ht="25" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -12701,7 +12737,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="24.95" customHeight="1">
+    <row r="65" spans="1:26" ht="25" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -12729,7 +12765,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="24.95" customHeight="1">
+    <row r="66" spans="1:26" ht="25" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -12757,7 +12793,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="24.95" customHeight="1">
+    <row r="67" spans="1:26" ht="25" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -12785,7 +12821,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="24.95" customHeight="1">
+    <row r="68" spans="1:26" ht="25" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -12813,7 +12849,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="24.95" customHeight="1">
+    <row r="69" spans="1:26" ht="25" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -12841,7 +12877,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="24.95" customHeight="1">
+    <row r="70" spans="1:26" ht="25" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -12869,7 +12905,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="24.95" customHeight="1">
+    <row r="71" spans="1:26" ht="25" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -12897,7 +12933,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="24.95" customHeight="1">
+    <row r="72" spans="1:26" ht="25" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -12925,7 +12961,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="24.95" customHeight="1">
+    <row r="73" spans="1:26" ht="25" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -12953,7 +12989,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="24.95" customHeight="1">
+    <row r="74" spans="1:26" ht="25" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -12981,7 +13017,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="24.95" customHeight="1">
+    <row r="75" spans="1:26" ht="25" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -13009,7 +13045,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="24.95" customHeight="1">
+    <row r="76" spans="1:26" ht="25" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -13037,7 +13073,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="24.95" customHeight="1">
+    <row r="77" spans="1:26" ht="25" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -13065,7 +13101,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="24.95" customHeight="1">
+    <row r="78" spans="1:26" ht="25" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -13093,7 +13129,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="24.95" customHeight="1">
+    <row r="79" spans="1:26" ht="25" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -13121,7 +13157,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="24.95" customHeight="1">
+    <row r="80" spans="1:26" ht="25" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -13149,7 +13185,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="24.95" customHeight="1">
+    <row r="81" spans="1:26" ht="25" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -13177,7 +13213,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="24.95" customHeight="1">
+    <row r="82" spans="1:26" ht="25" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -13205,7 +13241,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="24.95" customHeight="1">
+    <row r="83" spans="1:26" ht="25" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -13233,7 +13269,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="24.95" customHeight="1">
+    <row r="84" spans="1:26" ht="25" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -13261,7 +13297,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="24.95" customHeight="1">
+    <row r="85" spans="1:26" ht="25" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -13289,7 +13325,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="24.95" customHeight="1">
+    <row r="86" spans="1:26" ht="25" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -13317,7 +13353,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="24.95" customHeight="1">
+    <row r="87" spans="1:26" ht="25" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -13345,7 +13381,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="24.95" customHeight="1">
+    <row r="88" spans="1:26" ht="25" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -13373,7 +13409,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="24.95" customHeight="1">
+    <row r="89" spans="1:26" ht="25" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -13401,7 +13437,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="24.95" customHeight="1">
+    <row r="90" spans="1:26" ht="25" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -13429,7 +13465,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="24.95" customHeight="1">
+    <row r="91" spans="1:26" ht="25" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -13457,7 +13493,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="24.95" customHeight="1">
+    <row r="92" spans="1:26" ht="25" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -13485,7 +13521,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="24.95" customHeight="1">
+    <row r="93" spans="1:26" ht="25" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -13513,7 +13549,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="24.95" customHeight="1">
+    <row r="94" spans="1:26" ht="25" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -13541,7 +13577,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="24.95" customHeight="1">
+    <row r="95" spans="1:26" ht="25" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -13569,7 +13605,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="24.95" customHeight="1">
+    <row r="96" spans="1:26" ht="25" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -13597,7 +13633,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="24.95" customHeight="1">
+    <row r="97" spans="1:26" ht="25" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -13625,7 +13661,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="24.95" customHeight="1">
+    <row r="98" spans="1:26" ht="25" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -13653,7 +13689,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="24.95" customHeight="1">
+    <row r="99" spans="1:26" ht="25" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -13681,7 +13717,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="24.95" customHeight="1">
+    <row r="100" spans="1:26" ht="25" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -13709,7 +13745,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="24.95" customHeight="1">
+    <row r="101" spans="1:26" ht="25" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -13737,7 +13773,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="24.95" customHeight="1">
+    <row r="102" spans="1:26" ht="25" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -13765,7 +13801,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="24.95" customHeight="1">
+    <row r="103" spans="1:26" ht="25" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -13793,7 +13829,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="24.95" customHeight="1">
+    <row r="104" spans="1:26" ht="25" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -17915,13 +17951,13 @@
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:D104">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>D5="Present"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>D5="Late"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3">
+    <cfRule type="expression" dxfId="8" priority="3">
       <formula>D5="Absent"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18010,7 +18046,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
@@ -18018,26 +18054,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="62"/>
     </row>
     <row r="2" spans="1:6" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="62"/>
-    </row>
-    <row r="3" spans="1:6" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="65"/>
+    </row>
+    <row r="3" spans="1:6" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18065,7 +18101,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.95" customHeight="1">
+    <row r="5" spans="1:6" ht="25" customHeight="1">
       <c r="A5" s="33" t="s">
         <v>32</v>
       </c>
@@ -18085,7 +18121,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24.95" customHeight="1">
+    <row r="6" spans="1:6" ht="25" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>37</v>
       </c>
@@ -18105,7 +18141,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24.95" customHeight="1">
+    <row r="7" spans="1:6" ht="25" customHeight="1">
       <c r="A7" s="33" t="s">
         <v>38</v>
       </c>
@@ -18125,7 +18161,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24.95" customHeight="1">
+    <row r="8" spans="1:6" ht="25" customHeight="1">
       <c r="A8" s="31"/>
       <c r="B8" s="17" t="s">
         <v>57</v>
@@ -18143,7 +18179,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24.95" customHeight="1">
+    <row r="9" spans="1:6" ht="25" customHeight="1">
       <c r="A9" s="33"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -18155,7 +18191,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24.95" customHeight="1">
+    <row r="10" spans="1:6" ht="25" customHeight="1">
       <c r="A10" s="31"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -18165,7 +18201,7 @@
       <c r="E10" s="17"/>
       <c r="F10" s="19"/>
     </row>
-    <row r="11" spans="1:6" ht="24.95" customHeight="1">
+    <row r="11" spans="1:6" ht="25" customHeight="1">
       <c r="A11" s="33"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -18175,7 +18211,7 @@
       <c r="E11" s="25"/>
       <c r="F11" s="27"/>
     </row>
-    <row r="12" spans="1:6" ht="24.95" customHeight="1">
+    <row r="12" spans="1:6" ht="25" customHeight="1">
       <c r="A12" s="31"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -18185,7 +18221,7 @@
       <c r="E12" s="17"/>
       <c r="F12" s="19"/>
     </row>
-    <row r="13" spans="1:6" ht="24.95" customHeight="1">
+    <row r="13" spans="1:6" ht="25" customHeight="1">
       <c r="A13" s="34"/>
       <c r="B13" s="35"/>
       <c r="C13" s="35"/>
@@ -18210,7 +18246,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
@@ -18219,30 +18255,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="62"/>
-    </row>
-    <row r="3" spans="1:8" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="65"/>
+    </row>
+    <row r="3" spans="1:8" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18411,7 +18447,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
     <col min="5" max="6" width="30" customWidth="1"/>
@@ -18420,30 +18456,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="62"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="62"/>
-    </row>
-    <row r="3" spans="1:8" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="65"/>
+    </row>
+    <row r="3" spans="1:8" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -18539,7 +18575,7 @@
       <c r="G7" s="43"/>
       <c r="H7" s="27"/>
     </row>
-    <row r="8" spans="1:8" ht="24.95" customHeight="1">
+    <row r="8" spans="1:8" ht="25" customHeight="1">
       <c r="A8" s="38"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -18549,7 +18585,7 @@
       <c r="G8" s="44"/>
       <c r="H8" s="19"/>
     </row>
-    <row r="9" spans="1:8" ht="24.95" customHeight="1">
+    <row r="9" spans="1:8" ht="25" customHeight="1">
       <c r="A9" s="37"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -18559,7 +18595,7 @@
       <c r="G9" s="43"/>
       <c r="H9" s="27"/>
     </row>
-    <row r="10" spans="1:8" ht="24.95" customHeight="1">
+    <row r="10" spans="1:8" ht="25" customHeight="1">
       <c r="A10" s="38"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -18569,7 +18605,7 @@
       <c r="G10" s="44"/>
       <c r="H10" s="19"/>
     </row>
-    <row r="11" spans="1:8" ht="24.95" customHeight="1">
+    <row r="11" spans="1:8" ht="25" customHeight="1">
       <c r="A11" s="37"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -18579,7 +18615,7 @@
       <c r="G11" s="43"/>
       <c r="H11" s="27"/>
     </row>
-    <row r="12" spans="1:8" ht="24.95" customHeight="1">
+    <row r="12" spans="1:8" ht="25" customHeight="1">
       <c r="A12" s="38"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -18589,7 +18625,7 @@
       <c r="G12" s="44"/>
       <c r="H12" s="19"/>
     </row>
-    <row r="13" spans="1:8" ht="24.95" customHeight="1">
+    <row r="13" spans="1:8" ht="25" customHeight="1">
       <c r="A13" s="37"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -18599,7 +18635,7 @@
       <c r="G13" s="43"/>
       <c r="H13" s="27"/>
     </row>
-    <row r="14" spans="1:8" ht="24.95" customHeight="1">
+    <row r="14" spans="1:8" ht="25" customHeight="1">
       <c r="A14" s="38"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -18609,7 +18645,7 @@
       <c r="G14" s="44"/>
       <c r="H14" s="19"/>
     </row>
-    <row r="15" spans="1:8" ht="24.95" customHeight="1">
+    <row r="15" spans="1:8" ht="25" customHeight="1">
       <c r="A15" s="37"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -18619,7 +18655,7 @@
       <c r="G15" s="43"/>
       <c r="H15" s="27"/>
     </row>
-    <row r="16" spans="1:8" ht="24.95" customHeight="1">
+    <row r="16" spans="1:8" ht="25" customHeight="1">
       <c r="A16" s="38"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -18629,7 +18665,7 @@
       <c r="G16" s="44"/>
       <c r="H16" s="19"/>
     </row>
-    <row r="17" spans="1:8" ht="24.95" customHeight="1">
+    <row r="17" spans="1:8" ht="25" customHeight="1">
       <c r="A17" s="37"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -18639,7 +18675,7 @@
       <c r="G17" s="43"/>
       <c r="H17" s="27"/>
     </row>
-    <row r="18" spans="1:8" ht="24.95" customHeight="1">
+    <row r="18" spans="1:8" ht="25" customHeight="1">
       <c r="A18" s="38"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -18649,7 +18685,7 @@
       <c r="G18" s="44"/>
       <c r="H18" s="19"/>
     </row>
-    <row r="19" spans="1:8" ht="24.95" customHeight="1">
+    <row r="19" spans="1:8" ht="25" customHeight="1">
       <c r="A19" s="37"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -18659,7 +18695,7 @@
       <c r="G19" s="43"/>
       <c r="H19" s="27"/>
     </row>
-    <row r="20" spans="1:8" ht="24.95" customHeight="1">
+    <row r="20" spans="1:8" ht="25" customHeight="1">
       <c r="A20" s="38"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -18669,7 +18705,7 @@
       <c r="G20" s="44"/>
       <c r="H20" s="19"/>
     </row>
-    <row r="21" spans="1:8" ht="24.95" customHeight="1">
+    <row r="21" spans="1:8" ht="25" customHeight="1">
       <c r="A21" s="37"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -18679,7 +18715,7 @@
       <c r="G21" s="43"/>
       <c r="H21" s="27"/>
     </row>
-    <row r="22" spans="1:8" ht="24.95" customHeight="1">
+    <row r="22" spans="1:8" ht="25" customHeight="1">
       <c r="A22" s="38"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -18689,7 +18725,7 @@
       <c r="G22" s="44"/>
       <c r="H22" s="19"/>
     </row>
-    <row r="23" spans="1:8" ht="24.95" customHeight="1">
+    <row r="23" spans="1:8" ht="25" customHeight="1">
       <c r="A23" s="37"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -18699,7 +18735,7 @@
       <c r="G23" s="43"/>
       <c r="H23" s="27"/>
     </row>
-    <row r="24" spans="1:8" ht="24.95" customHeight="1">
+    <row r="24" spans="1:8" ht="25" customHeight="1">
       <c r="A24" s="38"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -18709,7 +18745,7 @@
       <c r="G24" s="44"/>
       <c r="H24" s="19"/>
     </row>
-    <row r="25" spans="1:8" ht="24.95" customHeight="1">
+    <row r="25" spans="1:8" ht="25" customHeight="1">
       <c r="A25" s="37"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -18719,7 +18755,7 @@
       <c r="G25" s="43"/>
       <c r="H25" s="27"/>
     </row>
-    <row r="26" spans="1:8" ht="24.95" customHeight="1">
+    <row r="26" spans="1:8" ht="25" customHeight="1">
       <c r="A26" s="38"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -18729,7 +18765,7 @@
       <c r="G26" s="44"/>
       <c r="H26" s="19"/>
     </row>
-    <row r="27" spans="1:8" ht="24.95" customHeight="1">
+    <row r="27" spans="1:8" ht="25" customHeight="1">
       <c r="A27" s="37"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -18739,7 +18775,7 @@
       <c r="G27" s="43"/>
       <c r="H27" s="27"/>
     </row>
-    <row r="28" spans="1:8" ht="24.95" customHeight="1">
+    <row r="28" spans="1:8" ht="25" customHeight="1">
       <c r="A28" s="38"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -18749,7 +18785,7 @@
       <c r="G28" s="44"/>
       <c r="H28" s="19"/>
     </row>
-    <row r="29" spans="1:8" ht="24.95" customHeight="1">
+    <row r="29" spans="1:8" ht="25" customHeight="1">
       <c r="A29" s="37"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -18759,7 +18795,7 @@
       <c r="G29" s="43"/>
       <c r="H29" s="27"/>
     </row>
-    <row r="30" spans="1:8" ht="24.95" customHeight="1">
+    <row r="30" spans="1:8" ht="25" customHeight="1">
       <c r="A30" s="38"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -18769,7 +18805,7 @@
       <c r="G30" s="44"/>
       <c r="H30" s="19"/>
     </row>
-    <row r="31" spans="1:8" ht="24.95" customHeight="1">
+    <row r="31" spans="1:8" ht="25" customHeight="1">
       <c r="A31" s="37"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -18779,7 +18815,7 @@
       <c r="G31" s="43"/>
       <c r="H31" s="27"/>
     </row>
-    <row r="32" spans="1:8" ht="24.95" customHeight="1">
+    <row r="32" spans="1:8" ht="25" customHeight="1">
       <c r="A32" s="38"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -18789,7 +18825,7 @@
       <c r="G32" s="44"/>
       <c r="H32" s="19"/>
     </row>
-    <row r="33" spans="1:8" ht="24.95" customHeight="1">
+    <row r="33" spans="1:8" ht="25" customHeight="1">
       <c r="A33" s="37"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -18799,7 +18835,7 @@
       <c r="G33" s="43"/>
       <c r="H33" s="27"/>
     </row>
-    <row r="34" spans="1:8" ht="24.95" customHeight="1">
+    <row r="34" spans="1:8" ht="25" customHeight="1">
       <c r="A34" s="38"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -18809,7 +18845,7 @@
       <c r="G34" s="44"/>
       <c r="H34" s="19"/>
     </row>
-    <row r="35" spans="1:8" ht="24.95" customHeight="1">
+    <row r="35" spans="1:8" ht="25" customHeight="1">
       <c r="A35" s="37"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -18819,7 +18855,7 @@
       <c r="G35" s="43"/>
       <c r="H35" s="27"/>
     </row>
-    <row r="36" spans="1:8" ht="24.95" customHeight="1">
+    <row r="36" spans="1:8" ht="25" customHeight="1">
       <c r="A36" s="38"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -18829,7 +18865,7 @@
       <c r="G36" s="44"/>
       <c r="H36" s="19"/>
     </row>
-    <row r="37" spans="1:8" ht="24.95" customHeight="1">
+    <row r="37" spans="1:8" ht="25" customHeight="1">
       <c r="A37" s="37"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -18839,7 +18875,7 @@
       <c r="G37" s="43"/>
       <c r="H37" s="27"/>
     </row>
-    <row r="38" spans="1:8" ht="24.95" customHeight="1">
+    <row r="38" spans="1:8" ht="25" customHeight="1">
       <c r="A38" s="38"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -18849,7 +18885,7 @@
       <c r="G38" s="44"/>
       <c r="H38" s="19"/>
     </row>
-    <row r="39" spans="1:8" ht="24.95" customHeight="1">
+    <row r="39" spans="1:8" ht="25" customHeight="1">
       <c r="A39" s="37"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -18859,7 +18895,7 @@
       <c r="G39" s="43"/>
       <c r="H39" s="27"/>
     </row>
-    <row r="40" spans="1:8" ht="24.95" customHeight="1">
+    <row r="40" spans="1:8" ht="25" customHeight="1">
       <c r="A40" s="38"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -18869,7 +18905,7 @@
       <c r="G40" s="44"/>
       <c r="H40" s="19"/>
     </row>
-    <row r="41" spans="1:8" ht="24.95" customHeight="1">
+    <row r="41" spans="1:8" ht="25" customHeight="1">
       <c r="A41" s="37"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -18879,7 +18915,7 @@
       <c r="G41" s="43"/>
       <c r="H41" s="27"/>
     </row>
-    <row r="42" spans="1:8" ht="24.95" customHeight="1">
+    <row r="42" spans="1:8" ht="25" customHeight="1">
       <c r="A42" s="38"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -18889,7 +18925,7 @@
       <c r="G42" s="44"/>
       <c r="H42" s="19"/>
     </row>
-    <row r="43" spans="1:8" ht="24.95" customHeight="1">
+    <row r="43" spans="1:8" ht="25" customHeight="1">
       <c r="A43" s="37"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -18899,7 +18935,7 @@
       <c r="G43" s="43"/>
       <c r="H43" s="27"/>
     </row>
-    <row r="44" spans="1:8" ht="24.95" customHeight="1">
+    <row r="44" spans="1:8" ht="25" customHeight="1">
       <c r="A44" s="38"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -18909,7 +18945,7 @@
       <c r="G44" s="44"/>
       <c r="H44" s="19"/>
     </row>
-    <row r="45" spans="1:8" ht="24.95" customHeight="1">
+    <row r="45" spans="1:8" ht="25" customHeight="1">
       <c r="A45" s="37"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -18919,7 +18955,7 @@
       <c r="G45" s="43"/>
       <c r="H45" s="27"/>
     </row>
-    <row r="46" spans="1:8" ht="24.95" customHeight="1">
+    <row r="46" spans="1:8" ht="25" customHeight="1">
       <c r="A46" s="38"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -18929,7 +18965,7 @@
       <c r="G46" s="44"/>
       <c r="H46" s="19"/>
     </row>
-    <row r="47" spans="1:8" ht="24.95" customHeight="1">
+    <row r="47" spans="1:8" ht="25" customHeight="1">
       <c r="A47" s="37"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -18939,7 +18975,7 @@
       <c r="G47" s="43"/>
       <c r="H47" s="27"/>
     </row>
-    <row r="48" spans="1:8" ht="24.95" customHeight="1">
+    <row r="48" spans="1:8" ht="25" customHeight="1">
       <c r="A48" s="38"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -18949,7 +18985,7 @@
       <c r="G48" s="44"/>
       <c r="H48" s="19"/>
     </row>
-    <row r="49" spans="1:8" ht="24.95" customHeight="1">
+    <row r="49" spans="1:8" ht="25" customHeight="1">
       <c r="A49" s="37"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -18959,7 +18995,7 @@
       <c r="G49" s="43"/>
       <c r="H49" s="27"/>
     </row>
-    <row r="50" spans="1:8" ht="24.95" customHeight="1">
+    <row r="50" spans="1:8" ht="25" customHeight="1">
       <c r="A50" s="39"/>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -18992,41 +19028,41 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
     <col min="5" max="10" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
-    </row>
-    <row r="3" spans="1:26" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -19038,7 +19074,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="15">
+    <row r="4" spans="1:26" ht="14.1">
       <c r="A4" s="23" t="s">
         <v>26</v>
       </c>
@@ -19170,7 +19206,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="24.95" customHeight="1">
+    <row r="8" spans="1:26" ht="25" customHeight="1">
       <c r="A8" s="29"/>
       <c r="B8" s="17"/>
       <c r="C8" s="18"/>
@@ -19198,7 +19234,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="24.95" customHeight="1">
+    <row r="9" spans="1:26" ht="25" customHeight="1">
       <c r="A9" s="28"/>
       <c r="B9" s="25"/>
       <c r="C9" s="26"/>
@@ -19226,7 +19262,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="24.95" customHeight="1">
+    <row r="10" spans="1:26" ht="25" customHeight="1">
       <c r="A10" s="29"/>
       <c r="B10" s="17"/>
       <c r="C10" s="18"/>
@@ -19254,7 +19290,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="24.95" customHeight="1">
+    <row r="11" spans="1:26" ht="25" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="25"/>
       <c r="C11" s="26"/>
@@ -19282,7 +19318,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="24.95" customHeight="1">
+    <row r="12" spans="1:26" ht="25" customHeight="1">
       <c r="A12" s="29"/>
       <c r="B12" s="17"/>
       <c r="C12" s="18"/>
@@ -19310,7 +19346,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="24.95" customHeight="1">
+    <row r="13" spans="1:26" ht="25" customHeight="1">
       <c r="A13" s="28"/>
       <c r="B13" s="25"/>
       <c r="C13" s="26"/>
@@ -19338,7 +19374,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="24.95" customHeight="1">
+    <row r="14" spans="1:26" ht="25" customHeight="1">
       <c r="A14" s="29"/>
       <c r="B14" s="17"/>
       <c r="C14" s="18"/>
@@ -19366,7 +19402,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="24.95" customHeight="1">
+    <row r="15" spans="1:26" ht="25" customHeight="1">
       <c r="A15" s="28"/>
       <c r="B15" s="25"/>
       <c r="C15" s="26"/>
@@ -19394,7 +19430,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="24.95" customHeight="1">
+    <row r="16" spans="1:26" ht="25" customHeight="1">
       <c r="A16" s="29"/>
       <c r="B16" s="17"/>
       <c r="C16" s="18"/>
@@ -19422,7 +19458,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="24.95" customHeight="1">
+    <row r="17" spans="1:26" ht="25" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="25"/>
       <c r="C17" s="26"/>
@@ -19450,7 +19486,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="24.95" customHeight="1">
+    <row r="18" spans="1:26" ht="25" customHeight="1">
       <c r="A18" s="29"/>
       <c r="B18" s="17"/>
       <c r="C18" s="18"/>
@@ -19478,7 +19514,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="24.95" customHeight="1">
+    <row r="19" spans="1:26" ht="25" customHeight="1">
       <c r="A19" s="28"/>
       <c r="B19" s="25"/>
       <c r="C19" s="26"/>
@@ -19506,7 +19542,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="24.95" customHeight="1">
+    <row r="20" spans="1:26" ht="25" customHeight="1">
       <c r="A20" s="29"/>
       <c r="B20" s="17"/>
       <c r="C20" s="18"/>
@@ -19534,7 +19570,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="24.95" customHeight="1">
+    <row r="21" spans="1:26" ht="25" customHeight="1">
       <c r="A21" s="28"/>
       <c r="B21" s="25"/>
       <c r="C21" s="26"/>
@@ -19562,7 +19598,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="24.95" customHeight="1">
+    <row r="22" spans="1:26" ht="25" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="17"/>
       <c r="C22" s="18"/>
@@ -19590,7 +19626,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="24.95" customHeight="1">
+    <row r="23" spans="1:26" ht="25" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="25"/>
       <c r="C23" s="26"/>
@@ -19618,7 +19654,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="24.95" customHeight="1">
+    <row r="24" spans="1:26" ht="25" customHeight="1">
       <c r="A24" s="29"/>
       <c r="B24" s="17"/>
       <c r="C24" s="18"/>
@@ -19646,7 +19682,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="24.95" customHeight="1">
+    <row r="25" spans="1:26" ht="25" customHeight="1">
       <c r="A25" s="28"/>
       <c r="B25" s="25"/>
       <c r="C25" s="26"/>
@@ -19674,7 +19710,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="24.95" customHeight="1">
+    <row r="26" spans="1:26" ht="25" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="18"/>
@@ -19702,7 +19738,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="24.95" customHeight="1">
+    <row r="27" spans="1:26" ht="25" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="26"/>
@@ -19730,7 +19766,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="24.95" customHeight="1">
+    <row r="28" spans="1:26" ht="25" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="18"/>
@@ -19758,7 +19794,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="24.95" customHeight="1">
+    <row r="29" spans="1:26" ht="25" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="26"/>
@@ -19786,7 +19822,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="24.95" customHeight="1">
+    <row r="30" spans="1:26" ht="25" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="18"/>
@@ -19814,7 +19850,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="24.95" customHeight="1">
+    <row r="31" spans="1:26" ht="25" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="26"/>
@@ -19842,7 +19878,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="24.95" customHeight="1">
+    <row r="32" spans="1:26" ht="25" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="18"/>
@@ -19870,7 +19906,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="24.95" customHeight="1">
+    <row r="33" spans="1:26" ht="25" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="26"/>
@@ -19898,7 +19934,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="24.95" customHeight="1">
+    <row r="34" spans="1:26" ht="25" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="18"/>
@@ -19926,7 +19962,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="24.95" customHeight="1">
+    <row r="35" spans="1:26" ht="25" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="26"/>
@@ -19954,7 +19990,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="24.95" customHeight="1">
+    <row r="36" spans="1:26" ht="25" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="18"/>
@@ -19982,7 +20018,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="24.95" customHeight="1">
+    <row r="37" spans="1:26" ht="25" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="26"/>
@@ -20010,7 +20046,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="24.95" customHeight="1">
+    <row r="38" spans="1:26" ht="25" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="18"/>
@@ -20038,7 +20074,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="24.95" customHeight="1">
+    <row r="39" spans="1:26" ht="25" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="26"/>
@@ -20066,7 +20102,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="24.95" customHeight="1">
+    <row r="40" spans="1:26" ht="25" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="18"/>
@@ -20094,7 +20130,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="24.95" customHeight="1">
+    <row r="41" spans="1:26" ht="25" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="26"/>
@@ -20122,7 +20158,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="24.95" customHeight="1">
+    <row r="42" spans="1:26" ht="25" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="18"/>
@@ -20150,7 +20186,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="24.95" customHeight="1">
+    <row r="43" spans="1:26" ht="25" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="26"/>
@@ -20178,7 +20214,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="24.95" customHeight="1">
+    <row r="44" spans="1:26" ht="25" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="18"/>
@@ -20206,7 +20242,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="24.95" customHeight="1">
+    <row r="45" spans="1:26" ht="25" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="26"/>
@@ -20234,7 +20270,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="24.95" customHeight="1">
+    <row r="46" spans="1:26" ht="25" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="18"/>
@@ -20262,7 +20298,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="24.95" customHeight="1">
+    <row r="47" spans="1:26" ht="25" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="26"/>
@@ -20290,7 +20326,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="24.95" customHeight="1">
+    <row r="48" spans="1:26" ht="25" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="18"/>
@@ -20318,7 +20354,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="24.95" customHeight="1">
+    <row r="49" spans="1:26" ht="25" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="26"/>
@@ -20346,7 +20382,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="24.95" customHeight="1">
+    <row r="50" spans="1:26" ht="25" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="18"/>
@@ -20374,7 +20410,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="24.95" customHeight="1">
+    <row r="51" spans="1:26" ht="25" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="26"/>
@@ -20402,7 +20438,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="24.95" customHeight="1">
+    <row r="52" spans="1:26" ht="25" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="18"/>
@@ -20430,7 +20466,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="24.95" customHeight="1">
+    <row r="53" spans="1:26" ht="25" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="26"/>
@@ -20458,7 +20494,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="24.95" customHeight="1">
+    <row r="54" spans="1:26" ht="25" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="18"/>
@@ -20486,7 +20522,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="24.95" customHeight="1">
+    <row r="55" spans="1:26" ht="25" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="26"/>
@@ -20514,7 +20550,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="24.95" customHeight="1">
+    <row r="56" spans="1:26" ht="25" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="18"/>
@@ -20542,7 +20578,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="24.95" customHeight="1">
+    <row r="57" spans="1:26" ht="25" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="26"/>
@@ -20570,7 +20606,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="24.95" customHeight="1">
+    <row r="58" spans="1:26" ht="25" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="18"/>
@@ -20598,7 +20634,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="24.95" customHeight="1">
+    <row r="59" spans="1:26" ht="25" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="26"/>
@@ -20626,7 +20662,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="24.95" customHeight="1">
+    <row r="60" spans="1:26" ht="25" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="18"/>
@@ -20654,7 +20690,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="24.95" customHeight="1">
+    <row r="61" spans="1:26" ht="25" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="26"/>
@@ -20682,7 +20718,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="24.95" customHeight="1">
+    <row r="62" spans="1:26" ht="25" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="18"/>
@@ -20710,7 +20746,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="24.95" customHeight="1">
+    <row r="63" spans="1:26" ht="25" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="26"/>
@@ -20738,7 +20774,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="24.95" customHeight="1">
+    <row r="64" spans="1:26" ht="25" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="18"/>
@@ -20766,7 +20802,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="24.95" customHeight="1">
+    <row r="65" spans="1:26" ht="25" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="26"/>
@@ -20794,7 +20830,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="24.95" customHeight="1">
+    <row r="66" spans="1:26" ht="25" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="18"/>
@@ -20822,7 +20858,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="24.95" customHeight="1">
+    <row r="67" spans="1:26" ht="25" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="26"/>
@@ -20850,7 +20886,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="24.95" customHeight="1">
+    <row r="68" spans="1:26" ht="25" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="18"/>
@@ -20878,7 +20914,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="24.95" customHeight="1">
+    <row r="69" spans="1:26" ht="25" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="26"/>
@@ -20906,7 +20942,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="24.95" customHeight="1">
+    <row r="70" spans="1:26" ht="25" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="18"/>
@@ -20934,7 +20970,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="24.95" customHeight="1">
+    <row r="71" spans="1:26" ht="25" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="26"/>
@@ -20962,7 +20998,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="24.95" customHeight="1">
+    <row r="72" spans="1:26" ht="25" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="18"/>
@@ -20990,7 +21026,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="24.95" customHeight="1">
+    <row r="73" spans="1:26" ht="25" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="26"/>
@@ -21018,7 +21054,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="24.95" customHeight="1">
+    <row r="74" spans="1:26" ht="25" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="18"/>
@@ -21046,7 +21082,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="24.95" customHeight="1">
+    <row r="75" spans="1:26" ht="25" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="26"/>
@@ -21074,7 +21110,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="24.95" customHeight="1">
+    <row r="76" spans="1:26" ht="25" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="18"/>
@@ -21102,7 +21138,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="24.95" customHeight="1">
+    <row r="77" spans="1:26" ht="25" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="26"/>
@@ -21130,7 +21166,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="24.95" customHeight="1">
+    <row r="78" spans="1:26" ht="25" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="18"/>
@@ -21158,7 +21194,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="24.95" customHeight="1">
+    <row r="79" spans="1:26" ht="25" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="26"/>
@@ -21186,7 +21222,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="24.95" customHeight="1">
+    <row r="80" spans="1:26" ht="25" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="18"/>
@@ -21214,7 +21250,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="24.95" customHeight="1">
+    <row r="81" spans="1:26" ht="25" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="26"/>
@@ -21242,7 +21278,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="24.95" customHeight="1">
+    <row r="82" spans="1:26" ht="25" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="18"/>
@@ -21270,7 +21306,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="24.95" customHeight="1">
+    <row r="83" spans="1:26" ht="25" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="26"/>
@@ -21298,7 +21334,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="24.95" customHeight="1">
+    <row r="84" spans="1:26" ht="25" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="18"/>
@@ -21326,7 +21362,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="24.95" customHeight="1">
+    <row r="85" spans="1:26" ht="25" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="26"/>
@@ -21354,7 +21390,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="24.95" customHeight="1">
+    <row r="86" spans="1:26" ht="25" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="18"/>
@@ -21382,7 +21418,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="24.95" customHeight="1">
+    <row r="87" spans="1:26" ht="25" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="26"/>
@@ -21410,7 +21446,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="24.95" customHeight="1">
+    <row r="88" spans="1:26" ht="25" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="18"/>
@@ -21438,7 +21474,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="24.95" customHeight="1">
+    <row r="89" spans="1:26" ht="25" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="26"/>
@@ -21466,7 +21502,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="24.95" customHeight="1">
+    <row r="90" spans="1:26" ht="25" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="18"/>
@@ -21494,7 +21530,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="24.95" customHeight="1">
+    <row r="91" spans="1:26" ht="25" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="26"/>
@@ -21522,7 +21558,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="24.95" customHeight="1">
+    <row r="92" spans="1:26" ht="25" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="18"/>
@@ -21550,7 +21586,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="24.95" customHeight="1">
+    <row r="93" spans="1:26" ht="25" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="26"/>
@@ -21578,7 +21614,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="24.95" customHeight="1">
+    <row r="94" spans="1:26" ht="25" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="18"/>
@@ -21606,7 +21642,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="24.95" customHeight="1">
+    <row r="95" spans="1:26" ht="25" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="26"/>
@@ -21634,7 +21670,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="24.95" customHeight="1">
+    <row r="96" spans="1:26" ht="25" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="18"/>
@@ -21662,7 +21698,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="24.95" customHeight="1">
+    <row r="97" spans="1:26" ht="25" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="26"/>
@@ -21690,7 +21726,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="24.95" customHeight="1">
+    <row r="98" spans="1:26" ht="25" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="18"/>
@@ -21718,7 +21754,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="24.95" customHeight="1">
+    <row r="99" spans="1:26" ht="25" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="26"/>
@@ -21746,7 +21782,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="24.95" customHeight="1">
+    <row r="100" spans="1:26" ht="25" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="18"/>
@@ -21774,7 +21810,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="24.95" customHeight="1">
+    <row r="101" spans="1:26" ht="25" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="26"/>
@@ -21802,7 +21838,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="24.95" customHeight="1">
+    <row r="102" spans="1:26" ht="25" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="18"/>
@@ -21830,7 +21866,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="24.95" customHeight="1">
+    <row r="103" spans="1:26" ht="25" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="26"/>
@@ -21858,7 +21894,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="24.95" customHeight="1">
+    <row r="104" spans="1:26" ht="25" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="21"/>
@@ -25980,13 +26016,13 @@
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="I5:I104">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="7" priority="1">
       <formula>I5="Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="6" priority="2">
       <formula>I5="Partly"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
+    <cfRule type="expression" dxfId="5" priority="3">
       <formula>I5="No"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -26026,46 +26062,46 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.47265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6171875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.37890625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="62"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="62"/>
-    </row>
-    <row r="3" spans="1:26" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -26076,32 +26112,32 @@
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="15">
-      <c r="A4" s="67" t="s">
+    <row r="4" spans="1:26" ht="14.1">
+      <c r="A4" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="58" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="68" t="s">
+      <c r="D4" s="58" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="68" t="s">
+      <c r="E4" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="F4" s="68" t="s">
+      <c r="F4" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="58" t="s">
         <v>101</v>
       </c>
-      <c r="H4" s="68" t="s">
+      <c r="H4" s="58" t="s">
         <v>102</v>
       </c>
-      <c r="I4" s="69" t="s">
+      <c r="I4" s="59" t="s">
         <v>103</v>
       </c>
       <c r="J4" s="1"/>
@@ -26256,7 +26292,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="24.95" customHeight="1">
+    <row r="8" spans="1:26" ht="25" customHeight="1">
       <c r="A8" s="28">
         <v>46277</v>
       </c>
@@ -26302,7 +26338,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="24.95" customHeight="1">
+    <row r="9" spans="1:26" ht="25" customHeight="1">
       <c r="A9" s="28">
         <v>46277</v>
       </c>
@@ -26346,7 +26382,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="24.95" customHeight="1">
+    <row r="10" spans="1:26" ht="25" customHeight="1">
       <c r="A10" s="28">
         <v>46277</v>
       </c>
@@ -26392,7 +26428,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="24.95" customHeight="1">
+    <row r="11" spans="1:26" ht="25" customHeight="1">
       <c r="A11" s="28">
         <v>46278</v>
       </c>
@@ -26438,7 +26474,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="24.95" customHeight="1">
+    <row r="12" spans="1:26" ht="25" customHeight="1">
       <c r="A12" s="28">
         <v>46278</v>
       </c>
@@ -26484,7 +26520,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="24.95" customHeight="1">
+    <row r="13" spans="1:26" ht="25" customHeight="1">
       <c r="A13" s="28">
         <v>46278</v>
       </c>
@@ -26530,7 +26566,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="24.95" customHeight="1">
+    <row r="14" spans="1:26" ht="25" customHeight="1">
       <c r="A14" s="29">
         <v>46284</v>
       </c>
@@ -26576,7 +26612,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="24.95" customHeight="1">
+    <row r="15" spans="1:26" ht="25" customHeight="1">
       <c r="A15" s="28">
         <v>46284</v>
       </c>
@@ -26622,7 +26658,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="24.95" customHeight="1">
+    <row r="16" spans="1:26" ht="25" customHeight="1">
       <c r="A16" s="29">
         <v>46284</v>
       </c>
@@ -26666,7 +26702,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="24.95" customHeight="1">
+    <row r="17" spans="1:26" ht="25" customHeight="1">
       <c r="A17" s="28">
         <v>46285</v>
       </c>
@@ -26708,7 +26744,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="24.95" customHeight="1">
+    <row r="18" spans="1:26" ht="25" customHeight="1">
       <c r="A18" s="29">
         <v>46285</v>
       </c>
@@ -26750,7 +26786,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="24.95" customHeight="1">
+    <row r="19" spans="1:26" ht="25" customHeight="1">
       <c r="A19" s="28">
         <v>46285</v>
       </c>
@@ -26792,7 +26828,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="24.95" customHeight="1">
+    <row r="20" spans="1:26" ht="25" customHeight="1">
       <c r="A20" s="29">
         <v>46291</v>
       </c>
@@ -26836,7 +26872,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="24.95" customHeight="1">
+    <row r="21" spans="1:26" ht="25" customHeight="1">
       <c r="A21" s="28">
         <v>46291</v>
       </c>
@@ -26880,7 +26916,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="24.95" customHeight="1">
+    <row r="22" spans="1:26" ht="25" customHeight="1">
       <c r="A22" s="29">
         <v>46291</v>
       </c>
@@ -26924,7 +26960,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="24.95" customHeight="1">
+    <row r="23" spans="1:26" ht="25" customHeight="1">
       <c r="A23" s="28">
         <v>46292</v>
       </c>
@@ -26964,7 +27000,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="24.95" customHeight="1">
+    <row r="24" spans="1:26" ht="25" customHeight="1">
       <c r="A24" s="29">
         <v>46292</v>
       </c>
@@ -27004,7 +27040,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="24.95" customHeight="1">
+    <row r="25" spans="1:26" ht="25" customHeight="1">
       <c r="A25" s="28">
         <v>46292</v>
       </c>
@@ -27044,14 +27080,28 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="24.95" customHeight="1">
-      <c r="A26" s="29"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
+    <row r="26" spans="1:26" ht="25" customHeight="1">
+      <c r="A26" s="29">
+        <v>46312</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="17">
+        <v>451</v>
+      </c>
+      <c r="E26" s="40">
+        <v>1</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>104</v>
+      </c>
       <c r="H26" s="17"/>
       <c r="I26" s="19"/>
       <c r="J26" s="1"/>
@@ -27072,14 +27122,28 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="24.95" customHeight="1">
-      <c r="A27" s="28"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
+    <row r="27" spans="1:26" ht="25" customHeight="1">
+      <c r="A27" s="28">
+        <v>46312</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="25">
+        <v>542</v>
+      </c>
+      <c r="E27" s="42">
+        <v>0.8</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>206</v>
+      </c>
       <c r="H27" s="25"/>
       <c r="I27" s="27"/>
       <c r="J27" s="1"/>
@@ -27100,14 +27164,28 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="24.95" customHeight="1">
-      <c r="A28" s="29"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+    <row r="28" spans="1:26" ht="25" customHeight="1">
+      <c r="A28" s="29">
+        <v>46312</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="17">
+        <v>425</v>
+      </c>
+      <c r="E28" s="40">
+        <v>1</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>104</v>
+      </c>
       <c r="H28" s="17"/>
       <c r="I28" s="19"/>
       <c r="J28" s="1"/>
@@ -27128,7 +27206,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="24.95" customHeight="1">
+    <row r="29" spans="1:26" ht="25" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -27156,7 +27234,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="24.95" customHeight="1">
+    <row r="30" spans="1:26" ht="25" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -27184,7 +27262,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="24.95" customHeight="1">
+    <row r="31" spans="1:26" ht="25" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -27212,7 +27290,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="24.95" customHeight="1">
+    <row r="32" spans="1:26" ht="25" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -27240,7 +27318,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="24.95" customHeight="1">
+    <row r="33" spans="1:26" ht="25" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -27268,7 +27346,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="24.95" customHeight="1">
+    <row r="34" spans="1:26" ht="25" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -27296,7 +27374,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="24.95" customHeight="1">
+    <row r="35" spans="1:26" ht="25" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -27324,7 +27402,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="24.95" customHeight="1">
+    <row r="36" spans="1:26" ht="25" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -27352,7 +27430,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="24.95" customHeight="1">
+    <row r="37" spans="1:26" ht="25" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -27380,7 +27458,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="24.95" customHeight="1">
+    <row r="38" spans="1:26" ht="25" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -27408,7 +27486,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="24.95" customHeight="1">
+    <row r="39" spans="1:26" ht="25" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -27436,7 +27514,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="24.95" customHeight="1">
+    <row r="40" spans="1:26" ht="25" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -27464,7 +27542,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="24.95" customHeight="1">
+    <row r="41" spans="1:26" ht="25" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -27492,7 +27570,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="24.95" customHeight="1">
+    <row r="42" spans="1:26" ht="25" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -27520,7 +27598,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="24.95" customHeight="1">
+    <row r="43" spans="1:26" ht="25" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -27548,7 +27626,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="24.95" customHeight="1">
+    <row r="44" spans="1:26" ht="25" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -27576,7 +27654,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="24.95" customHeight="1">
+    <row r="45" spans="1:26" ht="25" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -27604,7 +27682,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="24.95" customHeight="1">
+    <row r="46" spans="1:26" ht="25" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -27632,7 +27710,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="24.95" customHeight="1">
+    <row r="47" spans="1:26" ht="25" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -27660,7 +27738,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="24.95" customHeight="1">
+    <row r="48" spans="1:26" ht="25" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -27688,7 +27766,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="24.95" customHeight="1">
+    <row r="49" spans="1:26" ht="25" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -27716,7 +27794,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="24.95" customHeight="1">
+    <row r="50" spans="1:26" ht="25" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -27744,7 +27822,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="24.95" customHeight="1">
+    <row r="51" spans="1:26" ht="25" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -27772,7 +27850,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="24.95" customHeight="1">
+    <row r="52" spans="1:26" ht="25" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -27800,7 +27878,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="24.95" customHeight="1">
+    <row r="53" spans="1:26" ht="25" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -27828,7 +27906,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="24.95" customHeight="1">
+    <row r="54" spans="1:26" ht="25" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -27856,7 +27934,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="24.95" customHeight="1">
+    <row r="55" spans="1:26" ht="25" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -27884,7 +27962,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="24.95" customHeight="1">
+    <row r="56" spans="1:26" ht="25" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -27912,7 +27990,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="24.95" customHeight="1">
+    <row r="57" spans="1:26" ht="25" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -27940,7 +28018,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="24.95" customHeight="1">
+    <row r="58" spans="1:26" ht="25" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -27968,7 +28046,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="24.95" customHeight="1">
+    <row r="59" spans="1:26" ht="25" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -27996,7 +28074,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="24.95" customHeight="1">
+    <row r="60" spans="1:26" ht="25" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -28024,7 +28102,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="24.95" customHeight="1">
+    <row r="61" spans="1:26" ht="25" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -28052,7 +28130,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="24.95" customHeight="1">
+    <row r="62" spans="1:26" ht="25" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -28080,7 +28158,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="24.95" customHeight="1">
+    <row r="63" spans="1:26" ht="25" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -28108,7 +28186,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="24.95" customHeight="1">
+    <row r="64" spans="1:26" ht="25" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -28136,7 +28214,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="24.95" customHeight="1">
+    <row r="65" spans="1:26" ht="25" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -28164,7 +28242,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="24.95" customHeight="1">
+    <row r="66" spans="1:26" ht="25" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -28192,7 +28270,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="24.95" customHeight="1">
+    <row r="67" spans="1:26" ht="25" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -28220,7 +28298,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="24.95" customHeight="1">
+    <row r="68" spans="1:26" ht="25" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -28248,7 +28326,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="24.95" customHeight="1">
+    <row r="69" spans="1:26" ht="25" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -28276,7 +28354,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="24.95" customHeight="1">
+    <row r="70" spans="1:26" ht="25" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -28304,7 +28382,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="24.95" customHeight="1">
+    <row r="71" spans="1:26" ht="25" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -28332,7 +28410,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="24.95" customHeight="1">
+    <row r="72" spans="1:26" ht="25" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -28360,7 +28438,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="24.95" customHeight="1">
+    <row r="73" spans="1:26" ht="25" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -28388,7 +28466,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="24.95" customHeight="1">
+    <row r="74" spans="1:26" ht="25" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -28416,7 +28494,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="24.95" customHeight="1">
+    <row r="75" spans="1:26" ht="25" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -28444,7 +28522,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="24.95" customHeight="1">
+    <row r="76" spans="1:26" ht="25" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -28472,7 +28550,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="24.95" customHeight="1">
+    <row r="77" spans="1:26" ht="25" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -28500,7 +28578,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="24.95" customHeight="1">
+    <row r="78" spans="1:26" ht="25" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -28528,7 +28606,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="24.95" customHeight="1">
+    <row r="79" spans="1:26" ht="25" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -28556,7 +28634,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="24.95" customHeight="1">
+    <row r="80" spans="1:26" ht="25" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -28584,7 +28662,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="24.95" customHeight="1">
+    <row r="81" spans="1:26" ht="25" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -28612,7 +28690,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="24.95" customHeight="1">
+    <row r="82" spans="1:26" ht="25" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -28640,7 +28718,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="24.95" customHeight="1">
+    <row r="83" spans="1:26" ht="25" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -28668,7 +28746,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="24.95" customHeight="1">
+    <row r="84" spans="1:26" ht="25" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -28696,7 +28774,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="24.95" customHeight="1">
+    <row r="85" spans="1:26" ht="25" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -28724,7 +28802,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="24.95" customHeight="1">
+    <row r="86" spans="1:26" ht="25" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -28752,7 +28830,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="24.95" customHeight="1">
+    <row r="87" spans="1:26" ht="25" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -28780,7 +28858,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="24.95" customHeight="1">
+    <row r="88" spans="1:26" ht="25" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -28808,7 +28886,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="24.95" customHeight="1">
+    <row r="89" spans="1:26" ht="25" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -28836,7 +28914,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="24.95" customHeight="1">
+    <row r="90" spans="1:26" ht="25" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -28864,7 +28942,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="24.95" customHeight="1">
+    <row r="91" spans="1:26" ht="25" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -28892,7 +28970,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="24.95" customHeight="1">
+    <row r="92" spans="1:26" ht="25" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -28920,7 +28998,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="24.95" customHeight="1">
+    <row r="93" spans="1:26" ht="25" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -28948,7 +29026,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="24.95" customHeight="1">
+    <row r="94" spans="1:26" ht="25" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -28976,7 +29054,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="24.95" customHeight="1">
+    <row r="95" spans="1:26" ht="25" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -29004,7 +29082,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="24.95" customHeight="1">
+    <row r="96" spans="1:26" ht="25" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -29032,7 +29110,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="24.95" customHeight="1">
+    <row r="97" spans="1:26" ht="25" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -29060,7 +29138,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="24.95" customHeight="1">
+    <row r="98" spans="1:26" ht="25" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -29088,7 +29166,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="24.95" customHeight="1">
+    <row r="99" spans="1:26" ht="25" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -29116,7 +29194,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="24.95" customHeight="1">
+    <row r="100" spans="1:26" ht="25" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -29144,7 +29222,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="24.95" customHeight="1">
+    <row r="101" spans="1:26" ht="25" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -29172,7 +29250,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="24.95" customHeight="1">
+    <row r="102" spans="1:26" ht="25" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -29200,7 +29278,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="24.95" customHeight="1">
+    <row r="103" spans="1:26" ht="25" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -29228,7 +29306,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="24.95" customHeight="1">
+    <row r="104" spans="1:26" ht="25" customHeight="1">
       <c r="A104" s="29"/>
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
@@ -29256,7 +29334,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105" spans="1:26" ht="24.95" customHeight="1">
+    <row r="105" spans="1:26" ht="25" customHeight="1">
       <c r="A105" s="28"/>
       <c r="B105" s="25"/>
       <c r="C105" s="25"/>
@@ -29284,7 +29362,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106" spans="1:26" ht="24.95" customHeight="1">
+    <row r="106" spans="1:26" ht="25" customHeight="1">
       <c r="A106" s="29"/>
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
@@ -29312,7 +29390,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107" spans="1:26" ht="24.95" customHeight="1">
+    <row r="107" spans="1:26" ht="25" customHeight="1">
       <c r="A107" s="28"/>
       <c r="B107" s="25"/>
       <c r="C107" s="25"/>
@@ -29340,7 +29418,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108" spans="1:26" ht="24.95" customHeight="1">
+    <row r="108" spans="1:26" ht="25" customHeight="1">
       <c r="A108" s="29"/>
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
@@ -29368,7 +29446,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109" spans="1:26" ht="24.95" customHeight="1">
+    <row r="109" spans="1:26" ht="25" customHeight="1">
       <c r="A109" s="28"/>
       <c r="B109" s="25"/>
       <c r="C109" s="25"/>
@@ -29396,7 +29474,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110" spans="1:26" ht="24.95" customHeight="1">
+    <row r="110" spans="1:26" ht="25" customHeight="1">
       <c r="A110" s="29"/>
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
@@ -29424,7 +29502,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111" spans="1:26" ht="24.95" customHeight="1">
+    <row r="111" spans="1:26" ht="25" customHeight="1">
       <c r="A111" s="28"/>
       <c r="B111" s="25"/>
       <c r="C111" s="25"/>
@@ -29452,7 +29530,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112" spans="1:26" ht="24.95" customHeight="1">
+    <row r="112" spans="1:26" ht="25" customHeight="1">
       <c r="A112" s="29"/>
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
@@ -29480,7 +29558,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113" spans="1:26" ht="24.95" customHeight="1">
+    <row r="113" spans="1:26" ht="25" customHeight="1">
       <c r="A113" s="28"/>
       <c r="B113" s="25"/>
       <c r="C113" s="25"/>
@@ -29508,7 +29586,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114" spans="1:26" ht="24.95" customHeight="1">
+    <row r="114" spans="1:26" ht="25" customHeight="1">
       <c r="A114" s="29"/>
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
@@ -29536,7 +29614,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115" spans="1:26" ht="24.95" customHeight="1">
+    <row r="115" spans="1:26" ht="25" customHeight="1">
       <c r="A115" s="28"/>
       <c r="B115" s="25"/>
       <c r="C115" s="25"/>
@@ -29564,7 +29642,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116" spans="1:26" ht="24.95" customHeight="1">
+    <row r="116" spans="1:26" ht="25" customHeight="1">
       <c r="A116" s="29"/>
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
@@ -29592,7 +29670,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117" spans="1:26" ht="24.95" customHeight="1">
+    <row r="117" spans="1:26" ht="25" customHeight="1">
       <c r="A117" s="28"/>
       <c r="B117" s="25"/>
       <c r="C117" s="25"/>
@@ -29620,7 +29698,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118" spans="1:26" ht="24.95" customHeight="1">
+    <row r="118" spans="1:26" ht="25" customHeight="1">
       <c r="A118" s="29"/>
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
@@ -29648,7 +29726,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119" spans="1:26" ht="24.95" customHeight="1">
+    <row r="119" spans="1:26" ht="25" customHeight="1">
       <c r="A119" s="28"/>
       <c r="B119" s="25"/>
       <c r="C119" s="25"/>
@@ -29676,7 +29754,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120" spans="1:26" ht="24.95" customHeight="1">
+    <row r="120" spans="1:26" ht="25" customHeight="1">
       <c r="A120" s="29"/>
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
@@ -29704,7 +29782,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121" spans="1:26" ht="24.95" customHeight="1">
+    <row r="121" spans="1:26" ht="25" customHeight="1">
       <c r="A121" s="28"/>
       <c r="B121" s="25"/>
       <c r="C121" s="25"/>
@@ -29732,7 +29810,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122" spans="1:26" ht="24.95" customHeight="1">
+    <row r="122" spans="1:26" ht="25" customHeight="1">
       <c r="A122" s="29"/>
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
@@ -29760,7 +29838,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123" spans="1:26" ht="24.95" customHeight="1">
+    <row r="123" spans="1:26" ht="25" customHeight="1">
       <c r="A123" s="28"/>
       <c r="B123" s="25"/>
       <c r="C123" s="25"/>
@@ -29788,7 +29866,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124" spans="1:26" ht="24.95" customHeight="1">
+    <row r="124" spans="1:26" ht="25" customHeight="1">
       <c r="A124" s="29"/>
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
@@ -29816,7 +29894,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125" spans="1:26" ht="24.95" customHeight="1">
+    <row r="125" spans="1:26" ht="25" customHeight="1">
       <c r="A125" s="28"/>
       <c r="B125" s="25"/>
       <c r="C125" s="25"/>
@@ -29844,7 +29922,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126" spans="1:26" ht="24.95" customHeight="1">
+    <row r="126" spans="1:26" ht="25" customHeight="1">
       <c r="A126" s="29"/>
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
@@ -29872,7 +29950,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127" spans="1:26" ht="24.95" customHeight="1">
+    <row r="127" spans="1:26" ht="25" customHeight="1">
       <c r="A127" s="28"/>
       <c r="B127" s="25"/>
       <c r="C127" s="25"/>
@@ -29900,7 +29978,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128" spans="1:26" ht="24.95" customHeight="1">
+    <row r="128" spans="1:26" ht="25" customHeight="1">
       <c r="A128" s="29"/>
       <c r="B128" s="17"/>
       <c r="C128" s="17"/>
@@ -29928,7 +30006,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129" spans="1:26" ht="24.95" customHeight="1">
+    <row r="129" spans="1:26" ht="25" customHeight="1">
       <c r="A129" s="28"/>
       <c r="B129" s="25"/>
       <c r="C129" s="25"/>
@@ -29956,7 +30034,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130" spans="1:26" ht="24.95" customHeight="1">
+    <row r="130" spans="1:26" ht="25" customHeight="1">
       <c r="A130" s="29"/>
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
@@ -29984,7 +30062,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131" spans="1:26" ht="24.95" customHeight="1">
+    <row r="131" spans="1:26" ht="25" customHeight="1">
       <c r="A131" s="28"/>
       <c r="B131" s="25"/>
       <c r="C131" s="25"/>
@@ -30012,7 +30090,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132" spans="1:26" ht="24.95" customHeight="1">
+    <row r="132" spans="1:26" ht="25" customHeight="1">
       <c r="A132" s="29"/>
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
@@ -30040,7 +30118,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133" spans="1:26" ht="24.95" customHeight="1">
+    <row r="133" spans="1:26" ht="25" customHeight="1">
       <c r="A133" s="28"/>
       <c r="B133" s="25"/>
       <c r="C133" s="25"/>
@@ -30068,7 +30146,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134" spans="1:26" ht="24.95" customHeight="1">
+    <row r="134" spans="1:26" ht="25" customHeight="1">
       <c r="A134" s="29"/>
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
@@ -30096,7 +30174,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135" spans="1:26" ht="24.95" customHeight="1">
+    <row r="135" spans="1:26" ht="25" customHeight="1">
       <c r="A135" s="28"/>
       <c r="B135" s="25"/>
       <c r="C135" s="25"/>
@@ -30124,7 +30202,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136" spans="1:26" ht="24.95" customHeight="1">
+    <row r="136" spans="1:26" ht="25" customHeight="1">
       <c r="A136" s="29"/>
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
@@ -30152,7 +30230,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137" spans="1:26" ht="24.95" customHeight="1">
+    <row r="137" spans="1:26" ht="25" customHeight="1">
       <c r="A137" s="28"/>
       <c r="B137" s="25"/>
       <c r="C137" s="25"/>
@@ -30180,7 +30258,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138" spans="1:26" ht="24.95" customHeight="1">
+    <row r="138" spans="1:26" ht="25" customHeight="1">
       <c r="A138" s="29"/>
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
@@ -30208,7 +30286,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139" spans="1:26" ht="24.95" customHeight="1">
+    <row r="139" spans="1:26" ht="25" customHeight="1">
       <c r="A139" s="28"/>
       <c r="B139" s="25"/>
       <c r="C139" s="25"/>
@@ -30236,7 +30314,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140" spans="1:26" ht="24.95" customHeight="1">
+    <row r="140" spans="1:26" ht="25" customHeight="1">
       <c r="A140" s="29"/>
       <c r="B140" s="17"/>
       <c r="C140" s="17"/>
@@ -30264,7 +30342,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141" spans="1:26" ht="24.95" customHeight="1">
+    <row r="141" spans="1:26" ht="25" customHeight="1">
       <c r="A141" s="28"/>
       <c r="B141" s="25"/>
       <c r="C141" s="25"/>
@@ -30292,7 +30370,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142" spans="1:26" ht="24.95" customHeight="1">
+    <row r="142" spans="1:26" ht="25" customHeight="1">
       <c r="A142" s="29"/>
       <c r="B142" s="17"/>
       <c r="C142" s="17"/>
@@ -30320,7 +30398,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143" spans="1:26" ht="24.95" customHeight="1">
+    <row r="143" spans="1:26" ht="25" customHeight="1">
       <c r="A143" s="28"/>
       <c r="B143" s="25"/>
       <c r="C143" s="25"/>
@@ -30348,7 +30426,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144" spans="1:26" ht="24.95" customHeight="1">
+    <row r="144" spans="1:26" ht="25" customHeight="1">
       <c r="A144" s="29"/>
       <c r="B144" s="17"/>
       <c r="C144" s="17"/>
@@ -30376,7 +30454,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145" spans="1:26" ht="24.95" customHeight="1">
+    <row r="145" spans="1:26" ht="25" customHeight="1">
       <c r="A145" s="28"/>
       <c r="B145" s="25"/>
       <c r="C145" s="25"/>
@@ -30404,7 +30482,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146" spans="1:26" ht="24.95" customHeight="1">
+    <row r="146" spans="1:26" ht="25" customHeight="1">
       <c r="A146" s="29"/>
       <c r="B146" s="17"/>
       <c r="C146" s="17"/>
@@ -30432,7 +30510,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147" spans="1:26" ht="24.95" customHeight="1">
+    <row r="147" spans="1:26" ht="25" customHeight="1">
       <c r="A147" s="28"/>
       <c r="B147" s="25"/>
       <c r="C147" s="25"/>
@@ -30460,7 +30538,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148" spans="1:26" ht="24.95" customHeight="1">
+    <row r="148" spans="1:26" ht="25" customHeight="1">
       <c r="A148" s="29"/>
       <c r="B148" s="17"/>
       <c r="C148" s="17"/>
@@ -30488,7 +30566,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149" spans="1:26" ht="24.95" customHeight="1">
+    <row r="149" spans="1:26" ht="25" customHeight="1">
       <c r="A149" s="28"/>
       <c r="B149" s="25"/>
       <c r="C149" s="25"/>
@@ -30516,7 +30594,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150" spans="1:26" ht="24.95" customHeight="1">
+    <row r="150" spans="1:26" ht="25" customHeight="1">
       <c r="A150" s="29"/>
       <c r="B150" s="17"/>
       <c r="C150" s="17"/>
@@ -30544,7 +30622,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151" spans="1:26" ht="24.95" customHeight="1">
+    <row r="151" spans="1:26" ht="25" customHeight="1">
       <c r="A151" s="28"/>
       <c r="B151" s="25"/>
       <c r="C151" s="25"/>
@@ -30572,7 +30650,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152" spans="1:26" ht="24.95" customHeight="1">
+    <row r="152" spans="1:26" ht="25" customHeight="1">
       <c r="A152" s="29"/>
       <c r="B152" s="17"/>
       <c r="C152" s="17"/>
@@ -30600,7 +30678,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153" spans="1:26" ht="24.95" customHeight="1">
+    <row r="153" spans="1:26" ht="25" customHeight="1">
       <c r="A153" s="28"/>
       <c r="B153" s="25"/>
       <c r="C153" s="25"/>
@@ -30628,7 +30706,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154" spans="1:26" ht="24.95" customHeight="1">
+    <row r="154" spans="1:26" ht="25" customHeight="1">
       <c r="A154" s="29"/>
       <c r="B154" s="17"/>
       <c r="C154" s="17"/>
@@ -30656,7 +30734,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155" spans="1:26" ht="24.95" customHeight="1">
+    <row r="155" spans="1:26" ht="25" customHeight="1">
       <c r="A155" s="28"/>
       <c r="B155" s="25"/>
       <c r="C155" s="25"/>
@@ -30684,7 +30762,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156" spans="1:26" ht="24.95" customHeight="1">
+    <row r="156" spans="1:26" ht="25" customHeight="1">
       <c r="A156" s="29"/>
       <c r="B156" s="17"/>
       <c r="C156" s="17"/>
@@ -30712,7 +30790,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157" spans="1:26" ht="24.95" customHeight="1">
+    <row r="157" spans="1:26" ht="25" customHeight="1">
       <c r="A157" s="28"/>
       <c r="B157" s="25"/>
       <c r="C157" s="25"/>
@@ -30740,7 +30818,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158" spans="1:26" ht="24.95" customHeight="1">
+    <row r="158" spans="1:26" ht="25" customHeight="1">
       <c r="A158" s="29"/>
       <c r="B158" s="17"/>
       <c r="C158" s="17"/>
@@ -30768,7 +30846,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159" spans="1:26" ht="24.95" customHeight="1">
+    <row r="159" spans="1:26" ht="25" customHeight="1">
       <c r="A159" s="28"/>
       <c r="B159" s="25"/>
       <c r="C159" s="25"/>
@@ -30796,7 +30874,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160" spans="1:26" ht="24.95" customHeight="1">
+    <row r="160" spans="1:26" ht="25" customHeight="1">
       <c r="A160" s="29"/>
       <c r="B160" s="17"/>
       <c r="C160" s="17"/>
@@ -30824,7 +30902,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161" spans="1:26" ht="24.95" customHeight="1">
+    <row r="161" spans="1:26" ht="25" customHeight="1">
       <c r="A161" s="28"/>
       <c r="B161" s="25"/>
       <c r="C161" s="25"/>
@@ -30852,7 +30930,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162" spans="1:26" ht="24.95" customHeight="1">
+    <row r="162" spans="1:26" ht="25" customHeight="1">
       <c r="A162" s="29"/>
       <c r="B162" s="17"/>
       <c r="C162" s="17"/>
@@ -30880,7 +30958,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163" spans="1:26" ht="24.95" customHeight="1">
+    <row r="163" spans="1:26" ht="25" customHeight="1">
       <c r="A163" s="28"/>
       <c r="B163" s="25"/>
       <c r="C163" s="25"/>
@@ -30908,7 +30986,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164" spans="1:26" ht="24.95" customHeight="1">
+    <row r="164" spans="1:26" ht="25" customHeight="1">
       <c r="A164" s="29"/>
       <c r="B164" s="17"/>
       <c r="C164" s="17"/>
@@ -30936,7 +31014,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165" spans="1:26" ht="24.95" customHeight="1">
+    <row r="165" spans="1:26" ht="25" customHeight="1">
       <c r="A165" s="28"/>
       <c r="B165" s="25"/>
       <c r="C165" s="25"/>
@@ -30964,7 +31042,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166" spans="1:26" ht="24.95" customHeight="1">
+    <row r="166" spans="1:26" ht="25" customHeight="1">
       <c r="A166" s="29"/>
       <c r="B166" s="17"/>
       <c r="C166" s="17"/>
@@ -30992,7 +31070,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167" spans="1:26" ht="24.95" customHeight="1">
+    <row r="167" spans="1:26" ht="25" customHeight="1">
       <c r="A167" s="28"/>
       <c r="B167" s="25"/>
       <c r="C167" s="25"/>
@@ -31020,7 +31098,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168" spans="1:26" ht="24.95" customHeight="1">
+    <row r="168" spans="1:26" ht="25" customHeight="1">
       <c r="A168" s="29"/>
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
@@ -31048,7 +31126,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169" spans="1:26" ht="24.95" customHeight="1">
+    <row r="169" spans="1:26" ht="25" customHeight="1">
       <c r="A169" s="28"/>
       <c r="B169" s="25"/>
       <c r="C169" s="25"/>
@@ -31076,7 +31154,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170" spans="1:26" ht="24.95" customHeight="1">
+    <row r="170" spans="1:26" ht="25" customHeight="1">
       <c r="A170" s="29"/>
       <c r="B170" s="17"/>
       <c r="C170" s="17"/>
@@ -31104,7 +31182,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171" spans="1:26" ht="24.95" customHeight="1">
+    <row r="171" spans="1:26" ht="25" customHeight="1">
       <c r="A171" s="28"/>
       <c r="B171" s="25"/>
       <c r="C171" s="25"/>
@@ -31132,7 +31210,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172" spans="1:26" ht="24.95" customHeight="1">
+    <row r="172" spans="1:26" ht="25" customHeight="1">
       <c r="A172" s="29"/>
       <c r="B172" s="17"/>
       <c r="C172" s="17"/>
@@ -31160,7 +31238,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173" spans="1:26" ht="24.95" customHeight="1">
+    <row r="173" spans="1:26" ht="25" customHeight="1">
       <c r="A173" s="28"/>
       <c r="B173" s="25"/>
       <c r="C173" s="25"/>
@@ -31188,7 +31266,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174" spans="1:26" ht="24.95" customHeight="1">
+    <row r="174" spans="1:26" ht="25" customHeight="1">
       <c r="A174" s="29"/>
       <c r="B174" s="17"/>
       <c r="C174" s="17"/>
@@ -31216,7 +31294,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175" spans="1:26" ht="24.95" customHeight="1">
+    <row r="175" spans="1:26" ht="25" customHeight="1">
       <c r="A175" s="28"/>
       <c r="B175" s="25"/>
       <c r="C175" s="25"/>
@@ -31244,7 +31322,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176" spans="1:26" ht="24.95" customHeight="1">
+    <row r="176" spans="1:26" ht="25" customHeight="1">
       <c r="A176" s="29"/>
       <c r="B176" s="17"/>
       <c r="C176" s="17"/>
@@ -31272,7 +31350,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177" spans="1:26" ht="24.95" customHeight="1">
+    <row r="177" spans="1:26" ht="25" customHeight="1">
       <c r="A177" s="28"/>
       <c r="B177" s="25"/>
       <c r="C177" s="25"/>
@@ -31300,7 +31378,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178" spans="1:26" ht="24.95" customHeight="1">
+    <row r="178" spans="1:26" ht="25" customHeight="1">
       <c r="A178" s="29"/>
       <c r="B178" s="17"/>
       <c r="C178" s="17"/>
@@ -31328,7 +31406,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179" spans="1:26" ht="24.95" customHeight="1">
+    <row r="179" spans="1:26" ht="25" customHeight="1">
       <c r="A179" s="28"/>
       <c r="B179" s="25"/>
       <c r="C179" s="25"/>
@@ -31356,7 +31434,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180" spans="1:26" ht="24.95" customHeight="1">
+    <row r="180" spans="1:26" ht="25" customHeight="1">
       <c r="A180" s="29"/>
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
@@ -31384,7 +31462,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181" spans="1:26" ht="24.95" customHeight="1">
+    <row r="181" spans="1:26" ht="25" customHeight="1">
       <c r="A181" s="28"/>
       <c r="B181" s="25"/>
       <c r="C181" s="25"/>
@@ -31412,7 +31490,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182" spans="1:26" ht="24.95" customHeight="1">
+    <row r="182" spans="1:26" ht="25" customHeight="1">
       <c r="A182" s="29"/>
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
@@ -31440,7 +31518,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183" spans="1:26" ht="24.95" customHeight="1">
+    <row r="183" spans="1:26" ht="25" customHeight="1">
       <c r="A183" s="28"/>
       <c r="B183" s="25"/>
       <c r="C183" s="25"/>
@@ -31468,7 +31546,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184" spans="1:26" ht="24.95" customHeight="1">
+    <row r="184" spans="1:26" ht="25" customHeight="1">
       <c r="A184" s="29"/>
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
@@ -31496,7 +31574,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185" spans="1:26" ht="24.95" customHeight="1">
+    <row r="185" spans="1:26" ht="25" customHeight="1">
       <c r="A185" s="28"/>
       <c r="B185" s="25"/>
       <c r="C185" s="25"/>
@@ -31524,7 +31602,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186" spans="1:26" ht="24.95" customHeight="1">
+    <row r="186" spans="1:26" ht="25" customHeight="1">
       <c r="A186" s="29"/>
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
@@ -31552,7 +31630,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187" spans="1:26" ht="24.95" customHeight="1">
+    <row r="187" spans="1:26" ht="25" customHeight="1">
       <c r="A187" s="28"/>
       <c r="B187" s="25"/>
       <c r="C187" s="25"/>
@@ -31580,7 +31658,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188" spans="1:26" ht="24.95" customHeight="1">
+    <row r="188" spans="1:26" ht="25" customHeight="1">
       <c r="A188" s="29"/>
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
@@ -31608,7 +31686,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189" spans="1:26" ht="24.95" customHeight="1">
+    <row r="189" spans="1:26" ht="25" customHeight="1">
       <c r="A189" s="28"/>
       <c r="B189" s="25"/>
       <c r="C189" s="25"/>
@@ -31636,7 +31714,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190" spans="1:26" ht="24.95" customHeight="1">
+    <row r="190" spans="1:26" ht="25" customHeight="1">
       <c r="A190" s="29"/>
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
@@ -31664,7 +31742,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191" spans="1:26" ht="24.95" customHeight="1">
+    <row r="191" spans="1:26" ht="25" customHeight="1">
       <c r="A191" s="28"/>
       <c r="B191" s="25"/>
       <c r="C191" s="25"/>
@@ -31692,7 +31770,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192" spans="1:26" ht="24.95" customHeight="1">
+    <row r="192" spans="1:26" ht="25" customHeight="1">
       <c r="A192" s="29"/>
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
@@ -31720,7 +31798,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193" spans="1:26" ht="24.95" customHeight="1">
+    <row r="193" spans="1:26" ht="25" customHeight="1">
       <c r="A193" s="28"/>
       <c r="B193" s="25"/>
       <c r="C193" s="25"/>
@@ -31748,7 +31826,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194" spans="1:26" ht="24.95" customHeight="1">
+    <row r="194" spans="1:26" ht="25" customHeight="1">
       <c r="A194" s="29"/>
       <c r="B194" s="17"/>
       <c r="C194" s="17"/>
@@ -31776,7 +31854,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195" spans="1:26" ht="24.95" customHeight="1">
+    <row r="195" spans="1:26" ht="25" customHeight="1">
       <c r="A195" s="28"/>
       <c r="B195" s="25"/>
       <c r="C195" s="25"/>
@@ -31804,7 +31882,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196" spans="1:26" ht="24.95" customHeight="1">
+    <row r="196" spans="1:26" ht="25" customHeight="1">
       <c r="A196" s="29"/>
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
@@ -31832,7 +31910,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197" spans="1:26" ht="24.95" customHeight="1">
+    <row r="197" spans="1:26" ht="25" customHeight="1">
       <c r="A197" s="28"/>
       <c r="B197" s="25"/>
       <c r="C197" s="25"/>
@@ -31860,7 +31938,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198" spans="1:26" ht="24.95" customHeight="1">
+    <row r="198" spans="1:26" ht="25" customHeight="1">
       <c r="A198" s="29"/>
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
@@ -31888,7 +31966,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199" spans="1:26" ht="24.95" customHeight="1">
+    <row r="199" spans="1:26" ht="25" customHeight="1">
       <c r="A199" s="28"/>
       <c r="B199" s="25"/>
       <c r="C199" s="25"/>
@@ -31916,7 +31994,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200" spans="1:26" ht="24.95" customHeight="1">
+    <row r="200" spans="1:26" ht="25" customHeight="1">
       <c r="A200" s="29"/>
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
@@ -31944,7 +32022,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201" spans="1:26" ht="24.95" customHeight="1">
+    <row r="201" spans="1:26" ht="25" customHeight="1">
       <c r="A201" s="28"/>
       <c r="B201" s="25"/>
       <c r="C201" s="25"/>
@@ -31972,7 +32050,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202" spans="1:26" ht="24.95" customHeight="1">
+    <row r="202" spans="1:26" ht="25" customHeight="1">
       <c r="A202" s="29"/>
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
@@ -32000,7 +32078,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203" spans="1:26" ht="24.95" customHeight="1">
+    <row r="203" spans="1:26" ht="25" customHeight="1">
       <c r="A203" s="28"/>
       <c r="B203" s="25"/>
       <c r="C203" s="25"/>
@@ -32028,7 +32106,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204" spans="1:26" ht="24.95" customHeight="1">
+    <row r="204" spans="1:26" ht="25" customHeight="1">
       <c r="A204" s="30"/>
       <c r="B204" s="20"/>
       <c r="C204" s="20"/>
@@ -33362,10 +33440,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G204">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>G5="Strong"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>G5="Needs Revision"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -33411,7 +33489,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="4" width="11" customWidth="1"/>
@@ -33420,34 +33498,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="62"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
-    </row>
-    <row r="3" spans="1:10" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="65"/>
+    </row>
+    <row r="3" spans="1:10" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -33491,7 +33569,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="63.95" customHeight="1">
+    <row r="5" spans="1:10" ht="64" customHeight="1">
       <c r="A5" s="33" t="s">
         <v>47</v>
       </c>
@@ -33521,7 +33599,7 @@
       </c>
       <c r="J5" s="27"/>
     </row>
-    <row r="6" spans="1:10" ht="63.95" customHeight="1">
+    <row r="6" spans="1:10" ht="64" customHeight="1">
       <c r="A6" s="31" t="s">
         <v>47</v>
       </c>
@@ -33551,7 +33629,7 @@
       </c>
       <c r="J6" s="19"/>
     </row>
-    <row r="7" spans="1:10" ht="63.95" customHeight="1">
+    <row r="7" spans="1:10" ht="64" customHeight="1">
       <c r="A7" s="33" t="s">
         <v>47</v>
       </c>
@@ -33581,7 +33659,7 @@
       </c>
       <c r="J7" s="27"/>
     </row>
-    <row r="8" spans="1:10" ht="63.95" customHeight="1">
+    <row r="8" spans="1:10" ht="64" customHeight="1">
       <c r="A8" s="31" t="s">
         <v>47</v>
       </c>
@@ -33611,7 +33689,7 @@
       </c>
       <c r="J8" s="19"/>
     </row>
-    <row r="9" spans="1:10" ht="63.95" customHeight="1">
+    <row r="9" spans="1:10" ht="64" customHeight="1">
       <c r="A9" s="33" t="s">
         <v>47</v>
       </c>
@@ -33641,7 +33719,7 @@
       </c>
       <c r="J9" s="27"/>
     </row>
-    <row r="10" spans="1:10" ht="63.95" customHeight="1">
+    <row r="10" spans="1:10" ht="64" customHeight="1">
       <c r="A10" s="31" t="s">
         <v>47</v>
       </c>
@@ -33671,7 +33749,7 @@
       </c>
       <c r="J10" s="19"/>
     </row>
-    <row r="11" spans="1:10" ht="63.95" customHeight="1">
+    <row r="11" spans="1:10" ht="64" customHeight="1">
       <c r="A11" s="33" t="s">
         <v>33</v>
       </c>
@@ -33701,7 +33779,7 @@
       </c>
       <c r="J11" s="27"/>
     </row>
-    <row r="12" spans="1:10" ht="63.95" customHeight="1">
+    <row r="12" spans="1:10" ht="64" customHeight="1">
       <c r="A12" s="31" t="s">
         <v>33</v>
       </c>
@@ -33731,7 +33809,7 @@
       </c>
       <c r="J12" s="19"/>
     </row>
-    <row r="13" spans="1:10" ht="63.95" customHeight="1">
+    <row r="13" spans="1:10" ht="64" customHeight="1">
       <c r="A13" s="33" t="s">
         <v>33</v>
       </c>
@@ -33761,7 +33839,7 @@
       </c>
       <c r="J13" s="27"/>
     </row>
-    <row r="14" spans="1:10" ht="63.95" customHeight="1">
+    <row r="14" spans="1:10" ht="64" customHeight="1">
       <c r="A14" s="31" t="s">
         <v>33</v>
       </c>
@@ -33791,7 +33869,7 @@
       </c>
       <c r="J14" s="19"/>
     </row>
-    <row r="15" spans="1:10" ht="63.95" customHeight="1">
+    <row r="15" spans="1:10" ht="64" customHeight="1">
       <c r="A15" s="33" t="s">
         <v>33</v>
       </c>
@@ -33821,7 +33899,7 @@
       </c>
       <c r="J15" s="27"/>
     </row>
-    <row r="16" spans="1:10" ht="63.95" customHeight="1">
+    <row r="16" spans="1:10" ht="64" customHeight="1">
       <c r="A16" s="32" t="s">
         <v>33</v>
       </c>
@@ -33869,7 +33947,7 @@
     <tabColor rgb="FF24374B"/>
   </sheetPr>
   <dimension ref="A1:Z250"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
     <col min="3" max="4" width="30" customWidth="1"/>
@@ -33878,32 +33956,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="38.1" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="60" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="59"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="62"/>
     </row>
     <row r="2" spans="1:26" ht="30" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="62"/>
-    </row>
-    <row r="3" spans="1:26" ht="24.95" customHeight="1">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
+    </row>
+    <row r="3" spans="1:26" ht="25" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -33914,7 +33992,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:26" ht="15">
+    <row r="4" spans="1:26" ht="14.1">
       <c r="A4" s="23" t="s">
         <v>178</v>
       </c>
@@ -34044,7 +34122,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="24.95" customHeight="1">
+    <row r="8" spans="1:26" ht="25" customHeight="1">
       <c r="A8" s="29"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -34072,7 +34150,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9" spans="1:26" ht="24.95" customHeight="1">
+    <row r="9" spans="1:26" ht="25" customHeight="1">
       <c r="A9" s="28"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
@@ -34100,7 +34178,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10" spans="1:26" ht="24.95" customHeight="1">
+    <row r="10" spans="1:26" ht="25" customHeight="1">
       <c r="A10" s="29"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -34128,7 +34206,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="24.95" customHeight="1">
+    <row r="11" spans="1:26" ht="25" customHeight="1">
       <c r="A11" s="28"/>
       <c r="B11" s="25"/>
       <c r="C11" s="25"/>
@@ -34156,7 +34234,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12" spans="1:26" ht="24.95" customHeight="1">
+    <row r="12" spans="1:26" ht="25" customHeight="1">
       <c r="A12" s="29"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
@@ -34184,7 +34262,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13" spans="1:26" ht="24.95" customHeight="1">
+    <row r="13" spans="1:26" ht="25" customHeight="1">
       <c r="A13" s="28"/>
       <c r="B13" s="25"/>
       <c r="C13" s="25"/>
@@ -34212,7 +34290,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14" spans="1:26" ht="24.95" customHeight="1">
+    <row r="14" spans="1:26" ht="25" customHeight="1">
       <c r="A14" s="29"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -34240,7 +34318,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" ht="24.95" customHeight="1">
+    <row r="15" spans="1:26" ht="25" customHeight="1">
       <c r="A15" s="28"/>
       <c r="B15" s="25"/>
       <c r="C15" s="25"/>
@@ -34268,7 +34346,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" ht="24.95" customHeight="1">
+    <row r="16" spans="1:26" ht="25" customHeight="1">
       <c r="A16" s="29"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
@@ -34296,7 +34374,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="24.95" customHeight="1">
+    <row r="17" spans="1:26" ht="25" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -34324,7 +34402,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" ht="24.95" customHeight="1">
+    <row r="18" spans="1:26" ht="25" customHeight="1">
       <c r="A18" s="29"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
@@ -34352,7 +34430,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="24.95" customHeight="1">
+    <row r="19" spans="1:26" ht="25" customHeight="1">
       <c r="A19" s="28"/>
       <c r="B19" s="25"/>
       <c r="C19" s="25"/>
@@ -34380,7 +34458,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" ht="24.95" customHeight="1">
+    <row r="20" spans="1:26" ht="25" customHeight="1">
       <c r="A20" s="29"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
@@ -34408,7 +34486,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="24.95" customHeight="1">
+    <row r="21" spans="1:26" ht="25" customHeight="1">
       <c r="A21" s="28"/>
       <c r="B21" s="25"/>
       <c r="C21" s="25"/>
@@ -34436,7 +34514,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22" spans="1:26" ht="24.95" customHeight="1">
+    <row r="22" spans="1:26" ht="25" customHeight="1">
       <c r="A22" s="29"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -34464,7 +34542,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23" spans="1:26" ht="24.95" customHeight="1">
+    <row r="23" spans="1:26" ht="25" customHeight="1">
       <c r="A23" s="28"/>
       <c r="B23" s="25"/>
       <c r="C23" s="25"/>
@@ -34492,7 +34570,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="24.95" customHeight="1">
+    <row r="24" spans="1:26" ht="25" customHeight="1">
       <c r="A24" s="29"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -34520,7 +34598,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="24.95" customHeight="1">
+    <row r="25" spans="1:26" ht="25" customHeight="1">
       <c r="A25" s="28"/>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
@@ -34548,7 +34626,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26" spans="1:26" ht="24.95" customHeight="1">
+    <row r="26" spans="1:26" ht="25" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -34576,7 +34654,7 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
     </row>
-    <row r="27" spans="1:26" ht="24.95" customHeight="1">
+    <row r="27" spans="1:26" ht="25" customHeight="1">
       <c r="A27" s="28"/>
       <c r="B27" s="25"/>
       <c r="C27" s="25"/>
@@ -34604,7 +34682,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28" spans="1:26" ht="24.95" customHeight="1">
+    <row r="28" spans="1:26" ht="25" customHeight="1">
       <c r="A28" s="29"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -34632,7 +34710,7 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="24.95" customHeight="1">
+    <row r="29" spans="1:26" ht="25" customHeight="1">
       <c r="A29" s="28"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -34660,7 +34738,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="24.95" customHeight="1">
+    <row r="30" spans="1:26" ht="25" customHeight="1">
       <c r="A30" s="29"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
@@ -34688,7 +34766,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31" spans="1:26" ht="24.95" customHeight="1">
+    <row r="31" spans="1:26" ht="25" customHeight="1">
       <c r="A31" s="28"/>
       <c r="B31" s="25"/>
       <c r="C31" s="25"/>
@@ -34716,7 +34794,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="24.95" customHeight="1">
+    <row r="32" spans="1:26" ht="25" customHeight="1">
       <c r="A32" s="29"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -34744,7 +34822,7 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33" spans="1:26" ht="24.95" customHeight="1">
+    <row r="33" spans="1:26" ht="25" customHeight="1">
       <c r="A33" s="28"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -34772,7 +34850,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="24.95" customHeight="1">
+    <row r="34" spans="1:26" ht="25" customHeight="1">
       <c r="A34" s="29"/>
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
@@ -34800,7 +34878,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="24.95" customHeight="1">
+    <row r="35" spans="1:26" ht="25" customHeight="1">
       <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
@@ -34828,7 +34906,7 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36" spans="1:26" ht="24.95" customHeight="1">
+    <row r="36" spans="1:26" ht="25" customHeight="1">
       <c r="A36" s="29"/>
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
@@ -34856,7 +34934,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37" spans="1:26" ht="24.95" customHeight="1">
+    <row r="37" spans="1:26" ht="25" customHeight="1">
       <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="25"/>
@@ -34884,7 +34962,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38" spans="1:26" ht="24.95" customHeight="1">
+    <row r="38" spans="1:26" ht="25" customHeight="1">
       <c r="A38" s="29"/>
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
@@ -34912,7 +34990,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39" spans="1:26" ht="24.95" customHeight="1">
+    <row r="39" spans="1:26" ht="25" customHeight="1">
       <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="25"/>
@@ -34940,7 +35018,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40" spans="1:26" ht="24.95" customHeight="1">
+    <row r="40" spans="1:26" ht="25" customHeight="1">
       <c r="A40" s="29"/>
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
@@ -34968,7 +35046,7 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41" spans="1:26" ht="24.95" customHeight="1">
+    <row r="41" spans="1:26" ht="25" customHeight="1">
       <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="25"/>
@@ -34996,7 +35074,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42" spans="1:26" ht="24.95" customHeight="1">
+    <row r="42" spans="1:26" ht="25" customHeight="1">
       <c r="A42" s="29"/>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -35024,7 +35102,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43" spans="1:26" ht="24.95" customHeight="1">
+    <row r="43" spans="1:26" ht="25" customHeight="1">
       <c r="A43" s="28"/>
       <c r="B43" s="25"/>
       <c r="C43" s="25"/>
@@ -35052,7 +35130,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44" spans="1:26" ht="24.95" customHeight="1">
+    <row r="44" spans="1:26" ht="25" customHeight="1">
       <c r="A44" s="29"/>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -35080,7 +35158,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45" spans="1:26" ht="24.95" customHeight="1">
+    <row r="45" spans="1:26" ht="25" customHeight="1">
       <c r="A45" s="28"/>
       <c r="B45" s="25"/>
       <c r="C45" s="25"/>
@@ -35108,7 +35186,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46" spans="1:26" ht="24.95" customHeight="1">
+    <row r="46" spans="1:26" ht="25" customHeight="1">
       <c r="A46" s="29"/>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -35136,7 +35214,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47" spans="1:26" ht="24.95" customHeight="1">
+    <row r="47" spans="1:26" ht="25" customHeight="1">
       <c r="A47" s="28"/>
       <c r="B47" s="25"/>
       <c r="C47" s="25"/>
@@ -35164,7 +35242,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48" spans="1:26" ht="24.95" customHeight="1">
+    <row r="48" spans="1:26" ht="25" customHeight="1">
       <c r="A48" s="29"/>
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
@@ -35192,7 +35270,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49" spans="1:26" ht="24.95" customHeight="1">
+    <row r="49" spans="1:26" ht="25" customHeight="1">
       <c r="A49" s="28"/>
       <c r="B49" s="25"/>
       <c r="C49" s="25"/>
@@ -35220,7 +35298,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50" spans="1:26" ht="24.95" customHeight="1">
+    <row r="50" spans="1:26" ht="25" customHeight="1">
       <c r="A50" s="29"/>
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
@@ -35248,7 +35326,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51" spans="1:26" ht="24.95" customHeight="1">
+    <row r="51" spans="1:26" ht="25" customHeight="1">
       <c r="A51" s="28"/>
       <c r="B51" s="25"/>
       <c r="C51" s="25"/>
@@ -35276,7 +35354,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52" spans="1:26" ht="24.95" customHeight="1">
+    <row r="52" spans="1:26" ht="25" customHeight="1">
       <c r="A52" s="29"/>
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
@@ -35304,7 +35382,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53" spans="1:26" ht="24.95" customHeight="1">
+    <row r="53" spans="1:26" ht="25" customHeight="1">
       <c r="A53" s="28"/>
       <c r="B53" s="25"/>
       <c r="C53" s="25"/>
@@ -35332,7 +35410,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54" spans="1:26" ht="24.95" customHeight="1">
+    <row r="54" spans="1:26" ht="25" customHeight="1">
       <c r="A54" s="29"/>
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
@@ -35360,7 +35438,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55" spans="1:26" ht="24.95" customHeight="1">
+    <row r="55" spans="1:26" ht="25" customHeight="1">
       <c r="A55" s="28"/>
       <c r="B55" s="25"/>
       <c r="C55" s="25"/>
@@ -35388,7 +35466,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56" spans="1:26" ht="24.95" customHeight="1">
+    <row r="56" spans="1:26" ht="25" customHeight="1">
       <c r="A56" s="29"/>
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
@@ -35416,7 +35494,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57" spans="1:26" ht="24.95" customHeight="1">
+    <row r="57" spans="1:26" ht="25" customHeight="1">
       <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="25"/>
@@ -35444,7 +35522,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58" spans="1:26" ht="24.95" customHeight="1">
+    <row r="58" spans="1:26" ht="25" customHeight="1">
       <c r="A58" s="29"/>
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
@@ -35472,7 +35550,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59" spans="1:26" ht="24.95" customHeight="1">
+    <row r="59" spans="1:26" ht="25" customHeight="1">
       <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="25"/>
@@ -35500,7 +35578,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60" spans="1:26" ht="24.95" customHeight="1">
+    <row r="60" spans="1:26" ht="25" customHeight="1">
       <c r="A60" s="29"/>
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
@@ -35528,7 +35606,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61" spans="1:26" ht="24.95" customHeight="1">
+    <row r="61" spans="1:26" ht="25" customHeight="1">
       <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="25"/>
@@ -35556,7 +35634,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62" spans="1:26" ht="24.95" customHeight="1">
+    <row r="62" spans="1:26" ht="25" customHeight="1">
       <c r="A62" s="29"/>
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
@@ -35584,7 +35662,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63" spans="1:26" ht="24.95" customHeight="1">
+    <row r="63" spans="1:26" ht="25" customHeight="1">
       <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="25"/>
@@ -35612,7 +35690,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64" spans="1:26" ht="24.95" customHeight="1">
+    <row r="64" spans="1:26" ht="25" customHeight="1">
       <c r="A64" s="29"/>
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
@@ -35640,7 +35718,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65" spans="1:26" ht="24.95" customHeight="1">
+    <row r="65" spans="1:26" ht="25" customHeight="1">
       <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="25"/>
@@ -35668,7 +35746,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66" spans="1:26" ht="24.95" customHeight="1">
+    <row r="66" spans="1:26" ht="25" customHeight="1">
       <c r="A66" s="29"/>
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
@@ -35696,7 +35774,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67" spans="1:26" ht="24.95" customHeight="1">
+    <row r="67" spans="1:26" ht="25" customHeight="1">
       <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="25"/>
@@ -35724,7 +35802,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68" spans="1:26" ht="24.95" customHeight="1">
+    <row r="68" spans="1:26" ht="25" customHeight="1">
       <c r="A68" s="29"/>
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
@@ -35752,7 +35830,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69" spans="1:26" ht="24.95" customHeight="1">
+    <row r="69" spans="1:26" ht="25" customHeight="1">
       <c r="A69" s="28"/>
       <c r="B69" s="25"/>
       <c r="C69" s="25"/>
@@ -35780,7 +35858,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70" spans="1:26" ht="24.95" customHeight="1">
+    <row r="70" spans="1:26" ht="25" customHeight="1">
       <c r="A70" s="29"/>
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
@@ -35808,7 +35886,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71" spans="1:26" ht="24.95" customHeight="1">
+    <row r="71" spans="1:26" ht="25" customHeight="1">
       <c r="A71" s="28"/>
       <c r="B71" s="25"/>
       <c r="C71" s="25"/>
@@ -35836,7 +35914,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72" spans="1:26" ht="24.95" customHeight="1">
+    <row r="72" spans="1:26" ht="25" customHeight="1">
       <c r="A72" s="29"/>
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
@@ -35864,7 +35942,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73" spans="1:26" ht="24.95" customHeight="1">
+    <row r="73" spans="1:26" ht="25" customHeight="1">
       <c r="A73" s="28"/>
       <c r="B73" s="25"/>
       <c r="C73" s="25"/>
@@ -35892,7 +35970,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74" spans="1:26" ht="24.95" customHeight="1">
+    <row r="74" spans="1:26" ht="25" customHeight="1">
       <c r="A74" s="29"/>
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
@@ -35920,7 +35998,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75" spans="1:26" ht="24.95" customHeight="1">
+    <row r="75" spans="1:26" ht="25" customHeight="1">
       <c r="A75" s="28"/>
       <c r="B75" s="25"/>
       <c r="C75" s="25"/>
@@ -35948,7 +36026,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76" spans="1:26" ht="24.95" customHeight="1">
+    <row r="76" spans="1:26" ht="25" customHeight="1">
       <c r="A76" s="29"/>
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
@@ -35976,7 +36054,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77" spans="1:26" ht="24.95" customHeight="1">
+    <row r="77" spans="1:26" ht="25" customHeight="1">
       <c r="A77" s="28"/>
       <c r="B77" s="25"/>
       <c r="C77" s="25"/>
@@ -36004,7 +36082,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78" spans="1:26" ht="24.95" customHeight="1">
+    <row r="78" spans="1:26" ht="25" customHeight="1">
       <c r="A78" s="29"/>
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
@@ -36032,7 +36110,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79" spans="1:26" ht="24.95" customHeight="1">
+    <row r="79" spans="1:26" ht="25" customHeight="1">
       <c r="A79" s="28"/>
       <c r="B79" s="25"/>
       <c r="C79" s="25"/>
@@ -36060,7 +36138,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80" spans="1:26" ht="24.95" customHeight="1">
+    <row r="80" spans="1:26" ht="25" customHeight="1">
       <c r="A80" s="29"/>
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
@@ -36088,7 +36166,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81" spans="1:26" ht="24.95" customHeight="1">
+    <row r="81" spans="1:26" ht="25" customHeight="1">
       <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="25"/>
@@ -36116,7 +36194,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82" spans="1:26" ht="24.95" customHeight="1">
+    <row r="82" spans="1:26" ht="25" customHeight="1">
       <c r="A82" s="29"/>
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
@@ -36144,7 +36222,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83" spans="1:26" ht="24.95" customHeight="1">
+    <row r="83" spans="1:26" ht="25" customHeight="1">
       <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="25"/>
@@ -36172,7 +36250,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84" spans="1:26" ht="24.95" customHeight="1">
+    <row r="84" spans="1:26" ht="25" customHeight="1">
       <c r="A84" s="29"/>
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
@@ -36200,7 +36278,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85" spans="1:26" ht="24.95" customHeight="1">
+    <row r="85" spans="1:26" ht="25" customHeight="1">
       <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="25"/>
@@ -36228,7 +36306,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86" spans="1:26" ht="24.95" customHeight="1">
+    <row r="86" spans="1:26" ht="25" customHeight="1">
       <c r="A86" s="29"/>
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
@@ -36256,7 +36334,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87" spans="1:26" ht="24.95" customHeight="1">
+    <row r="87" spans="1:26" ht="25" customHeight="1">
       <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="25"/>
@@ -36284,7 +36362,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88" spans="1:26" ht="24.95" customHeight="1">
+    <row r="88" spans="1:26" ht="25" customHeight="1">
       <c r="A88" s="29"/>
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
@@ -36312,7 +36390,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89" spans="1:26" ht="24.95" customHeight="1">
+    <row r="89" spans="1:26" ht="25" customHeight="1">
       <c r="A89" s="28"/>
       <c r="B89" s="25"/>
       <c r="C89" s="25"/>
@@ -36340,7 +36418,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90" spans="1:26" ht="24.95" customHeight="1">
+    <row r="90" spans="1:26" ht="25" customHeight="1">
       <c r="A90" s="29"/>
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
@@ -36368,7 +36446,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91" spans="1:26" ht="24.95" customHeight="1">
+    <row r="91" spans="1:26" ht="25" customHeight="1">
       <c r="A91" s="28"/>
       <c r="B91" s="25"/>
       <c r="C91" s="25"/>
@@ -36396,7 +36474,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92" spans="1:26" ht="24.95" customHeight="1">
+    <row r="92" spans="1:26" ht="25" customHeight="1">
       <c r="A92" s="29"/>
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
@@ -36424,7 +36502,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93" spans="1:26" ht="24.95" customHeight="1">
+    <row r="93" spans="1:26" ht="25" customHeight="1">
       <c r="A93" s="28"/>
       <c r="B93" s="25"/>
       <c r="C93" s="25"/>
@@ -36452,7 +36530,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94" spans="1:26" ht="24.95" customHeight="1">
+    <row r="94" spans="1:26" ht="25" customHeight="1">
       <c r="A94" s="29"/>
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
@@ -36480,7 +36558,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95" spans="1:26" ht="24.95" customHeight="1">
+    <row r="95" spans="1:26" ht="25" customHeight="1">
       <c r="A95" s="28"/>
       <c r="B95" s="25"/>
       <c r="C95" s="25"/>
@@ -36508,7 +36586,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96" spans="1:26" ht="24.95" customHeight="1">
+    <row r="96" spans="1:26" ht="25" customHeight="1">
       <c r="A96" s="29"/>
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
@@ -36536,7 +36614,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97" spans="1:26" ht="24.95" customHeight="1">
+    <row r="97" spans="1:26" ht="25" customHeight="1">
       <c r="A97" s="28"/>
       <c r="B97" s="25"/>
       <c r="C97" s="25"/>
@@ -36564,7 +36642,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98" spans="1:26" ht="24.95" customHeight="1">
+    <row r="98" spans="1:26" ht="25" customHeight="1">
       <c r="A98" s="29"/>
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
@@ -36592,7 +36670,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99" spans="1:26" ht="24.95" customHeight="1">
+    <row r="99" spans="1:26" ht="25" customHeight="1">
       <c r="A99" s="28"/>
       <c r="B99" s="25"/>
       <c r="C99" s="25"/>
@@ -36620,7 +36698,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100" spans="1:26" ht="24.95" customHeight="1">
+    <row r="100" spans="1:26" ht="25" customHeight="1">
       <c r="A100" s="29"/>
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
@@ -36648,7 +36726,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101" spans="1:26" ht="24.95" customHeight="1">
+    <row r="101" spans="1:26" ht="25" customHeight="1">
       <c r="A101" s="28"/>
       <c r="B101" s="25"/>
       <c r="C101" s="25"/>
@@ -36676,7 +36754,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102" spans="1:26" ht="24.95" customHeight="1">
+    <row r="102" spans="1:26" ht="25" customHeight="1">
       <c r="A102" s="29"/>
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
@@ -36704,7 +36782,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103" spans="1:26" ht="24.95" customHeight="1">
+    <row r="103" spans="1:26" ht="25" customHeight="1">
       <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="25"/>
@@ -36732,7 +36810,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104" spans="1:26" ht="24.95" customHeight="1">
+    <row r="104" spans="1:26" ht="25" customHeight="1">
       <c r="A104" s="30"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -40854,13 +40932,13 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="F5:F104">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>F5="Completed"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>F5="In Progress"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>F5="Needs Revision"</formula>
     </cfRule>
   </conditionalFormatting>
